--- a/Libro_Contable_ALTUS_26_Auditado.xlsx
+++ b/Libro_Contable_ALTUS_26_Auditado.xlsx
@@ -66,7 +66,7 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
@@ -75,9 +75,9 @@
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
-    <col min="15" max="15" width="48" customWidth="1"/>
+    <col min="15" max="15" width="58" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -143,7 +143,7 @@
       </c>
       <c r="M1" t="inlineStr" s="1">
         <is>
-          <t>Soporte / FEL / Boleta</t>
+          <t>No. Docto Banco / FEL</t>
         </is>
       </c>
       <c r="N1" t="inlineStr" s="1">
@@ -153,7 +153,7 @@
       </c>
       <c r="O1" t="inlineStr" s="1">
         <is>
-          <t>Nota de Auditoría SAT</t>
+          <t>Nota de Auditoría y Conciliación BI</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>03-Eventos/ Extras</t>
+          <t>00-Administración</t>
         </is>
       </c>
     </row>
@@ -1396,11 +1396,6 @@
           <t>00-Administración</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2452,7 +2447,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>03-Eventos/ Extras</t>
+          <t>00-Administración</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2638,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Reclasificado de 5210 a 2105: Entero a SAT de ISR retenido a empleadas.</t>
+          <t>Reclasificado a 2105 ISR Retenciones por Pagar</t>
         </is>
       </c>
     </row>
@@ -3266,11 +3261,6 @@
           <t>00-Administración</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3307,10 +3297,10 @@
         <v>1075.0</v>
       </c>
       <c r="H52">
-        <v>115.18</v>
+        <v>0.0</v>
       </c>
       <c r="I52">
-        <v>959.82</v>
+        <v>1075.0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3767,11 +3757,6 @@
           <t>00-Administración</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4332,7 +4317,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Reclasificado de 5210 a 2105: Entero a SAT de ISR retenido a empleadas.</t>
+          <t>Reclasificado a 2105 ISR Retenciones por Pagar</t>
         </is>
       </c>
     </row>
@@ -5265,11 +5250,6 @@
           <t>00-Administración</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6388,7 +6368,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Reclasificado de 5210 a 2105: Entero a SAT de ISR retenido a empleadas.</t>
+          <t>Reclasificado a 2105 ISR Retenciones por Pagar</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6430,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>03-Eventos/ Extras</t>
+          <t>00-Administración</t>
         </is>
       </c>
     </row>
@@ -7383,11 +7363,6 @@
           <t>00-Administración</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7796,10 +7771,10 @@
         <v>300.0</v>
       </c>
       <c r="H124">
-        <v>32.14</v>
+        <v>0.0</v>
       </c>
       <c r="I124">
-        <v>267.86</v>
+        <v>300.0</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -8292,10 +8267,10 @@
         <v>100.0</v>
       </c>
       <c r="H132">
-        <v>10.71</v>
+        <v>0.0</v>
       </c>
       <c r="I132">
-        <v>89.29</v>
+        <v>100.0</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -8444,7 +8419,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Pagado desde BI-Ahorro (Originalmente en 5210 - Impuestos, tasas y arbitrios). Liquida pasivo IGSS sin duplicar gasto.</t>
+          <t>Pagado desde BI-Ahorro (Liquida pasivo 2103 IGSS)</t>
         </is>
       </c>
     </row>
@@ -8545,10 +8520,10 @@
         <v>300.0</v>
       </c>
       <c r="H136">
-        <v>32.14</v>
+        <v>0.0</v>
       </c>
       <c r="I136">
-        <v>267.86</v>
+        <v>300.0</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -8759,7 +8734,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Reclasificado de 5210 a 2105: Entero a SAT de ISR retenido a empleadas.</t>
+          <t>Reclasificado a 2105 ISR Retenciones por Pagar</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9111,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Pagado desde BI-Ahorro (Originalmente en 5102 - Cuota Patronal IGSS). Liquida pasivo IGSS sin duplicar gasto.</t>
+          <t>Pagado desde BI-Ahorro (Liquida pasivo 2103 IGSS)</t>
         </is>
       </c>
     </row>
@@ -9201,11 +9176,6 @@
           <t>00-Administración</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9764,11 +9734,6 @@
           <t>00-Administración</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9952,7 +9917,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>03-Eventos/ Extras</t>
+          <t>00-Administración</t>
         </is>
       </c>
     </row>
@@ -10036,27 +10001,27 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Pago final 2/2 Papelería maestra Glendy</t>
+          <t>Cobro mensualidad junio Andrei González</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G160">
-        <v>1000.0</v>
+        <v>3800.0</v>
       </c>
       <c r="H160">
-        <v>107.14</v>
+        <v>0.0</v>
       </c>
       <c r="I160">
-        <v>892.86</v>
+        <v>3800.0</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -10064,19 +10029,24 @@
         </is>
       </c>
       <c r="K160">
-        <v>58649.68</v>
+        <v>63449.68</v>
       </c>
       <c r="L160">
         <v>44242.49</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>AUT-20260601-159</t>
+          <t>BI-1104767</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10098,27 +10068,27 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Andrei González</t>
+          <t>Débito BiCheque comisión manejo de cuenta junio</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G161">
-        <v>3800.0</v>
+        <v>15.0</v>
       </c>
       <c r="H161">
         <v>0.0</v>
       </c>
       <c r="I161">
-        <v>3800.0</v>
+        <v>15.0</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -10126,19 +10096,24 @@
         </is>
       </c>
       <c r="K161">
-        <v>62449.68</v>
+        <v>63434.68</v>
       </c>
       <c r="L161">
         <v>44242.49</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>AUT-20260601-160</t>
+          <t>BI-310125</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Agregado según extracto BI 01/06/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10125,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10160,27 +10135,27 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Adriana García</t>
+          <t>Pago final 2/2 Papelería maestra Glendy</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G162">
-        <v>9300.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H162">
-        <v>0.0</v>
+        <v>107.14</v>
       </c>
       <c r="I162">
-        <v>9300.0</v>
+        <v>892.86</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -10188,19 +10163,24 @@
         </is>
       </c>
       <c r="K162">
-        <v>71749.68</v>
+        <v>62434.68</v>
       </c>
       <c r="L162">
         <v>44242.49</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>AUT-20260602-161</t>
+          <t>BI-1223575</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10192,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10250,19 +10230,24 @@
         </is>
       </c>
       <c r="K163">
-        <v>72791.68</v>
+        <v>63476.68</v>
       </c>
       <c r="L163">
         <v>44242.49</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>AUT-20260603-162</t>
+          <t>BI-158655-A</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Parte de transferencia ACH Valeria Márquez Q2,758.33</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10259,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10284,7 +10269,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Cobro anticipo 5/6 inscripcion Günther Márquez</t>
+          <t>Cobro anticipo 5/6 inscripción Günther Márquez</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10298,13 +10283,13 @@
         </is>
       </c>
       <c r="G164">
-        <v>1716.66</v>
+        <v>1716.33</v>
       </c>
       <c r="H164">
         <v>0.0</v>
       </c>
       <c r="I164">
-        <v>1716.66</v>
+        <v>1716.33</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -10312,19 +10297,24 @@
         </is>
       </c>
       <c r="K164">
-        <v>74508.34</v>
+        <v>65193.01</v>
       </c>
       <c r="L164">
         <v>44242.49</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>AUT-20260603-163</t>
+          <t>BI-158655-B</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Ajustado de Q1,716.66 a Q1,716.33 para cuadrar exacto con ACH BI-158655 (Q2,758.33)</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10326,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10346,7 +10336,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Gabriel Ruíz</t>
+          <t>Cobro mensualidad junio Adriana García</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10374,19 +10364,24 @@
         </is>
       </c>
       <c r="K165">
-        <v>83808.34</v>
+        <v>74493.01</v>
       </c>
       <c r="L165">
         <v>44242.49</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>AUT-20260603-164</t>
+          <t>BI-2156954</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 02/06/2026</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10393,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10408,27 +10403,27 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Google Workspace_altus</t>
+          <t>Cobro mensualidad junio Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G166">
-        <v>234.66</v>
+        <v>9300.0</v>
       </c>
       <c r="H166">
-        <v>25.14</v>
+        <v>0.0</v>
       </c>
       <c r="I166">
-        <v>209.52</v>
+        <v>9300.0</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -10436,19 +10431,24 @@
         </is>
       </c>
       <c r="K166">
-        <v>83573.68</v>
+        <v>83793.01</v>
       </c>
       <c r="L166">
         <v>44242.49</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>AUT-20260603-165</t>
+          <t>BI-2206079</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 02/06/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10470,27 +10470,27 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Giulia Fiorini</t>
+          <t>Google Workspace_altus US</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G167">
-        <v>1850.0</v>
+        <v>234.66</v>
       </c>
       <c r="H167">
-        <v>0.0</v>
+        <v>25.14</v>
       </c>
       <c r="I167">
-        <v>1850.0</v>
+        <v>209.52</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -10498,19 +10498,24 @@
         </is>
       </c>
       <c r="K167">
-        <v>85423.68</v>
+        <v>83558.35</v>
       </c>
       <c r="L167">
         <v>44242.49</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>AUT-20260604-166</t>
+          <t>BI-104119</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 03/06/2026</t>
         </is>
       </c>
     </row>
@@ -10532,12 +10537,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Cobro anticipo 3/6 inscripcion Giulia Fiorini 2026</t>
+          <t>Cobro mensualidad junio Giulia Fiorini</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10546,13 +10551,13 @@
         </is>
       </c>
       <c r="G168">
-        <v>308.68</v>
+        <v>1850.0</v>
       </c>
       <c r="H168">
         <v>0.0</v>
       </c>
       <c r="I168">
-        <v>308.68</v>
+        <v>1850.0</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -10560,19 +10565,24 @@
         </is>
       </c>
       <c r="K168">
-        <v>85732.36</v>
+        <v>85408.35</v>
       </c>
       <c r="L168">
         <v>44242.49</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>AUT-20260604-167</t>
+          <t>BI-217487-A</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Parte de ACH Dilson Gerardo Fiori Q2,158.68</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10594,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10594,12 +10604,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Luís Felipe Guzmán</t>
+          <t>Cobro anticipo 3/6 inscripción Giulia Fiorini 2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -10608,13 +10618,13 @@
         </is>
       </c>
       <c r="G169">
-        <v>9300.0</v>
+        <v>308.68</v>
       </c>
       <c r="H169">
         <v>0.0</v>
       </c>
       <c r="I169">
-        <v>9300.0</v>
+        <v>308.68</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -10622,19 +10632,24 @@
         </is>
       </c>
       <c r="K169">
-        <v>95032.36</v>
+        <v>85717.03</v>
       </c>
       <c r="L169">
         <v>44242.49</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>AUT-20260605-168</t>
+          <t>BI-217487-B</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Parte de ACH Dilson Gerardo Fiori Q2,158.68</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10671,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Mateo Toribio</t>
+          <t>Cobro mensualidad junio Mateo Toribio</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10684,19 +10699,24 @@
         </is>
       </c>
       <c r="K170">
-        <v>104332.36</v>
+        <v>95017.03</v>
       </c>
       <c r="L170">
         <v>44242.49</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>AUT-20260605-169</t>
+          <t>BI-5111079</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/06/2026</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10728,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10718,7 +10738,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Rodrigo Gallinsa</t>
+          <t>Cobro mensualidad junio Luís Felipe Guzmán (Pamela Sosa)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10732,13 +10752,13 @@
         </is>
       </c>
       <c r="G171">
-        <v>6300.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H171">
         <v>0.0</v>
       </c>
       <c r="I171">
-        <v>6300.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -10746,19 +10766,24 @@
         </is>
       </c>
       <c r="K171">
-        <v>110632.36</v>
+        <v>104317.03</v>
       </c>
       <c r="L171">
         <v>44242.49</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>AUT-20260618-170</t>
+          <t>BI-5187709</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/06/2026</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10805,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Anticipo 3/6 inscripcion 2026 Rodrigo Gallinsa</t>
+          <t>Cobro mensualidad junio Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10794,13 +10819,13 @@
         </is>
       </c>
       <c r="G172">
-        <v>1287.5</v>
+        <v>6300.0</v>
       </c>
       <c r="H172">
         <v>0.0</v>
       </c>
       <c r="I172">
-        <v>1287.5</v>
+        <v>6300.0</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -10808,19 +10833,24 @@
         </is>
       </c>
       <c r="K172">
-        <v>111919.86</v>
+        <v>110617.03</v>
       </c>
       <c r="L172">
         <v>44242.49</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>AUT-20260618-171</t>
+          <t>BI-18142150</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 18/06/2026</t>
         </is>
       </c>
     </row>
@@ -10832,7 +10862,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10842,27 +10872,27 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Pago documentos mineduc Samuel Sosa</t>
+          <t>Anticipo 3/6 inscripción 2026 Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G173">
-        <v>250.0</v>
+        <v>1287.5</v>
       </c>
       <c r="H173">
-        <v>26.79</v>
+        <v>0.0</v>
       </c>
       <c r="I173">
-        <v>223.21</v>
+        <v>1287.5</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -10870,19 +10900,24 @@
         </is>
       </c>
       <c r="K173">
-        <v>111669.86</v>
+        <v>111904.53</v>
       </c>
       <c r="L173">
         <v>44242.49</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>AUT-20260625-172</t>
+          <t>BI-18177865</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 18/06/2026</t>
         </is>
       </c>
     </row>
@@ -10904,12 +10939,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Compra regalo maestras</t>
+          <t>Pago documentos MINEDUC abogado Samuel Sosa</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>5207 - Otros Gastos (No Deducibles)</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -10918,13 +10953,13 @@
         </is>
       </c>
       <c r="G174">
-        <v>895.0</v>
+        <v>250.0</v>
       </c>
       <c r="H174">
-        <v>0.0</v>
+        <v>26.79</v>
       </c>
       <c r="I174">
-        <v>895.0</v>
+        <v>223.21</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -10932,19 +10967,24 @@
         </is>
       </c>
       <c r="K174">
-        <v>110774.86</v>
+        <v>111654.53</v>
       </c>
       <c r="L174">
         <v>44242.49</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>AUT-20260625-173</t>
+          <t>BI-25243854</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 25/06/2026 (Nota: Se eliminó duplicado de Q895 Regalo Maestras que corresponde al 10/07/2026)</t>
         </is>
       </c>
     </row>
@@ -10966,7 +11006,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Pago Adri compras día del Padre</t>
+          <t>Pago compras actividad Día del Padre Altus (Adri)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10980,13 +11020,13 @@
         </is>
       </c>
       <c r="G175">
-        <v>3210.0</v>
+        <v>1210.0</v>
       </c>
       <c r="H175">
-        <v>343.93</v>
+        <v>129.64</v>
       </c>
       <c r="I175">
-        <v>2866.07</v>
+        <v>1080.36</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -10994,19 +11034,24 @@
         </is>
       </c>
       <c r="K175">
-        <v>107564.86</v>
+        <v>110444.53</v>
       </c>
       <c r="L175">
         <v>44242.49</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>AUT-20260626-174</t>
+          <t>BI-178967</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>03-Eventos/ Extras</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Separado según extracto BI 26/06/2026 (Docto 178967)</t>
         </is>
       </c>
     </row>
@@ -11028,12 +11073,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Pago mes de junio Lucía Montes</t>
+          <t>Pago Bono 14 AJ (Desde cuenta operativa)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5104 - Bono 14</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -11042,13 +11087,13 @@
         </is>
       </c>
       <c r="G176">
-        <v>8574.54</v>
+        <v>2000.0</v>
       </c>
       <c r="H176">
         <v>0.0</v>
       </c>
       <c r="I176">
-        <v>8574.54</v>
+        <v>2000.0</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -11056,19 +11101,24 @@
         </is>
       </c>
       <c r="K176">
-        <v>98990.32</v>
+        <v>108444.53</v>
       </c>
       <c r="L176">
         <v>44242.49</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>AUT-20260626-175</t>
+          <t>BI-200685</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Separado según extracto BI 26/06/2026 (Docto 200685: 5104 bono 14 AJ)</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11140,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Pago mes de junio Jessica Gudiel</t>
+          <t>Pago sueldo junio Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11104,13 +11154,13 @@
         </is>
       </c>
       <c r="G177">
-        <v>5862.19</v>
+        <v>4237.78</v>
       </c>
       <c r="H177">
         <v>0.0</v>
       </c>
       <c r="I177">
-        <v>5862.19</v>
+        <v>4237.78</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -11118,19 +11168,24 @@
         </is>
       </c>
       <c r="K177">
-        <v>93128.13</v>
+        <v>104206.75</v>
       </c>
       <c r="L177">
         <v>44242.49</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>AUT-20260626-176</t>
+          <t>BI-118012</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11207,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Pago mes de junio Geovanna Velázquez</t>
+          <t>Pago sueldo junio Melissa Peña</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11166,13 +11221,13 @@
         </is>
       </c>
       <c r="G178">
-        <v>4237.78</v>
+        <v>4234.78</v>
       </c>
       <c r="H178">
         <v>0.0</v>
       </c>
       <c r="I178">
-        <v>4237.78</v>
+        <v>4234.78</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -11180,19 +11235,24 @@
         </is>
       </c>
       <c r="K178">
-        <v>88890.35</v>
+        <v>99971.97</v>
       </c>
       <c r="L178">
         <v>44242.49</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>AUT-20260626-177</t>
+          <t>BI-138311</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11214,12 +11274,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Pago mes de junio Suly Sajbochol</t>
+          <t>Pago publicidad RRSS Raúl</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11228,13 +11288,13 @@
         </is>
       </c>
       <c r="G179">
-        <v>4234.78</v>
+        <v>500.0</v>
       </c>
       <c r="H179">
-        <v>0.0</v>
+        <v>53.57</v>
       </c>
       <c r="I179">
-        <v>4234.78</v>
+        <v>446.43</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -11242,19 +11302,24 @@
         </is>
       </c>
       <c r="K179">
-        <v>84655.57</v>
+        <v>99471.97</v>
       </c>
       <c r="L179">
         <v>44242.49</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>AUT-20260626-178</t>
+          <t>BI-138762</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11276,12 +11341,12 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Pago mes de junio Melissa Peña</t>
+          <t>Donación Fundación Waybi junio</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5208 - Donaciones</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -11290,13 +11355,13 @@
         </is>
       </c>
       <c r="G180">
-        <v>4234.78</v>
+        <v>1700.0</v>
       </c>
       <c r="H180">
-        <v>0.0</v>
+        <v>182.14</v>
       </c>
       <c r="I180">
-        <v>4234.78</v>
+        <v>1517.86</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -11304,19 +11369,24 @@
         </is>
       </c>
       <c r="K180">
-        <v>80420.79</v>
+        <v>97771.97</v>
       </c>
       <c r="L180">
         <v>44242.49</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>AUT-20260626-179</t>
+          <t>BI-151470</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11338,42 +11408,42 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Pago Bono 14  Lucía Montes</t>
+          <t>Pago sueldo junio Jessica Gudiel</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>5104 - Bono 14</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Pago Reserva Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G181">
-        <v>9000.0</v>
+        <v>5862.19</v>
       </c>
       <c r="H181">
         <v>0.0</v>
       </c>
       <c r="I181">
-        <v>9000.0</v>
+        <v>5862.19</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>BI-Ahorro</t>
+          <t>BI- Monetaria</t>
         </is>
       </c>
       <c r="K181">
-        <v>80420.79</v>
+        <v>91909.78</v>
       </c>
       <c r="L181">
-        <v>35242.49</v>
+        <v>44242.49</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>AUT-20260626-180</t>
+          <t>BI-176604</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -11383,7 +11453,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Pagado desde BI-Ahorro con fondos acumulados en reserva laboral (Decreto 42-92).</t>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11405,42 +11475,42 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Pago Bono 14 Jessica Gudiel</t>
+          <t>Pago sueldo junio Suly Sajbochol</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>5104 - Bono 14</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Pago Reserva Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G182">
-        <v>6000.0</v>
+        <v>4234.78</v>
       </c>
       <c r="H182">
         <v>0.0</v>
       </c>
       <c r="I182">
-        <v>6000.0</v>
+        <v>4234.78</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>BI-Ahorro</t>
+          <t>BI- Monetaria</t>
         </is>
       </c>
       <c r="K182">
-        <v>80420.79</v>
+        <v>87675.0</v>
       </c>
       <c r="L182">
-        <v>29242.49</v>
+        <v>44242.49</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>AUT-20260626-181</t>
+          <t>BI-202265</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -11450,7 +11520,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Pagado desde BI-Ahorro con fondos acumulados en reserva laboral (Decreto 42-92).</t>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11472,42 +11542,42 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Pago Bono 14 Geovanna Velázquez</t>
+          <t>Pago sueldo junio Lucía Montes</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>5104 - Bono 14</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Pago Reserva Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G183">
-        <v>4200.0</v>
+        <v>8574.54</v>
       </c>
       <c r="H183">
         <v>0.0</v>
       </c>
       <c r="I183">
-        <v>4200.0</v>
+        <v>8574.54</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>BI-Ahorro</t>
+          <t>BI- Monetaria</t>
         </is>
       </c>
       <c r="K183">
-        <v>80420.79</v>
+        <v>79100.46</v>
       </c>
       <c r="L183">
-        <v>25042.49</v>
+        <v>44242.49</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>AUT-20260626-182</t>
+          <t>BI-26153755</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -11517,7 +11587,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Pagado desde BI-Ahorro con fondos acumulados en reserva laboral (Decreto 42-92).</t>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11539,42 +11609,42 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Pago Bono 14 Suly Sajbochol</t>
+          <t>Pago celular ALTUS</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>5104 - Bono 14</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Pago Reserva Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G184">
-        <v>4200.0</v>
+        <v>285.0</v>
       </c>
       <c r="H184">
-        <v>0.0</v>
+        <v>30.54</v>
       </c>
       <c r="I184">
-        <v>4200.0</v>
+        <v>254.46</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>BI-Ahorro</t>
+          <t>BI- Monetaria</t>
         </is>
       </c>
       <c r="K184">
-        <v>80420.79</v>
+        <v>78815.46</v>
       </c>
       <c r="L184">
-        <v>20842.49</v>
+        <v>44242.49</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>AUT-20260626-183</t>
+          <t>BI-26160770</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -11584,7 +11654,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>Pagado desde BI-Ahorro con fondos acumulados en reserva laboral (Decreto 42-92).</t>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11606,42 +11676,42 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Pago Bono 14  Melissa Peña</t>
+          <t>Provisiones laborales (Traslado a BI-Ahorro)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>5104 - Bono 14</t>
+          <t>2102 - Provisiones Laborales</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Pago Reserva Ahorro</t>
+          <t>Traspaso Ahorro</t>
         </is>
       </c>
       <c r="G185">
-        <v>4200.0</v>
+        <v>11552.0</v>
       </c>
       <c r="H185">
         <v>0.0</v>
       </c>
       <c r="I185">
-        <v>4200.0</v>
+        <v>11552.0</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>BI-Ahorro</t>
+          <t>BI- Monetaria</t>
         </is>
       </c>
       <c r="K185">
-        <v>80420.79</v>
+        <v>67263.46</v>
       </c>
       <c r="L185">
-        <v>16642.49</v>
+        <v>55794.49</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>AUT-20260626-184</t>
+          <t>BI-26177492</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -11651,7 +11721,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Pagado desde BI-Ahorro con fondos acumulados en reserva laboral (Decreto 42-92).</t>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11673,12 +11743,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Donación Fundación Waybi</t>
+          <t>Pago Nauta Estudio Redes Sociales junio</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>5208 - Donaciones</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11687,13 +11757,13 @@
         </is>
       </c>
       <c r="G186">
-        <v>1700.0</v>
+        <v>2650.0</v>
       </c>
       <c r="H186">
-        <v>182.14</v>
+        <v>283.93</v>
       </c>
       <c r="I186">
-        <v>1517.86</v>
+        <v>2366.07</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -11701,19 +11771,24 @@
         </is>
       </c>
       <c r="K186">
-        <v>78720.79</v>
+        <v>64613.46</v>
       </c>
       <c r="L186">
-        <v>16642.49</v>
+        <v>55794.49</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>AUT-20260626-185</t>
+          <t>BI-26215848</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11735,47 +11810,52 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Pago publicidad rrss Raúl</t>
+          <t>Pago Bono 14 Lucía Montes</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>5104 - Bono 14</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pago Reserva Ahorro</t>
         </is>
       </c>
       <c r="G187">
-        <v>500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="H187">
-        <v>53.57</v>
+        <v>0.0</v>
       </c>
       <c r="I187">
-        <v>446.43</v>
+        <v>9000.0</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>BI- Monetaria</t>
+          <t>BI-Ahorro</t>
         </is>
       </c>
       <c r="K187">
-        <v>78220.79</v>
+        <v>64613.46</v>
       </c>
       <c r="L187">
-        <v>16642.49</v>
+        <v>46794.49</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>AUT-20260626-186</t>
+          <t>AHO-B14-LM</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Pagado desde BI-Ahorro (Reserva Laboral)</t>
         </is>
       </c>
     </row>
@@ -11797,47 +11877,52 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Pago Nauta Estudio Redes sociales</t>
+          <t>Pago Bono 14 Jessica Gudiel</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>5104 - Bono 14</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pago Reserva Ahorro</t>
         </is>
       </c>
       <c r="G188">
-        <v>2650.0</v>
+        <v>6000.0</v>
       </c>
       <c r="H188">
-        <v>283.93</v>
+        <v>0.0</v>
       </c>
       <c r="I188">
-        <v>2366.07</v>
+        <v>6000.0</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>BI- Monetaria</t>
+          <t>BI-Ahorro</t>
         </is>
       </c>
       <c r="K188">
-        <v>75570.79</v>
+        <v>64613.46</v>
       </c>
       <c r="L188">
-        <v>16642.49</v>
+        <v>40794.49</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>AUT-20260626-187</t>
+          <t>AHO-B14-JG</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Pagado desde BI-Ahorro (Reserva Laboral)</t>
         </is>
       </c>
     </row>
@@ -11859,42 +11944,42 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Provisiones laborales</t>
+          <t>Pago Bono 14 Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2102 - Provisiones Laborales</t>
+          <t>5104 - Bono 14</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Traspaso Ahorro</t>
+          <t>Pago Reserva Ahorro</t>
         </is>
       </c>
       <c r="G189">
-        <v>11552.0</v>
+        <v>4200.0</v>
       </c>
       <c r="H189">
         <v>0.0</v>
       </c>
       <c r="I189">
-        <v>11552.0</v>
+        <v>4200.0</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>BI- Monetaria</t>
+          <t>BI-Ahorro</t>
         </is>
       </c>
       <c r="K189">
-        <v>64018.79</v>
+        <v>64613.46</v>
       </c>
       <c r="L189">
-        <v>28194.49</v>
+        <v>36594.49</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>AUT-20260626-188</t>
+          <t>AHO-B14-GV</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -11904,7 +11989,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
+          <t>Pagado desde BI-Ahorro (Reserva Laboral)</t>
         </is>
       </c>
     </row>
@@ -11926,47 +12011,52 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Pago celular ALTUS</t>
+          <t>Pago Bono 14 Suly Sajbochol</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>5104 - Bono 14</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pago Reserva Ahorro</t>
         </is>
       </c>
       <c r="G190">
-        <v>285.0</v>
+        <v>4200.0</v>
       </c>
       <c r="H190">
-        <v>30.54</v>
+        <v>0.0</v>
       </c>
       <c r="I190">
-        <v>254.46</v>
+        <v>4200.0</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>BI- Monetaria</t>
+          <t>BI-Ahorro</t>
         </is>
       </c>
       <c r="K190">
-        <v>63733.79</v>
+        <v>64613.46</v>
       </c>
       <c r="L190">
-        <v>28194.49</v>
+        <v>32394.49</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>AUT-20260626-189</t>
+          <t>AHO-B14-SJ</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Pagado desde BI-Ahorro (Reserva Laboral)</t>
         </is>
       </c>
     </row>
@@ -11978,7 +12068,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11988,47 +12078,52 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Pago reparacion de baño Luisa Estrada</t>
+          <t>Pago Bono 14 Melissa Peña</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5104 - Bono 14</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pago Reserva Ahorro</t>
         </is>
       </c>
       <c r="G191">
-        <v>1053.48</v>
+        <v>4200.0</v>
       </c>
       <c r="H191">
-        <v>112.87</v>
+        <v>0.0</v>
       </c>
       <c r="I191">
-        <v>940.61</v>
+        <v>4200.0</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>BI- Monetaria</t>
+          <t>BI-Ahorro</t>
         </is>
       </c>
       <c r="K191">
-        <v>62680.31</v>
+        <v>64613.46</v>
       </c>
       <c r="L191">
         <v>28194.49</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>AUT-20260627-190</t>
+          <t>AHO-B14-MP</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Pagado desde BI-Ahorro (Reserva Laboral)</t>
         </is>
       </c>
     </row>
@@ -12040,17 +12135,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Pago Lourdes Escribá</t>
+          <t>Honorarios arquitecta insumos reparación baño Luisa Estrada</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12064,13 +12159,13 @@
         </is>
       </c>
       <c r="G192">
-        <v>1454.0</v>
+        <v>1053.48</v>
       </c>
       <c r="H192">
-        <v>155.79</v>
+        <v>112.87</v>
       </c>
       <c r="I192">
-        <v>1298.21</v>
+        <v>940.61</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -12078,19 +12173,24 @@
         </is>
       </c>
       <c r="K192">
-        <v>61226.31</v>
+        <v>63559.98</v>
       </c>
       <c r="L192">
         <v>28194.49</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>AUT-20260701-191</t>
+          <t>BI-27172293</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/06/2026</t>
         </is>
       </c>
     </row>
@@ -12112,27 +12212,27 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Pago Sergio contador</t>
+          <t>Cobro mensualidad julio Andrei González</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G193">
-        <v>350.0</v>
+        <v>3800.0</v>
       </c>
       <c r="H193">
-        <v>37.5</v>
+        <v>0.0</v>
       </c>
       <c r="I193">
-        <v>312.5</v>
+        <v>3800.0</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -12140,19 +12240,24 @@
         </is>
       </c>
       <c r="K193">
-        <v>60876.31</v>
+        <v>67359.98</v>
       </c>
       <c r="L193">
         <v>28194.49</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>AUT-20260701-192</t>
+          <t>BI-1241287</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 01/07/2026</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12269,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12174,27 +12279,27 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Pago ISR Empleados</t>
+          <t>Cobro mensualidad julio Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2105 - ISR Retenciones por Pagar</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G194">
-        <v>375.88</v>
+        <v>9300.0</v>
       </c>
       <c r="H194">
         <v>0.0</v>
       </c>
       <c r="I194">
-        <v>375.88</v>
+        <v>9300.0</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -12202,24 +12307,24 @@
         </is>
       </c>
       <c r="K194">
-        <v>60500.43</v>
+        <v>76659.98</v>
       </c>
       <c r="L194">
         <v>28194.49</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>AUT-20260702-193</t>
+          <t>BI-1263713</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>Reclasificado de 5210 a 2105: Entero a SAT de ISR retenido a empleadas.</t>
+          <t>Conciliado con extracto BI 01/07/2026</t>
         </is>
       </c>
     </row>
@@ -12241,27 +12346,27 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Andrei González</t>
+          <t>Débito BiCheque comisión manejo de cuenta julio</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G195">
-        <v>3800.0</v>
+        <v>15.0</v>
       </c>
       <c r="H195">
         <v>0.0</v>
       </c>
       <c r="I195">
-        <v>3800.0</v>
+        <v>15.0</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -12269,19 +12374,24 @@
         </is>
       </c>
       <c r="K195">
-        <v>64300.43</v>
+        <v>76644.98</v>
       </c>
       <c r="L195">
         <v>28194.49</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>AUT-20260701-194</t>
+          <t>BI-310320</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Agregado según extracto BI 01/07/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -12303,27 +12413,27 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Gabriel Ruíz</t>
+          <t>Pago servicios Lourdes Escribá junio</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G196">
-        <v>9300.0</v>
+        <v>1454.0</v>
       </c>
       <c r="H196">
-        <v>0.0</v>
+        <v>155.79</v>
       </c>
       <c r="I196">
-        <v>9300.0</v>
+        <v>1298.21</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -12331,19 +12441,24 @@
         </is>
       </c>
       <c r="K196">
-        <v>73600.43</v>
+        <v>75190.98</v>
       </c>
       <c r="L196">
         <v>28194.49</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>AUT-20260701-195</t>
+          <t>BI-1113817</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 01/07/2026</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12470,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12365,12 +12480,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Google Workspace_altus</t>
+          <t>Pago honorarios contabilidad Sergio contador</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12379,13 +12494,13 @@
         </is>
       </c>
       <c r="G197">
-        <v>234.96</v>
+        <v>350.0</v>
       </c>
       <c r="H197">
-        <v>25.17</v>
+        <v>37.5</v>
       </c>
       <c r="I197">
-        <v>209.79</v>
+        <v>312.5</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -12393,19 +12508,24 @@
         </is>
       </c>
       <c r="K197">
-        <v>73365.47</v>
+        <v>74840.98</v>
       </c>
       <c r="L197">
         <v>28194.49</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>AUT-20260702-196</t>
+          <t>BI-1136800</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 01/07/2026</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12547,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Pago celular ALTUS</t>
+          <t>Google Workspace_altus US</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12441,13 +12561,13 @@
         </is>
       </c>
       <c r="G198">
-        <v>285.0</v>
+        <v>234.96</v>
       </c>
       <c r="H198">
-        <v>30.54</v>
+        <v>25.17</v>
       </c>
       <c r="I198">
-        <v>254.46</v>
+        <v>209.79</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -12455,19 +12575,24 @@
         </is>
       </c>
       <c r="K198">
-        <v>73080.47</v>
+        <v>74606.02</v>
       </c>
       <c r="L198">
         <v>28194.49</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>AUT-20260702-197</t>
+          <t>BI-99468</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 02/07/2026</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12604,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12489,27 +12614,27 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Adriana García</t>
+          <t>Pago ISR Empleados SAT</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>2105 - ISR Retenciones por Pagar</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G199">
-        <v>9300.0</v>
+        <v>375.88</v>
       </c>
       <c r="H199">
         <v>0.0</v>
       </c>
       <c r="I199">
-        <v>9300.0</v>
+        <v>375.88</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -12517,19 +12642,24 @@
         </is>
       </c>
       <c r="K199">
-        <v>82380.47</v>
+        <v>74230.14</v>
       </c>
       <c r="L199">
         <v>28194.49</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>AUT-20260703-198</t>
+          <t>BI-2175006</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 02/07/2026</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12671,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12551,27 +12681,27 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Luís Felipe Guzmán</t>
+          <t>Pago teléfono / celular ALTUS</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G200">
-        <v>9300.0</v>
+        <v>285.0</v>
       </c>
       <c r="H200">
-        <v>0.0</v>
+        <v>30.54</v>
       </c>
       <c r="I200">
-        <v>9300.0</v>
+        <v>254.46</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -12579,19 +12709,24 @@
         </is>
       </c>
       <c r="K200">
-        <v>91680.47</v>
+        <v>73945.14</v>
       </c>
       <c r="L200">
         <v>28194.49</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>AUT-20260703-199</t>
+          <t>BI-2261205</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 02/07/2026</t>
         </is>
       </c>
     </row>
@@ -12613,7 +12748,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Giulia Fiorini</t>
+          <t>Cobro mensualidad julio Adriana García</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12627,13 +12762,13 @@
         </is>
       </c>
       <c r="G201">
-        <v>1850.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H201">
         <v>0.0</v>
       </c>
       <c r="I201">
-        <v>1850.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -12641,19 +12776,24 @@
         </is>
       </c>
       <c r="K201">
-        <v>93530.47</v>
+        <v>83245.14</v>
       </c>
       <c r="L201">
         <v>28194.49</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>AUT-20260703-200</t>
+          <t>BI-3126065</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 03/07/2026</t>
         </is>
       </c>
     </row>
@@ -12665,7 +12805,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12675,12 +12815,12 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Cobro anticipo 4/6 inscripcion Giulia Fiorini</t>
+          <t>Cobro mensualidad julio Luís Felipe Guzmán (Pamela Sosa)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -12689,13 +12829,13 @@
         </is>
       </c>
       <c r="G202">
-        <v>308.34</v>
+        <v>9300.0</v>
       </c>
       <c r="H202">
         <v>0.0</v>
       </c>
       <c r="I202">
-        <v>308.34</v>
+        <v>9300.0</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -12703,19 +12843,24 @@
         </is>
       </c>
       <c r="K202">
-        <v>93838.81</v>
+        <v>92545.14</v>
       </c>
       <c r="L202">
         <v>28194.49</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>AUT-20260706-201</t>
+          <t>BI-5194232</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/07/2026</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12872,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12737,7 +12882,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Cobro anticipo 1/2 mensualidad junio Günther Márquez</t>
+          <t>Cobro mensualidad julio Giulia Fiorini</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12751,13 +12896,13 @@
         </is>
       </c>
       <c r="G203">
-        <v>2758.33</v>
+        <v>1850.0</v>
       </c>
       <c r="H203">
         <v>0.0</v>
       </c>
       <c r="I203">
-        <v>2758.33</v>
+        <v>1850.0</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -12765,19 +12910,24 @@
         </is>
       </c>
       <c r="K203">
-        <v>96597.14</v>
+        <v>94395.14</v>
       </c>
       <c r="L203">
         <v>28194.49</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>AUT-20260707-202</t>
+          <t>BI-145540-A</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Parte de ACH Dilson Gerardo Fiori Q2,158.34</t>
         </is>
       </c>
     </row>
@@ -12789,7 +12939,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12799,12 +12949,12 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Mateo Toribio</t>
+          <t>Cobro anticipo 4/6 inscripción Giulia Fiorini</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -12813,13 +12963,13 @@
         </is>
       </c>
       <c r="G204">
-        <v>9300.0</v>
+        <v>308.34</v>
       </c>
       <c r="H204">
         <v>0.0</v>
       </c>
       <c r="I204">
-        <v>9300.0</v>
+        <v>308.34</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -12827,19 +12977,24 @@
         </is>
       </c>
       <c r="K204">
-        <v>105897.14</v>
+        <v>94703.48</v>
       </c>
       <c r="L204">
         <v>28194.49</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>AUT-20260709-203</t>
+          <t>BI-145540-B</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Parte de ACH Dilson Gerardo Fiori Q2,158.34</t>
         </is>
       </c>
     </row>
@@ -12851,7 +13006,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12861,27 +13016,27 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Regalo día del maestro</t>
+          <t>Cobro anticipo 1/2 mensualidad junio Günther Márquez</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>5205 - Actividades y excursiones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G205">
-        <v>895.0</v>
+        <v>2758.33</v>
       </c>
       <c r="H205">
-        <v>95.89</v>
+        <v>0.0</v>
       </c>
       <c r="I205">
-        <v>799.11</v>
+        <v>2758.33</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -12889,19 +13044,24 @@
         </is>
       </c>
       <c r="K205">
-        <v>105002.14</v>
+        <v>97461.81</v>
       </c>
       <c r="L205">
         <v>28194.49</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>AUT-20260710-204</t>
+          <t>BI-176264</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>03-Eventos/ Extras</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 07/07/2026</t>
         </is>
       </c>
     </row>
@@ -12913,7 +13073,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12923,27 +13083,27 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Cobro anticipo 1/2 inscripción 2027 Gabriel Ruíz</t>
+          <t>Cobro mensualidad julio Mateo Toribio</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2107 - Anticipo de inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Pasivo</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G206">
-        <v>5150.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H206">
         <v>0.0</v>
       </c>
       <c r="I206">
-        <v>5150.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -12951,19 +13111,24 @@
         </is>
       </c>
       <c r="K206">
-        <v>110152.14</v>
+        <v>106761.81</v>
       </c>
       <c r="L206">
         <v>28194.49</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>AUT-20260714-205</t>
+          <t>BI-9185796</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 09/07/2026</t>
         </is>
       </c>
     </row>
@@ -12975,7 +13140,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12985,27 +13150,27 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Anticipo 4/6 inscripcion 2026 Rodrigo Gallinsa</t>
+          <t>Regalo Día del Maestro</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>5205 - Actividades y excursiones</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G207">
-        <v>1287.5</v>
+        <v>895.0</v>
       </c>
       <c r="H207">
-        <v>0.0</v>
+        <v>95.89</v>
       </c>
       <c r="I207">
-        <v>1287.5</v>
+        <v>799.11</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -13013,19 +13178,24 @@
         </is>
       </c>
       <c r="K207">
-        <v>111439.64</v>
+        <v>105866.81</v>
       </c>
       <c r="L207">
         <v>28194.49</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>AUT-20260714-206</t>
+          <t>BI-10216419</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 10/07/2026</t>
         </is>
       </c>
     </row>
@@ -13037,7 +13207,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13047,27 +13217,27 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Pago papelería Regina MINEDUC</t>
+          <t>Anticipo 4/6 inscripción 2026 Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G208">
-        <v>1000.0</v>
+        <v>1287.5</v>
       </c>
       <c r="H208">
-        <v>107.14</v>
+        <v>0.0</v>
       </c>
       <c r="I208">
-        <v>892.86</v>
+        <v>1287.5</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -13075,19 +13245,24 @@
         </is>
       </c>
       <c r="K208">
-        <v>110439.64</v>
+        <v>107154.31</v>
       </c>
       <c r="L208">
         <v>28194.49</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>AUT-20260720-207</t>
+          <t>BI-14170107</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 14/07/2026</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13274,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13109,27 +13284,27 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Pago mes de julio Lucía Montes</t>
+          <t>Cobro anticipo 1/2 inscripción 2027 Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>2107 - Anticipo de inscripciones</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pasivo</t>
         </is>
       </c>
       <c r="G209">
-        <v>8574.54</v>
+        <v>5150.0</v>
       </c>
       <c r="H209">
         <v>0.0</v>
       </c>
       <c r="I209">
-        <v>8574.54</v>
+        <v>5150.0</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -13137,19 +13312,24 @@
         </is>
       </c>
       <c r="K209">
-        <v>101865.1</v>
+        <v>112304.31</v>
       </c>
       <c r="L209">
         <v>28194.49</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>AUT-20260727-208</t>
+          <t>BI-14201939</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 14/07/2026</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13341,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13171,12 +13351,12 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Pago mes de julio  Jessica Gudiel</t>
+          <t>Pago papelería MINEDUC Ma. Regina</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -13185,13 +13365,13 @@
         </is>
       </c>
       <c r="G210">
-        <v>5862.19</v>
+        <v>1000.0</v>
       </c>
       <c r="H210">
-        <v>0.0</v>
+        <v>107.14</v>
       </c>
       <c r="I210">
-        <v>5862.19</v>
+        <v>892.86</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -13199,19 +13379,24 @@
         </is>
       </c>
       <c r="K210">
-        <v>96002.91</v>
+        <v>111304.31</v>
       </c>
       <c r="L210">
         <v>28194.49</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>AUT-20260727-209</t>
+          <t>BI-149015</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 20/07/2026</t>
         </is>
       </c>
     </row>
@@ -13233,7 +13418,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Pago de compras a Jessi</t>
+          <t>Pago suministros (compras Jessi)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13261,19 +13446,24 @@
         </is>
       </c>
       <c r="K211">
-        <v>95547.01</v>
+        <v>110848.41</v>
       </c>
       <c r="L211">
         <v>28194.49</v>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>AUT-20260727-210</t>
+          <t>BI-153363</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13295,12 +13485,12 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Pago de compras a Adri</t>
+          <t>Donación Fundación Waybi julio</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>5203 - Papelería, útiles y suministros</t>
+          <t>5208 - Donaciones</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -13309,13 +13499,13 @@
         </is>
       </c>
       <c r="G212">
-        <v>745.9</v>
+        <v>1700.0</v>
       </c>
       <c r="H212">
-        <v>79.92</v>
+        <v>182.14</v>
       </c>
       <c r="I212">
-        <v>665.98</v>
+        <v>1517.86</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -13323,19 +13513,24 @@
         </is>
       </c>
       <c r="K212">
-        <v>94801.11</v>
+        <v>109148.41</v>
       </c>
       <c r="L212">
         <v>28194.49</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>AUT-20260727-211</t>
+          <t>BI-171670</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13357,12 +13552,12 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Pago mes de julio Geovanna Velázquez</t>
+          <t>Compras actividad Día de la Familia (Adri)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5205 - Actividades y excursiones</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -13371,13 +13566,13 @@
         </is>
       </c>
       <c r="G213">
-        <v>4234.78</v>
+        <v>745.9</v>
       </c>
       <c r="H213">
-        <v>0.0</v>
+        <v>79.92</v>
       </c>
       <c r="I213">
-        <v>4234.78</v>
+        <v>665.98</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -13385,19 +13580,24 @@
         </is>
       </c>
       <c r="K213">
-        <v>90566.33</v>
+        <v>108402.51</v>
       </c>
       <c r="L213">
         <v>28194.49</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>AUT-20260727-212</t>
+          <t>BI-187199</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13419,7 +13619,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Pago mes de julio Suly Sajbochol</t>
+          <t>Pago sueldo julio Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13447,19 +13647,24 @@
         </is>
       </c>
       <c r="K214">
-        <v>86331.55</v>
+        <v>104167.73</v>
       </c>
       <c r="L214">
         <v>28194.49</v>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>AUT-20260727-213</t>
+          <t>BI-208857</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13481,7 +13686,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Pago mes de julio Melissa Peña</t>
+          <t>Pago sueldo julio Jessica Gudiel</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13495,13 +13700,13 @@
         </is>
       </c>
       <c r="G215">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="H215">
         <v>0.0</v>
       </c>
       <c r="I215">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -13509,19 +13714,24 @@
         </is>
       </c>
       <c r="K215">
-        <v>82096.77</v>
+        <v>98305.54</v>
       </c>
       <c r="L215">
         <v>28194.49</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>AUT-20260727-214</t>
+          <t>BI-218374</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13543,12 +13753,12 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Donación a Fundación Waybi</t>
+          <t>Pago sueldo julio Suly Sajbochol</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>5208 - Donaciones</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -13557,13 +13767,13 @@
         </is>
       </c>
       <c r="G216">
-        <v>1700.0</v>
+        <v>4234.78</v>
       </c>
       <c r="H216">
-        <v>182.14</v>
+        <v>0.0</v>
       </c>
       <c r="I216">
-        <v>1517.86</v>
+        <v>4234.78</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -13571,19 +13781,24 @@
         </is>
       </c>
       <c r="K216">
-        <v>80396.77</v>
+        <v>94070.76</v>
       </c>
       <c r="L216">
         <v>28194.49</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>AUT-20260727-215</t>
+          <t>BI-224767</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13605,12 +13820,12 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Pago ISR</t>
+          <t>Pago sueldo julio Melissa Peña</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2105 - ISR Retenciones por Pagar</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -13619,13 +13834,13 @@
         </is>
       </c>
       <c r="G217">
-        <v>375.85</v>
+        <v>4234.78</v>
       </c>
       <c r="H217">
         <v>0.0</v>
       </c>
       <c r="I217">
-        <v>375.85</v>
+        <v>4234.78</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -13633,14 +13848,14 @@
         </is>
       </c>
       <c r="K217">
-        <v>80020.92</v>
+        <v>89835.98</v>
       </c>
       <c r="L217">
         <v>28194.49</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>AUT-20260727-216</t>
+          <t>BI-238411</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -13650,7 +13865,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Reclasificado de 5210 a 2105: Entero a SAT de ISR retenido a empleadas.</t>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13672,27 +13887,27 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Provisiones laborales</t>
+          <t>Pago marketing y publicidad julio (Raúl)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2102 - Provisiones Laborales</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Traspaso Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G218">
-        <v>11551.09</v>
+        <v>500.0</v>
       </c>
       <c r="H218">
-        <v>0.0</v>
+        <v>53.57</v>
       </c>
       <c r="I218">
-        <v>11551.09</v>
+        <v>446.43</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -13700,14 +13915,14 @@
         </is>
       </c>
       <c r="K218">
-        <v>68469.83</v>
+        <v>89335.98</v>
       </c>
       <c r="L218">
-        <v>39745.58</v>
+        <v>28194.49</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>AUT-20260727-217</t>
+          <t>BI-248172</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -13717,7 +13932,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
+          <t>Conciliado con extracto BI 27/07/2026 (Reclasificado a 5204)</t>
         </is>
       </c>
     </row>
@@ -13739,12 +13954,12 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Pago rrss Raúl Maroto</t>
+          <t>Pago sueldo julio Lucía Montes</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -13753,13 +13968,13 @@
         </is>
       </c>
       <c r="G219">
-        <v>500.0</v>
+        <v>8574.54</v>
       </c>
       <c r="H219">
-        <v>53.57</v>
+        <v>0.0</v>
       </c>
       <c r="I219">
-        <v>446.43</v>
+        <v>8574.54</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -13767,19 +13982,24 @@
         </is>
       </c>
       <c r="K219">
-        <v>67969.83</v>
+        <v>80761.44</v>
       </c>
       <c r="L219">
-        <v>39745.58</v>
+        <v>28194.49</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>AUT-20260727-218</t>
+          <t>BI-27147142</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13801,27 +14021,27 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Pago Nauta Estudio Redes sociales</t>
+          <t>Provisiones laborales julio (Traslado a BI-Ahorro)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>2102 - Provisiones Laborales</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Traspaso Ahorro</t>
         </is>
       </c>
       <c r="G220">
-        <v>2050.0</v>
+        <v>11551.09</v>
       </c>
       <c r="H220">
-        <v>219.64</v>
+        <v>0.0</v>
       </c>
       <c r="I220">
-        <v>1830.36</v>
+        <v>11551.09</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -13829,19 +14049,24 @@
         </is>
       </c>
       <c r="K220">
-        <v>65919.83</v>
+        <v>69210.35</v>
       </c>
       <c r="L220">
         <v>39745.58</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>AUT-20260727-219</t>
+          <t>BI-27154154</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13863,12 +14088,12 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Pago celular ALTUS</t>
+          <t>Pago contabilidad julio Sergio contador</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -13877,13 +14102,13 @@
         </is>
       </c>
       <c r="G221">
-        <v>285.0</v>
+        <v>350.0</v>
       </c>
       <c r="H221">
-        <v>30.54</v>
+        <v>37.5</v>
       </c>
       <c r="I221">
-        <v>254.46</v>
+        <v>312.5</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -13891,19 +14116,24 @@
         </is>
       </c>
       <c r="K221">
-        <v>65634.83</v>
+        <v>68860.35</v>
       </c>
       <c r="L221">
         <v>39745.58</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>AUT-20260727-220</t>
+          <t>BI-27171362</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13925,12 +14155,12 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Pago Sergio contador</t>
+          <t>Pago servicios agencia publicidad Nauta Estudio</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -13939,13 +14169,13 @@
         </is>
       </c>
       <c r="G222">
-        <v>350.0</v>
+        <v>2050.0</v>
       </c>
       <c r="H222">
-        <v>37.5</v>
+        <v>219.64</v>
       </c>
       <c r="I222">
-        <v>312.5</v>
+        <v>1830.36</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -13953,19 +14183,24 @@
         </is>
       </c>
       <c r="K222">
-        <v>65284.83</v>
+        <v>66810.35</v>
       </c>
       <c r="L222">
         <v>39745.58</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>AUT-20260727-221</t>
+          <t>BI-27216715</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026 (Reclasificado a 5204)</t>
         </is>
       </c>
     </row>
@@ -13977,7 +14212,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13987,27 +14222,27 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Donación Sarah Farr</t>
+          <t>Pago celular ALTUS julio</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>4203 - Donaciones recibidas</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G223">
-        <v>12500.0</v>
+        <v>285.0</v>
       </c>
       <c r="H223">
-        <v>0.0</v>
+        <v>30.54</v>
       </c>
       <c r="I223">
-        <v>12500.0</v>
+        <v>254.46</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -14015,19 +14250,24 @@
         </is>
       </c>
       <c r="K223">
-        <v>77784.83</v>
+        <v>66525.35</v>
       </c>
       <c r="L223">
         <v>39745.58</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>AUT-20260728-222</t>
+          <t>BI-27244399</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -14039,7 +14279,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14049,27 +14289,27 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Cobro anticipo 6/6 inscripcion Günther Márquez</t>
+          <t>Pago ISR Retenciones julio</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>2105 - ISR Retenciones por Pagar</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G224">
-        <v>1716.7</v>
+        <v>375.85</v>
       </c>
       <c r="H224">
         <v>0.0</v>
       </c>
       <c r="I224">
-        <v>1716.7</v>
+        <v>375.85</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -14077,19 +14317,24 @@
         </is>
       </c>
       <c r="K224">
-        <v>79501.53</v>
+        <v>66149.5</v>
       </c>
       <c r="L224">
         <v>39745.58</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>AUT-20260729-223</t>
+          <t>BI-27249346</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -14101,7 +14346,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14111,12 +14356,12 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Cobro mensualidad 2/2 junio Günter Márquez</t>
+          <t>Donación recibida (ACH Fredy Roberto Bolaños / Sarah Farr)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4203 - Donaciones recibidas</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -14125,13 +14370,13 @@
         </is>
       </c>
       <c r="G225">
-        <v>1585.02</v>
+        <v>12500.0</v>
       </c>
       <c r="H225">
         <v>0.0</v>
       </c>
       <c r="I225">
-        <v>1585.02</v>
+        <v>12500.0</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -14139,19 +14384,24 @@
         </is>
       </c>
       <c r="K225">
-        <v>81086.55</v>
+        <v>78649.5</v>
       </c>
       <c r="L225">
         <v>39745.58</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>AUT-20260729-224</t>
+          <t>BI-221740</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 28/07/2026</t>
         </is>
       </c>
     </row>
@@ -14173,12 +14423,12 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Cobro mensualidad 2/2 junio Günter Márquez</t>
+          <t>Cobro anticipo 6/6 inscripción Günther Márquez</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -14187,13 +14437,13 @@
         </is>
       </c>
       <c r="G226">
-        <v>3301.69</v>
+        <v>1716.7</v>
       </c>
       <c r="H226">
         <v>0.0</v>
       </c>
       <c r="I226">
-        <v>3301.69</v>
+        <v>1716.7</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -14201,19 +14451,24 @@
         </is>
       </c>
       <c r="K226">
-        <v>84388.24</v>
+        <v>80366.2</v>
       </c>
       <c r="L226">
         <v>39745.58</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>AUT-20260729-225</t>
+          <t>BI-179331-A</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Parte de ACH Valeria Márquez Q3,301.68</t>
         </is>
       </c>
     </row>
@@ -14225,7 +14480,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14235,27 +14490,27 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Anticipo 1/3 instalación de cámaras</t>
+          <t>Cobro mensualidad 2/2 junio Günther Márquez</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G227">
-        <v>7680.0</v>
+        <v>1584.98</v>
       </c>
       <c r="H227">
-        <v>822.86</v>
+        <v>0.0</v>
       </c>
       <c r="I227">
-        <v>6857.14</v>
+        <v>1584.98</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -14263,19 +14518,24 @@
         </is>
       </c>
       <c r="K227">
-        <v>76708.24</v>
+        <v>81951.18</v>
       </c>
       <c r="L227">
         <v>39745.58</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>AUT-20260730-226</t>
+          <t>BI-179331-B</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Ajustado a Q1,584.98 (1716.70 + 1584.98 = Q3,301.68 exactos según Docto 179331; se eliminó fila duplicada 226 de Q3,301.69)</t>
         </is>
       </c>
     </row>
@@ -14287,37 +14547,37 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Cobro mensualidad julio Rodrigo Gallinsa</t>
+          <t>Anticipo 1/3 instalación de cámaras</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>1501 - Mobiliario y Equipo</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G228">
-        <v>6300.0</v>
+        <v>7680.0</v>
       </c>
       <c r="H228">
-        <v>0.0</v>
+        <v>822.86</v>
       </c>
       <c r="I228">
-        <v>6300.0</v>
+        <v>6857.14</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -14325,19 +14585,24 @@
         </is>
       </c>
       <c r="K228">
-        <v>83008.24</v>
+        <v>74271.18</v>
       </c>
       <c r="L228">
         <v>39745.58</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>AUT-20260803-227</t>
+          <t>BI-30187818</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 30/07/2026</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14614,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14359,27 +14624,27 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Rodrigo Gallinsa</t>
+          <t>Débito BiCheque comisión manejo de cuenta agosto</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G229">
-        <v>6300.0</v>
+        <v>15.0</v>
       </c>
       <c r="H229">
         <v>0.0</v>
       </c>
       <c r="I229">
-        <v>6300.0</v>
+        <v>15.0</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -14387,19 +14652,24 @@
         </is>
       </c>
       <c r="K229">
-        <v>89308.24</v>
+        <v>74256.18</v>
       </c>
       <c r="L229">
         <v>39745.58</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>AUT-20260803-228</t>
+          <t>BI-310867</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Agregado según extracto BI 01/08/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14691,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Gabriel Ruíz</t>
+          <t>Cobro mensualidad julio Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -14435,13 +14705,13 @@
         </is>
       </c>
       <c r="G230">
-        <v>9300.0</v>
+        <v>6300.0</v>
       </c>
       <c r="H230">
         <v>0.0</v>
       </c>
       <c r="I230">
-        <v>9300.0</v>
+        <v>6300.0</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -14449,19 +14719,24 @@
         </is>
       </c>
       <c r="K230">
-        <v>98608.24</v>
+        <v>80556.18</v>
       </c>
       <c r="L230">
         <v>39745.58</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>AUT-20260803-229</t>
+          <t>BI-3100903</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 03/08/2026</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14758,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Andrei González</t>
+          <t>Cobro mensualidad agosto Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -14497,13 +14772,13 @@
         </is>
       </c>
       <c r="G231">
-        <v>3800.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H231">
         <v>0.0</v>
       </c>
       <c r="I231">
-        <v>3800.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -14511,19 +14786,24 @@
         </is>
       </c>
       <c r="K231">
-        <v>102408.24</v>
+        <v>89856.18</v>
       </c>
       <c r="L231">
         <v>39745.58</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>AUT-20260803-230</t>
+          <t>BI-3101691</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 03/08/2026</t>
         </is>
       </c>
     </row>
@@ -14535,7 +14815,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14545,27 +14825,27 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Google Workspace_altus</t>
+          <t>Cobro mensualidad agosto Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G232">
-        <v>234.96</v>
+        <v>6300.0</v>
       </c>
       <c r="H232">
-        <v>25.17</v>
+        <v>0.0</v>
       </c>
       <c r="I232">
-        <v>209.79</v>
+        <v>6300.0</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -14573,19 +14853,24 @@
         </is>
       </c>
       <c r="K232">
-        <v>102173.28</v>
+        <v>96156.18</v>
       </c>
       <c r="L232">
         <v>39745.58</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>AUT-20260805-231</t>
+          <t>BI-3120501</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 03/08/2026</t>
         </is>
       </c>
     </row>
@@ -14597,7 +14882,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14607,7 +14892,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Luís Felipe Guzmán</t>
+          <t>Cobro mensualidad agosto Andrei González</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14621,13 +14906,13 @@
         </is>
       </c>
       <c r="G233">
-        <v>9300.0</v>
+        <v>3800.0</v>
       </c>
       <c r="H233">
         <v>0.0</v>
       </c>
       <c r="I233">
-        <v>9300.0</v>
+        <v>3800.0</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -14635,19 +14920,24 @@
         </is>
       </c>
       <c r="K233">
-        <v>111473.28</v>
+        <v>99956.18</v>
       </c>
       <c r="L233">
         <v>39745.58</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>AUT-20260805-232</t>
+          <t>BI-3171312</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 03/08/2026</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14949,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14669,27 +14959,27 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Adriana García</t>
+          <t>Google Workspace_altus US</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G234">
-        <v>9300.0</v>
+        <v>234.96</v>
       </c>
       <c r="H234">
-        <v>0.0</v>
+        <v>25.17</v>
       </c>
       <c r="I234">
-        <v>9300.0</v>
+        <v>209.79</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -14697,19 +14987,24 @@
         </is>
       </c>
       <c r="K234">
-        <v>120773.28</v>
+        <v>99721.22</v>
       </c>
       <c r="L234">
         <v>39745.58</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>AUT-20260806-233</t>
+          <t>BI-102140</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 04/08/2026</t>
         </is>
       </c>
     </row>
@@ -14721,7 +15016,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14731,7 +15026,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Mateo Toribio</t>
+          <t>Cobro mensualidad agosto Luís Felipe Guzmán (Pamela Sosa)</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -14759,19 +15054,24 @@
         </is>
       </c>
       <c r="K235">
-        <v>130073.28</v>
+        <v>109021.22</v>
       </c>
       <c r="L235">
         <v>39745.58</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>AUT-20260807-234</t>
+          <t>BI-5138116</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/08/2026</t>
         </is>
       </c>
     </row>
@@ -14783,7 +15083,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14793,27 +15093,27 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Pago 2/3 instalación de cámaras</t>
+          <t>Cobro mensualidad agosto Adriana García</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G236">
-        <v>3473.58</v>
+        <v>9300.0</v>
       </c>
       <c r="H236">
-        <v>372.17</v>
+        <v>0.0</v>
       </c>
       <c r="I236">
-        <v>3101.41</v>
+        <v>9300.0</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -14821,19 +15121,24 @@
         </is>
       </c>
       <c r="K236">
-        <v>126599.7</v>
+        <v>118321.22</v>
       </c>
       <c r="L236">
         <v>39745.58</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>AUT-20260807-235</t>
+          <t>BI-6179707</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 06/08/2026</t>
         </is>
       </c>
     </row>
@@ -14845,7 +15150,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14855,7 +15160,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Giulia Fiorini</t>
+          <t>Cobro mensualidad agosto Mateo Toribio</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -14869,13 +15174,13 @@
         </is>
       </c>
       <c r="G237">
-        <v>1850.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H237">
         <v>0.0</v>
       </c>
       <c r="I237">
-        <v>1850.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -14883,19 +15188,24 @@
         </is>
       </c>
       <c r="K237">
-        <v>128449.7</v>
+        <v>127621.22</v>
       </c>
       <c r="L237">
         <v>39745.58</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>AUT-20260809-236</t>
+          <t>BI-7229247</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 07/08/2026</t>
         </is>
       </c>
     </row>
@@ -14907,7 +15217,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14917,27 +15227,27 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Cobro anticipo 5/6  inscripción Giulia Fiorini</t>
+          <t>Pago 2/3 instalación de cámaras</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>1501 - Mobiliario y Equipo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G238">
-        <v>308.35</v>
+        <v>3473.58</v>
       </c>
       <c r="H238">
-        <v>0.0</v>
+        <v>372.17</v>
       </c>
       <c r="I238">
-        <v>308.35</v>
+        <v>3101.41</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -14945,19 +15255,24 @@
         </is>
       </c>
       <c r="K238">
-        <v>128758.05</v>
+        <v>124147.64</v>
       </c>
       <c r="L238">
         <v>39745.58</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>AUT-20260809-237</t>
+          <t>BI-7169841</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 07/08/2026</t>
         </is>
       </c>
     </row>
@@ -14969,7 +15284,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14979,27 +15294,27 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Pago 3/3 instalación de cámaras</t>
+          <t>Cobro mensualidad agosto Giulia Fiorini</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G239">
-        <v>1275.0</v>
+        <v>1850.0</v>
       </c>
       <c r="H239">
-        <v>136.61</v>
+        <v>0.0</v>
       </c>
       <c r="I239">
-        <v>1138.39</v>
+        <v>1850.0</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -15007,19 +15322,24 @@
         </is>
       </c>
       <c r="K239">
-        <v>127483.05</v>
+        <v>125997.64</v>
       </c>
       <c r="L239">
         <v>39745.58</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>AUT-20260813-238</t>
+          <t>BI-9087491-A</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Parte de Docto 9087491 por Q2,158.34</t>
         </is>
       </c>
     </row>
@@ -15031,7 +15351,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15041,27 +15361,27 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Pago mes de Lucía Montes</t>
+          <t>Cobro anticipo 5/6 inscripción Giulia Fiorini</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G240">
-        <v>8574.53</v>
+        <v>308.34</v>
       </c>
       <c r="H240">
         <v>0.0</v>
       </c>
       <c r="I240">
-        <v>8574.53</v>
+        <v>308.34</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -15069,19 +15389,24 @@
         </is>
       </c>
       <c r="K240">
-        <v>118908.52</v>
+        <v>126305.98</v>
       </c>
       <c r="L240">
         <v>39745.58</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>AUT-20260827-239</t>
+          <t>BI-9087491-B</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Ajustado de Q308.35 a Q308.34 para cuadrar exacto con Docto 9087491 (Q2,158.34)</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15418,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15103,12 +15428,12 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Pago mes de Jessica Gudiel</t>
+          <t>Último pago 3/3 instalación de cámaras</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>1501 - Mobiliario y Equipo</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -15117,13 +15442,13 @@
         </is>
       </c>
       <c r="G241">
-        <v>5862.19</v>
+        <v>1275.0</v>
       </c>
       <c r="H241">
-        <v>0.0</v>
+        <v>136.61</v>
       </c>
       <c r="I241">
-        <v>5862.19</v>
+        <v>1138.39</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -15131,19 +15456,24 @@
         </is>
       </c>
       <c r="K241">
-        <v>113046.33</v>
+        <v>125030.98</v>
       </c>
       <c r="L241">
         <v>39745.58</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>AUT-20260827-240</t>
+          <t>BI-13192758</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 13/08/2026</t>
         </is>
       </c>
     </row>
@@ -15165,7 +15495,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Pago mes de Geovanna Velázquez</t>
+          <t>Pago sueldo agosto Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -15193,19 +15523,24 @@
         </is>
       </c>
       <c r="K242">
-        <v>108811.55</v>
+        <v>120796.2</v>
       </c>
       <c r="L242">
         <v>39745.58</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>AUT-20260827-241</t>
+          <t>BI-137504</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15562,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Pago mes de Suly Sajbochol</t>
+          <t>Pago sueldo agosto Suly Sajbochol</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -15255,19 +15590,24 @@
         </is>
       </c>
       <c r="K243">
-        <v>104576.77</v>
+        <v>116561.42</v>
       </c>
       <c r="L243">
         <v>39745.58</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>AUT-20260827-242</t>
+          <t>BI-152608</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15289,7 +15629,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Melissa Peña</t>
+          <t>Pago sueldo agosto Melissa Peña</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -15317,19 +15657,24 @@
         </is>
       </c>
       <c r="K244">
-        <v>100341.99</v>
+        <v>112326.64</v>
       </c>
       <c r="L244">
         <v>39745.58</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>AUT-20260827-243</t>
+          <t>BI-165806</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15351,7 +15696,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Donación a Fundación waybi</t>
+          <t>Donación agosto Fundación Waybi</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -15379,19 +15724,24 @@
         </is>
       </c>
       <c r="K245">
-        <v>98641.99</v>
+        <v>110626.64</v>
       </c>
       <c r="L245">
         <v>39745.58</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>AUT-20260827-244</t>
+          <t>BI-184088</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15413,12 +15763,12 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Pago ISR</t>
+          <t>Pago sueldo agosto Jessica Gudiel</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2105 - ISR Retenciones por Pagar</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -15427,13 +15777,13 @@
         </is>
       </c>
       <c r="G246">
-        <v>375.85</v>
+        <v>5862.19</v>
       </c>
       <c r="H246">
         <v>0.0</v>
       </c>
       <c r="I246">
-        <v>375.85</v>
+        <v>5862.19</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -15441,14 +15791,14 @@
         </is>
       </c>
       <c r="K246">
-        <v>98266.14</v>
+        <v>104764.45</v>
       </c>
       <c r="L246">
         <v>39745.58</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>AUT-20260827-245</t>
+          <t>BI-226221</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -15458,7 +15808,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>Reclasificado de 5210 a 2105: Entero a SAT de ISR retenido a empleadas.</t>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15480,27 +15830,27 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Provisiones laborales</t>
+          <t>Pago RRSS Altus Raúl</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2102 - Provisiones Laborales</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Traspaso Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G247">
-        <v>42000.0</v>
+        <v>500.0</v>
       </c>
       <c r="H247">
-        <v>0.0</v>
+        <v>53.57</v>
       </c>
       <c r="I247">
-        <v>42000.0</v>
+        <v>446.43</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -15508,14 +15858,14 @@
         </is>
       </c>
       <c r="K247">
-        <v>56266.14</v>
+        <v>104264.45</v>
       </c>
       <c r="L247">
-        <v>81745.58</v>
+        <v>39745.58</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>AUT-20260827-246</t>
+          <t>BI-231535</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -15525,7 +15875,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15547,12 +15897,12 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Pago Raúl rrss Altus</t>
+          <t>Pago sueldo agosto Lucía Montes</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -15561,13 +15911,13 @@
         </is>
       </c>
       <c r="G248">
-        <v>500.0</v>
+        <v>8574.54</v>
       </c>
       <c r="H248">
-        <v>53.57</v>
+        <v>0.0</v>
       </c>
       <c r="I248">
-        <v>446.43</v>
+        <v>8574.54</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -15575,19 +15925,24 @@
         </is>
       </c>
       <c r="K248">
-        <v>55766.14</v>
+        <v>95689.91</v>
       </c>
       <c r="L248">
-        <v>81745.58</v>
+        <v>39745.58</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>AUT-20260827-247</t>
+          <t>BI-27123339</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Ajustado a Q8,574.54 exactos según Docto 27123339</t>
         </is>
       </c>
     </row>
@@ -15609,7 +15964,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Publicidad agencia Nautaestudio Isa González</t>
+          <t>Publicidad agencia Nauta Estudio Isa González</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -15637,19 +15992,24 @@
         </is>
       </c>
       <c r="K249">
-        <v>53716.14</v>
+        <v>93639.91</v>
       </c>
       <c r="L249">
-        <v>81745.58</v>
+        <v>39745.58</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>AUT-20260827-248</t>
+          <t>BI-27143053</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15671,27 +16031,27 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Pago celular ALTUS</t>
+          <t>Provisiones laborales agosto (Traslado a BI-Ahorro)</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>2102 - Provisiones Laborales</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Traspaso Ahorro</t>
         </is>
       </c>
       <c r="G250">
-        <v>285.0</v>
+        <v>42000.0</v>
       </c>
       <c r="H250">
-        <v>30.54</v>
+        <v>0.0</v>
       </c>
       <c r="I250">
-        <v>254.46</v>
+        <v>42000.0</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -15699,19 +16059,24 @@
         </is>
       </c>
       <c r="K250">
-        <v>53431.14</v>
+        <v>51639.91</v>
       </c>
       <c r="L250">
         <v>81745.58</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>AUT-20260827-249</t>
+          <t>BI-27145997</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15733,7 +16098,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Pago servicio Sergio contador</t>
+          <t>Honorarios contabilidad agosto Sergio contador</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -15761,19 +16126,24 @@
         </is>
       </c>
       <c r="K251">
-        <v>53081.14</v>
+        <v>51289.91</v>
       </c>
       <c r="L251">
         <v>81745.58</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>AUT-20260827-250</t>
+          <t>BI-27176761</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15785,37 +16155,37 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Andrei González</t>
+          <t>Pago impuesto ISR retenido agosto</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>2105 - ISR Retenciones por Pagar</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G252">
-        <v>3800.0</v>
+        <v>375.85</v>
       </c>
       <c r="H252">
         <v>0.0</v>
       </c>
       <c r="I252">
-        <v>3800.0</v>
+        <v>375.85</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -15823,19 +16193,24 @@
         </is>
       </c>
       <c r="K252">
-        <v>56881.14</v>
+        <v>50914.06</v>
       </c>
       <c r="L252">
         <v>81745.58</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>AUT-20260901-251</t>
+          <t>BI-27197546</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15847,37 +16222,37 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Gabriel Ruíz</t>
+          <t>Pago celular ALTUS agosto</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G253">
-        <v>9300.0</v>
+        <v>285.0</v>
       </c>
       <c r="H253">
-        <v>0.0</v>
+        <v>30.54</v>
       </c>
       <c r="I253">
-        <v>9300.0</v>
+        <v>254.46</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -15885,19 +16260,24 @@
         </is>
       </c>
       <c r="K253">
-        <v>66181.14</v>
+        <v>50629.06</v>
       </c>
       <c r="L253">
         <v>81745.58</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>AUT-20260901-252</t>
+          <t>BI-27208297</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15909,7 +16289,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15919,27 +16299,27 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Google Workspace_altus</t>
+          <t>Cobro mensualidad septiembre Andrei González</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G254">
-        <v>234.96</v>
+        <v>3800.0</v>
       </c>
       <c r="H254">
-        <v>25.17</v>
+        <v>0.0</v>
       </c>
       <c r="I254">
-        <v>209.79</v>
+        <v>3800.0</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -15947,19 +16327,24 @@
         </is>
       </c>
       <c r="K254">
-        <v>65946.18</v>
+        <v>54429.06</v>
       </c>
       <c r="L254">
         <v>81745.58</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>AUT-20260902-253</t>
+          <t>BI-1163180</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 01/09/2026</t>
         </is>
       </c>
     </row>
@@ -15971,7 +16356,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15981,27 +16366,27 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Compra dolar city</t>
+          <t>Cobro mensualidad septiembre Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>5203 - Papelería, útiles y suministros</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G255">
-        <v>245.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H255">
-        <v>26.25</v>
+        <v>0.0</v>
       </c>
       <c r="I255">
-        <v>218.75</v>
+        <v>9300.0</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -16009,19 +16394,24 @@
         </is>
       </c>
       <c r="K255">
-        <v>65701.18</v>
+        <v>63729.06</v>
       </c>
       <c r="L255">
         <v>81745.58</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>AUT-20260902-254</t>
+          <t>BI-1224897</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 01/09/2026</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16423,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16043,27 +16433,27 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Adriana García</t>
+          <t>Débito BiCheque comisión manejo de cuenta septiembre</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G256">
-        <v>9300.0</v>
+        <v>15.0</v>
       </c>
       <c r="H256">
         <v>0.0</v>
       </c>
       <c r="I256">
-        <v>9300.0</v>
+        <v>15.0</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -16071,19 +16461,24 @@
         </is>
       </c>
       <c r="K256">
-        <v>75001.18</v>
+        <v>63714.06</v>
       </c>
       <c r="L256">
         <v>81745.58</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>AUT-20260904-255</t>
+          <t>BI-309025</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Agregado según extracto BI 01/09/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -16095,7 +16490,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16105,12 +16500,12 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Reparación ventana anticipo 1/2</t>
+          <t>Google Workspace_altus US</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -16119,13 +16514,13 @@
         </is>
       </c>
       <c r="G257">
-        <v>1550.0</v>
+        <v>234.96</v>
       </c>
       <c r="H257">
-        <v>166.07</v>
+        <v>25.17</v>
       </c>
       <c r="I257">
-        <v>1383.93</v>
+        <v>209.79</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -16133,19 +16528,24 @@
         </is>
       </c>
       <c r="K257">
-        <v>73451.18</v>
+        <v>63479.1</v>
       </c>
       <c r="L257">
         <v>81745.58</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>AUT-20260904-256</t>
+          <t>BI-123361</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16557,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16167,27 +16567,27 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Luis Felipe Guzmán</t>
+          <t>Compra Dollar City suministros</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5203 - Papelería, útiles y suministros</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G258">
-        <v>9300.0</v>
+        <v>245.0</v>
       </c>
       <c r="H258">
-        <v>0.0</v>
+        <v>26.25</v>
       </c>
       <c r="I258">
-        <v>9300.0</v>
+        <v>218.75</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -16195,19 +16595,24 @@
         </is>
       </c>
       <c r="K258">
-        <v>82751.18</v>
+        <v>63234.1</v>
       </c>
       <c r="L258">
         <v>81745.58</v>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>AUT-20260905-257</t>
+          <t>BI-2183529</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16624,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16229,7 +16634,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Giulia Fiorini</t>
+          <t>Cobro mensualidad septiembre Adriana García</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -16243,13 +16648,13 @@
         </is>
       </c>
       <c r="G259">
-        <v>1850.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H259">
         <v>0.0</v>
       </c>
       <c r="I259">
-        <v>1850.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -16257,19 +16662,24 @@
         </is>
       </c>
       <c r="K259">
-        <v>84601.18</v>
+        <v>72534.1</v>
       </c>
       <c r="L259">
         <v>81745.58</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>AUT-20260906-258</t>
+          <t>BI-4169159</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -16281,7 +16691,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16291,27 +16701,27 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Cobro anticipo inscripción 6/6 Giulia Fiorini</t>
+          <t>Honorarios reparación ventana anticipo 1/2</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G260">
-        <v>308.35</v>
+        <v>1550.0</v>
       </c>
       <c r="H260">
-        <v>0.0</v>
+        <v>166.07</v>
       </c>
       <c r="I260">
-        <v>308.35</v>
+        <v>1383.93</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -16319,19 +16729,24 @@
         </is>
       </c>
       <c r="K260">
-        <v>84909.53</v>
+        <v>70984.1</v>
       </c>
       <c r="L260">
         <v>81745.58</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>AUT-20260906-259</t>
+          <t>BI-4099839</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16758,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16353,7 +16768,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Mateo Toribio</t>
+          <t>Cobro mensualidad septiembre Luís Felipe Guzmán (Pamela Sosa)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -16381,19 +16796,24 @@
         </is>
       </c>
       <c r="K261">
-        <v>94209.53</v>
+        <v>80284.1</v>
       </c>
       <c r="L261">
         <v>81745.58</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>AUT-20260910-260</t>
+          <t>BI-5101701</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/09/2026 (Actualizado en pestaña Colegiaturas S7 = Q9,300)</t>
         </is>
       </c>
     </row>
@@ -16405,7 +16825,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16415,7 +16835,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Rodrigo Gallinsa</t>
+          <t>Cobro mensualidad septiembre Giulia Fiorini (Agencia El Frutal)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -16429,13 +16849,13 @@
         </is>
       </c>
       <c r="G262">
-        <v>6300.0</v>
+        <v>1850.0</v>
       </c>
       <c r="H262">
         <v>0.0</v>
       </c>
       <c r="I262">
-        <v>6300.0</v>
+        <v>1850.0</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -16443,19 +16863,24 @@
         </is>
       </c>
       <c r="K262">
-        <v>100509.53</v>
+        <v>82134.1</v>
       </c>
       <c r="L262">
         <v>81745.58</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>AUT-20260916-261</t>
+          <t>BI-14269407-A</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Parte de Docto 14269407 por Q2,158.34</t>
         </is>
       </c>
     </row>
@@ -16467,7 +16892,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16477,27 +16902,27 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Cobro anticipo 1/3 Inscripción 2027 Santi Matta</t>
+          <t>Cobro anticipo 6/6 inscripción Giulia Fiorini</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2107 - Anticipo de inscripciones</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Pasivo</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G263">
-        <v>4000.0</v>
+        <v>308.34</v>
       </c>
       <c r="H263">
         <v>0.0</v>
       </c>
       <c r="I263">
-        <v>4000.0</v>
+        <v>308.34</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -16505,19 +16930,24 @@
         </is>
       </c>
       <c r="K263">
-        <v>104509.53</v>
+        <v>82442.44</v>
       </c>
       <c r="L263">
         <v>81745.58</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>AUT-20260921-262</t>
+          <t>BI-14269407-B</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Ajustado de Q308.35 a Q308.34 según Docto 14269407 (Q2,158.34)</t>
         </is>
       </c>
     </row>
@@ -16529,7 +16959,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16539,27 +16969,27 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Excursion día del niño</t>
+          <t>Cobro mensualidad septiembre Mateo Toribio</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>5205 - Actividades y excursiones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G264">
-        <v>260.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H264">
-        <v>27.86</v>
+        <v>0.0</v>
       </c>
       <c r="I264">
-        <v>232.14</v>
+        <v>9300.0</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -16567,19 +16997,24 @@
         </is>
       </c>
       <c r="K264">
-        <v>104249.53</v>
+        <v>91742.44</v>
       </c>
       <c r="L264">
         <v>81745.58</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>AUT-20260921-263</t>
+          <t>BI-9222400</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>03-Eventos/ Extras</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -16591,7 +17026,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16601,27 +17036,27 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Compra carretilla novex</t>
+          <t>Cobro mensualidad septiembre Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>5207 - Otros Gastos (No Deducibles)</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G265">
-        <v>425.0</v>
+        <v>6300.0</v>
       </c>
       <c r="H265">
         <v>0.0</v>
       </c>
       <c r="I265">
-        <v>425.0</v>
+        <v>6300.0</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -16629,19 +17064,24 @@
         </is>
       </c>
       <c r="K265">
-        <v>103824.53</v>
+        <v>98042.44</v>
       </c>
       <c r="L265">
         <v>81745.58</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>AUT-20260921-264</t>
+          <t>BI-16160513</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -16653,7 +17093,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16663,27 +17103,27 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Pago extintor 1</t>
+          <t>Cobro anticipo 1/3 Inscripción 2027 Santiago Matta (ACH Juan José Mata)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>5207 - Otros Gastos (No Deducibles)</t>
+          <t>2107 - Anticipo de inscripciones</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pasivo</t>
         </is>
       </c>
       <c r="G266">
-        <v>250.0</v>
+        <v>4000.0</v>
       </c>
       <c r="H266">
         <v>0.0</v>
       </c>
       <c r="I266">
-        <v>250.0</v>
+        <v>4000.0</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -16691,19 +17131,24 @@
         </is>
       </c>
       <c r="K266">
-        <v>103574.53</v>
+        <v>102042.44</v>
       </c>
       <c r="L266">
         <v>81745.58</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>AUT-20260922-265</t>
+          <t>BI-162290</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -16715,7 +17160,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16725,12 +17170,12 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Pago extintor 2</t>
+          <t>Excursión Día del Niño</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>5207 - Otros Gastos (No Deducibles)</t>
+          <t>5205 - Actividades y excursiones</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -16739,13 +17184,13 @@
         </is>
       </c>
       <c r="G267">
-        <v>250.0</v>
+        <v>260.0</v>
       </c>
       <c r="H267">
-        <v>0.0</v>
+        <v>27.86</v>
       </c>
       <c r="I267">
-        <v>250.0</v>
+        <v>232.14</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -16753,19 +17198,24 @@
         </is>
       </c>
       <c r="K267">
-        <v>103324.53</v>
+        <v>101782.44</v>
       </c>
       <c r="L267">
         <v>81745.58</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>AUT-20260925-266</t>
+          <t>BI-218928</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +17227,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16787,12 +17237,12 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Pago mes Lucía Montes</t>
+          <t>Compra carretilla Novex San Cristóbal</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5207 - Otros Gastos (No Deducibles)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -16801,13 +17251,13 @@
         </is>
       </c>
       <c r="G268">
-        <v>8574.53</v>
+        <v>425.0</v>
       </c>
       <c r="H268">
         <v>0.0</v>
       </c>
       <c r="I268">
-        <v>8574.53</v>
+        <v>425.0</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -16815,19 +17265,24 @@
         </is>
       </c>
       <c r="K268">
-        <v>94750.0</v>
+        <v>101357.44</v>
       </c>
       <c r="L268">
         <v>81745.58</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>AUT-20260929-267</t>
+          <t>BI-148758</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -16839,7 +17294,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16849,12 +17304,12 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Pago mes Jessica Gudiel</t>
+          <t>Pago extintor 1</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5207 - Otros Gastos (No Deducibles)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -16863,13 +17318,13 @@
         </is>
       </c>
       <c r="G269">
-        <v>5862.19</v>
+        <v>250.0</v>
       </c>
       <c r="H269">
         <v>0.0</v>
       </c>
       <c r="I269">
-        <v>5862.19</v>
+        <v>250.0</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -16877,19 +17332,24 @@
         </is>
       </c>
       <c r="K269">
-        <v>88887.81</v>
+        <v>101107.44</v>
       </c>
       <c r="L269">
         <v>81745.58</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>AUT-20260929-268</t>
+          <t>BI-22108017</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -16901,7 +17361,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16911,12 +17371,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Pago mes Geovanna Velázquez</t>
+          <t>Pago segundo extintor</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5207 - Otros Gastos (No Deducibles)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -16925,13 +17385,13 @@
         </is>
       </c>
       <c r="G270">
-        <v>4234.78</v>
+        <v>250.0</v>
       </c>
       <c r="H270">
         <v>0.0</v>
       </c>
       <c r="I270">
-        <v>4234.78</v>
+        <v>250.0</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -16939,19 +17399,24 @@
         </is>
       </c>
       <c r="K270">
-        <v>84653.03</v>
+        <v>100857.44</v>
       </c>
       <c r="L270">
         <v>81745.58</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>AUT-20260929-269</t>
+          <t>BI-25176197</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -16973,12 +17438,12 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Pago mes Suly Sajbochol</t>
+          <t>Donación Fundación Waybi septiembre</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5208 - Donaciones</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -16987,13 +17452,13 @@
         </is>
       </c>
       <c r="G271">
-        <v>4234.78</v>
+        <v>1700.0</v>
       </c>
       <c r="H271">
-        <v>0.0</v>
+        <v>182.14</v>
       </c>
       <c r="I271">
-        <v>4234.78</v>
+        <v>1517.86</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -17001,19 +17466,24 @@
         </is>
       </c>
       <c r="K271">
-        <v>80418.25</v>
+        <v>99157.44</v>
       </c>
       <c r="L271">
         <v>81745.58</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>AUT-20260929-270</t>
+          <t>BI-99935</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -17035,7 +17505,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Pago mes Melissa Peña</t>
+          <t>Pago sueldo septiembre Jessica Gudiel</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -17049,13 +17519,13 @@
         </is>
       </c>
       <c r="G272">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="H272">
         <v>0.0</v>
       </c>
       <c r="I272">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -17063,19 +17533,24 @@
         </is>
       </c>
       <c r="K272">
-        <v>76183.47</v>
+        <v>93295.25</v>
       </c>
       <c r="L272">
         <v>81745.58</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>AUT-20260929-271</t>
+          <t>BI-109817</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -17097,12 +17572,12 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Donación Fundación waybi</t>
+          <t>Pago sueldo septiembre Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>5208 - Donaciones</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -17111,13 +17586,13 @@
         </is>
       </c>
       <c r="G273">
-        <v>1700.0</v>
+        <v>4234.78</v>
       </c>
       <c r="H273">
-        <v>182.14</v>
+        <v>0.0</v>
       </c>
       <c r="I273">
-        <v>1517.86</v>
+        <v>4234.78</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -17125,19 +17600,24 @@
         </is>
       </c>
       <c r="K273">
-        <v>74483.47</v>
+        <v>89060.47</v>
       </c>
       <c r="L273">
         <v>81745.58</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>AUT-20260929-272</t>
+          <t>BI-132249</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -17159,12 +17639,12 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>Pago sueldo septiembre Suly Sajbochol</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2105 - ISR Retenciones por Pagar</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -17173,13 +17653,13 @@
         </is>
       </c>
       <c r="G274">
-        <v>375.85</v>
+        <v>4234.78</v>
       </c>
       <c r="H274">
         <v>0.0</v>
       </c>
       <c r="I274">
-        <v>375.85</v>
+        <v>4234.78</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -17187,14 +17667,14 @@
         </is>
       </c>
       <c r="K274">
-        <v>74107.62</v>
+        <v>84825.69</v>
       </c>
       <c r="L274">
         <v>81745.58</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>AUT-20260929-273</t>
+          <t>BI-147240</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -17204,7 +17684,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>Reclasificado de 5210 a 2105: Entero a SAT de ISR retenido a empleadas.</t>
+          <t>Conciliado con extracto BI 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -17226,12 +17706,12 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>IGSS</t>
+          <t>Pago sueldo septiembre Melissa Peña</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2103 - IGSS por Pagar</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -17240,13 +17720,13 @@
         </is>
       </c>
       <c r="G275">
-        <v>4278.0</v>
+        <v>4234.78</v>
       </c>
       <c r="H275">
         <v>0.0</v>
       </c>
       <c r="I275">
-        <v>4278.0</v>
+        <v>4234.78</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -17254,14 +17734,14 @@
         </is>
       </c>
       <c r="K275">
-        <v>69829.62</v>
+        <v>80590.91</v>
       </c>
       <c r="L275">
         <v>81745.58</v>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>AUT-20260929-274</t>
+          <t>BI-167114</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -17271,7 +17751,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>Reclasificado de 5210 a 2103: Pago de planilla IGSS.</t>
+          <t>Conciliado con extracto BI 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -17293,27 +17773,27 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Provisiones laborales</t>
+          <t>Pago agencia redes sociales Isa González</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2102 - Provisiones Laborales</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Traspaso Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G276">
-        <v>11551.09</v>
+        <v>1600.0</v>
       </c>
       <c r="H276">
-        <v>0.0</v>
+        <v>171.43</v>
       </c>
       <c r="I276">
-        <v>11551.09</v>
+        <v>1428.57</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -17321,14 +17801,14 @@
         </is>
       </c>
       <c r="K276">
-        <v>58278.53</v>
+        <v>78990.91</v>
       </c>
       <c r="L276">
-        <v>93296.67</v>
+        <v>81745.58</v>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>AUT-20260929-275</t>
+          <t>BI-29114366</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -17338,7 +17818,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>Traslado mensual de Monetaria a Cuenta de Ahorro (Fondo Reserva Laboral e IGSS)</t>
+          <t>Conciliado con extracto BI 29/09/2026 (Docto 29114366: 5204 AGENCIA REDES SOCIALES)</t>
         </is>
       </c>
     </row>
@@ -17360,12 +17840,12 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Pago rrss Isa González</t>
+          <t>Pago sueldo septiembre Lucía Montes</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -17374,13 +17854,13 @@
         </is>
       </c>
       <c r="G277">
-        <v>1600.0</v>
+        <v>8574.54</v>
       </c>
       <c r="H277">
-        <v>171.43</v>
+        <v>0.0</v>
       </c>
       <c r="I277">
-        <v>1428.57</v>
+        <v>8574.54</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -17388,19 +17868,24 @@
         </is>
       </c>
       <c r="K277">
-        <v>56678.53</v>
+        <v>70416.37</v>
       </c>
       <c r="L277">
-        <v>93296.67</v>
+        <v>81745.58</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>AUT-20260929-276</t>
+          <t>BI-29116957</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 29/09/2026 (Q8,574.54 exactos)</t>
         </is>
       </c>
     </row>
@@ -17422,12 +17907,12 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Gestión papelería Lourdes Escribá</t>
+          <t>Pago celular ALTUS septiembre</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -17436,13 +17921,13 @@
         </is>
       </c>
       <c r="G278">
-        <v>1454.0</v>
+        <v>285.0</v>
       </c>
       <c r="H278">
-        <v>155.79</v>
+        <v>30.54</v>
       </c>
       <c r="I278">
-        <v>1298.21</v>
+        <v>254.46</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -17450,19 +17935,24 @@
         </is>
       </c>
       <c r="K278">
-        <v>55224.53</v>
+        <v>70131.37</v>
       </c>
       <c r="L278">
-        <v>93296.67</v>
+        <v>81745.58</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>AUT-20260929-277</t>
+          <t>BI-29152215</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -17484,27 +17974,27 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Pago celular ALTUS</t>
+          <t>Provisiones laborales septiembre (Traslado a BI-Ahorro)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>2102 - Provisiones Laborales</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Traspaso Ahorro</t>
         </is>
       </c>
       <c r="G279">
-        <v>285.0</v>
+        <v>11551.09</v>
       </c>
       <c r="H279">
-        <v>30.54</v>
+        <v>0.0</v>
       </c>
       <c r="I279">
-        <v>254.46</v>
+        <v>11551.09</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -17512,19 +18002,24 @@
         </is>
       </c>
       <c r="K279">
-        <v>54939.53</v>
+        <v>58580.28</v>
       </c>
       <c r="L279">
         <v>93296.67</v>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>AUT-20260929-278</t>
+          <t>BI-29180131</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -17546,47 +18041,52 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Sergio contador</t>
+          <t>Pago planilla IGSS (desde cuenta BI-Ahorro)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>2103 - IGSS por Pagar</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pago Reserva Ahorro</t>
         </is>
       </c>
       <c r="G280">
-        <v>350.0</v>
+        <v>4278.0</v>
       </c>
       <c r="H280">
-        <v>37.5</v>
+        <v>0.0</v>
       </c>
       <c r="I280">
-        <v>312.5</v>
+        <v>4278.0</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>BI- Monetaria</t>
+          <t>BI-Ahorro</t>
         </is>
       </c>
       <c r="K280">
-        <v>54589.53</v>
+        <v>58580.28</v>
       </c>
       <c r="L280">
-        <v>93296.67</v>
+        <v>89018.67</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>AUT-20260929-279</t>
+          <t>AHO-IGSS-09</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Corregido origen de BI-Monetaria a BI-Ahorro (no aparece en extracto Monetaria 2061406126 porque se paga desde Ahorro)</t>
         </is>
       </c>
     </row>
@@ -17608,7 +18108,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Gabriel Ruíz</t>
+          <t>Cobro mensualidad octubre Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -17636,19 +18136,24 @@
         </is>
       </c>
       <c r="K281">
-        <v>63889.53</v>
+        <v>67880.28</v>
       </c>
       <c r="L281">
-        <v>93296.67</v>
+        <v>89018.67</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>AUT-20261001-280</t>
+          <t>BI-1266971</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -17660,7 +18165,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17670,27 +18175,27 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Adriana García</t>
+          <t>Débito BiCheque comisión manejo de cuenta octubre</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G282">
-        <v>9300.0</v>
+        <v>15.0</v>
       </c>
       <c r="H282">
         <v>0.0</v>
       </c>
       <c r="I282">
-        <v>9300.0</v>
+        <v>15.0</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -17698,19 +18203,24 @@
         </is>
       </c>
       <c r="K282">
-        <v>73189.53</v>
+        <v>67865.28</v>
       </c>
       <c r="L282">
-        <v>93296.67</v>
+        <v>89018.67</v>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>AUT-20261002-281</t>
+          <t>BI-309581</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Agregado según extracto BI 01/10/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -17722,7 +18232,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17732,7 +18242,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Andrei González</t>
+          <t>Cobro mensualidad octubre Andrei González</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -17760,19 +18270,24 @@
         </is>
       </c>
       <c r="K283">
-        <v>76989.53</v>
+        <v>71665.28</v>
       </c>
       <c r="L283">
-        <v>93296.67</v>
+        <v>89018.67</v>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>AUT-20261004-282</t>
+          <t>BI-2090132</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -17784,7 +18299,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17794,7 +18309,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Luís Felipe Guzmán</t>
+          <t>Cobro mensualidad octubre Adriana García</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -17822,19 +18337,493 @@
         </is>
       </c>
       <c r="K284">
-        <v>86289.53</v>
+        <v>80965.28</v>
       </c>
       <c r="L284">
-        <v>93296.67</v>
+        <v>89018.67</v>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>AUT-20261005-283</t>
+          <t>BI-2141911</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 02/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ALT-26-284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>octubre</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Google Workspace_altus US octubre</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>5212 - Telecomunicaciones e internet</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Gasto</t>
+        </is>
+      </c>
+      <c r="G285">
+        <v>235.27</v>
+      </c>
+      <c r="H285">
+        <v>25.21</v>
+      </c>
+      <c r="I285">
+        <v>210.06</v>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>BI- Monetaria</t>
+        </is>
+      </c>
+      <c r="K285">
+        <v>80730.01</v>
+      </c>
+      <c r="L285">
+        <v>89018.67</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>BI-168343</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Agregado según extracto BI 02/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ALT-26-285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>octubre</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Cobro mensualidad octubre Luís Felipe Guzmán (Pamela Sosa)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>4102 - Colegiaturas Mensuales</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="G286">
+        <v>9300.0</v>
+      </c>
+      <c r="H286">
+        <v>0.0</v>
+      </c>
+      <c r="I286">
+        <v>9300.0</v>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>BI- Monetaria</t>
+        </is>
+      </c>
+      <c r="K286">
+        <v>90030.01</v>
+      </c>
+      <c r="L286">
+        <v>89018.67</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>BI-5140139</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>ALT-26-286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>octubre</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Pago ISR retenido personal (correspondiente a cierre sep)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>2105 - ISR Retenciones por Pagar</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Gasto</t>
+        </is>
+      </c>
+      <c r="G287">
+        <v>375.85</v>
+      </c>
+      <c r="H287">
+        <v>0.0</v>
+      </c>
+      <c r="I287">
+        <v>375.85</v>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>BI- Monetaria</t>
+        </is>
+      </c>
+      <c r="K287">
+        <v>89654.16</v>
+      </c>
+      <c r="L287">
+        <v>89018.67</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>BI-6107849</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Movido de 29/09 a su fecha real de débito en banco 06/10/2026 (Docto 6107849)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>ALT-26-287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>octubre</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Honorarios contabilidad Sergio contador</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>5209 - Honorarios profesionales</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Gasto</t>
+        </is>
+      </c>
+      <c r="G288">
+        <v>350.0</v>
+      </c>
+      <c r="H288">
+        <v>37.5</v>
+      </c>
+      <c r="I288">
+        <v>312.5</v>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>BI- Monetaria</t>
+        </is>
+      </c>
+      <c r="K288">
+        <v>89304.16</v>
+      </c>
+      <c r="L288">
+        <v>89018.67</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>BI-6161486</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Movido de 29/09 a su fecha real de débito en banco 06/10/2026 (Docto 6161486)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ALT-26-288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>octubre</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Cobro mensualidad octubre Giulia Fiorini (ACH Dilson Gerardo Fiori)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>4102 - Colegiaturas Mensuales</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="G289">
+        <v>1850.0</v>
+      </c>
+      <c r="H289">
+        <v>0.0</v>
+      </c>
+      <c r="I289">
+        <v>1850.0</v>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>BI- Monetaria</t>
+        </is>
+      </c>
+      <c r="K289">
+        <v>91154.16</v>
+      </c>
+      <c r="L289">
+        <v>89018.67</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>BI-127890</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Agregado según extracto BI 07/10/2026 y actualizado en Colegiaturas T5</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>ALT-26-289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>octubre</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Honorarios gestión papelería Lourdes Escribá (2 meses: Q1,454 x 2)</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>5209 - Honorarios profesionales</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Gasto</t>
+        </is>
+      </c>
+      <c r="G290">
+        <v>2908.0</v>
+      </c>
+      <c r="H290">
+        <v>311.57</v>
+      </c>
+      <c r="I290">
+        <v>2596.43</v>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>BI- Monetaria</t>
+        </is>
+      </c>
+      <c r="K290">
+        <v>88246.16</v>
+      </c>
+      <c r="L290">
+        <v>89018.67</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>BI-157584</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Ajustado según extracto BI 07/10/2026 (Docto 157584 por Q2,908.00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>ALT-26-290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>octubre</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Cobro mensualidad octubre Mateo Toribio</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>4102 - Colegiaturas Mensuales</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="G291">
+        <v>9300.0</v>
+      </c>
+      <c r="H291">
+        <v>0.0</v>
+      </c>
+      <c r="I291">
+        <v>9300.0</v>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>BI- Monetaria</t>
+        </is>
+      </c>
+      <c r="K291">
+        <v>97546.16</v>
+      </c>
+      <c r="L291">
+        <v>89018.67</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>BI-8120167</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Agregado según extracto BI 08/10/2026 y actualizado en Colegiaturas T8</t>
         </is>
       </c>
     </row>
@@ -17870,7 +18859,7 @@
     <col min="23" max="23" width="12" customWidth="1"/>
     <col min="24" max="24" width="18" customWidth="1"/>
     <col min="25" max="25" width="18" customWidth="1"/>
-    <col min="26" max="26" width="20" customWidth="1"/>
+    <col min="26" max="26" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18357,7 +19346,7 @@
         <v>1850.0</v>
       </c>
       <c r="U5">
-        <v>0.0</v>
+        <v>1850.0</v>
       </c>
       <c r="V5">
         <v>0.0</v>
@@ -18366,14 +19355,14 @@
         <v>0.0</v>
       </c>
       <c r="X5">
-        <v>11100.0</v>
+        <v>12950.0</v>
       </c>
       <c r="Y5">
-        <v>1850.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Pendiente Octubre</t>
+          <t>Al Día</t>
         </is>
       </c>
     </row>
@@ -18545,7 +19534,7 @@
         <v>9300.0</v>
       </c>
       <c r="T7">
-        <v>0.0</v>
+        <v>9300.0</v>
       </c>
       <c r="U7">
         <v>9300.0</v>
@@ -18557,14 +19546,14 @@
         <v>0.0</v>
       </c>
       <c r="X7">
-        <v>83700.0</v>
+        <v>93000.0</v>
       </c>
       <c r="Y7">
-        <v>9300.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Con Saldo Pendiente</t>
+          <t>Al Día</t>
         </is>
       </c>
     </row>
@@ -18641,7 +19630,7 @@
         <v>9300.0</v>
       </c>
       <c r="U8">
-        <v>0.0</v>
+        <v>9300.0</v>
       </c>
       <c r="V8">
         <v>0.0</v>
@@ -18650,14 +19639,14 @@
         <v>0.0</v>
       </c>
       <c r="X8">
-        <v>83700.0</v>
+        <v>93000.0</v>
       </c>
       <c r="Y8">
-        <v>9300.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Pendiente Octubre</t>
+          <t>Al Día</t>
         </is>
       </c>
     </row>
@@ -18776,10 +19765,10 @@
         </is>
       </c>
       <c r="H10">
-        <v>0.0</v>
+        <v>10300.0</v>
       </c>
       <c r="I10">
-        <v>0.0</v>
+        <v>4000.0</v>
       </c>
       <c r="J10">
         <v>0.0</v>
@@ -18833,7 +19822,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Retirado</t>
+          <t>Inscrito 2027 (Anticipo Q4,000)</t>
         </is>
       </c>
     </row>
@@ -19554,14 +20543,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="55" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="65" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19572,42 +20560,37 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t>Saldo Libro BI-Monetaria (Q)</t>
+          <t>Saldo Libro BI-Monetaria Sin Intereses (Q)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t>Saldo Estado Cuenta BI (Q)</t>
+          <t>Saldo Extracto Banco Industrial 2061406126 (Q)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t>Diferencia (Q)</t>
+          <t>Intereses Acumulados No Contabilizados en Libro (Q)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
-          <t>Ajuste Conciliación (Q)</t>
+          <t>Saldo Monetaria Conciliado (Q)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
-          <t>Saldo Monetaria Conciliado (Q)</t>
+          <t>Saldo Acumulado BI-Ahorro (Q)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr" s="1">
         <is>
-          <t>Saldo Acumulado BI-Ahorro (Q)</t>
+          <t>Estado Auditoría</t>
         </is>
       </c>
       <c r="H1" t="inlineStr" s="1">
         <is>
-          <t>Estado Auditoría</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t>Explicación Técnica de Conciliación</t>
+          <t>Detalle de Conciliación Bancaria</t>
         </is>
       </c>
     </row>
@@ -19624,25 +20607,22 @@
         <v>55019.75</v>
       </c>
       <c r="D2">
-        <v>-12.01</v>
+        <v>12.01</v>
       </c>
       <c r="E2">
-        <v>-12.01</v>
+        <v>55019.75</v>
       </c>
       <c r="F2">
-        <v>55019.75</v>
-      </c>
-      <c r="G2">
         <v>9189.57</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>✅ Conciliado (Dif = Intereses)</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Conciliado con Ajuste</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Intereses bancarios acreditados / nota de crédito en estado de cuenta por Q 12.01 pendiente de asiento de ajuste.</t>
+          <t>Diferencia por intereses bancarios enero (+Q27.01) menos comisión BiCheque (-Q15.00).</t>
         </is>
       </c>
     </row>
@@ -19659,25 +20639,22 @@
         <v>54173.57</v>
       </c>
       <c r="D3">
-        <v>8.17</v>
+        <v>-8.17</v>
       </c>
       <c r="E3">
-        <v>8.17</v>
+        <v>54173.57</v>
       </c>
       <c r="F3">
-        <v>54173.57</v>
-      </c>
-      <c r="G3">
         <v>18346.49</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>✅ Conciliado (Dif = Intereses)</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Conciliado con Ajuste</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Comisión bancaria / ajuste de centavos en transferencias ACH por Q 8.17 pendiente de registrar.</t>
+          <t>Diferencia acumulada por intereses bancarios y comisión BiCheque feb.</t>
         </is>
       </c>
     </row>
@@ -19694,25 +20671,22 @@
         <v>63341.68</v>
       </c>
       <c r="D4">
-        <v>-36.29</v>
+        <v>36.29</v>
       </c>
       <c r="E4">
-        <v>-36.29</v>
+        <v>63341.68</v>
       </c>
       <c r="F4">
-        <v>63341.68</v>
-      </c>
-      <c r="G4">
         <v>32758.49</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>✅ Conciliado (Dif = Intereses)</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Conciliado con Ajuste</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Intereses bancarios acreditados / nota de crédito en estado de cuenta por Q 36.29 pendiente de asiento de ajuste.</t>
+          <t>Diferencia acumulada por intereses bancarios ene-mar.</t>
         </is>
       </c>
     </row>
@@ -19729,25 +20703,22 @@
         <v>70964.2</v>
       </c>
       <c r="D5">
-        <v>-165.2</v>
+        <v>165.2</v>
       </c>
       <c r="E5">
-        <v>-165.2</v>
+        <v>70964.2</v>
       </c>
       <c r="F5">
-        <v>70964.2</v>
-      </c>
-      <c r="G5">
         <v>44310.49</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>✅ Conciliado (Dif = Intereses)</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Conciliado con Ajuste</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Intereses bancarios acreditados / nota de crédito en estado de cuenta por Q 165.20 pendiente de asiento de ajuste.</t>
+          <t>Diferencia acumulada por intereses bancarios y ajuste centavos ene-abr.</t>
         </is>
       </c>
     </row>
@@ -19761,28 +20732,25 @@
         <v>59649.68</v>
       </c>
       <c r="C6">
-        <v>59837.0</v>
+        <v>59837.62</v>
       </c>
       <c r="D6">
-        <v>-187.32</v>
+        <v>187.94</v>
       </c>
       <c r="E6">
-        <v>-187.32</v>
+        <v>59837.62</v>
       </c>
       <c r="F6">
-        <v>59837.0</v>
-      </c>
-      <c r="G6">
         <v>44242.49</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>✅ Conciliado (Dif = Intereses)</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Conciliado con Ajuste</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Intereses bancarios acreditados / nota de crédito en estado de cuenta por Q 187.32 pendiente de asiento de ajuste.</t>
+          <t>Saldo final confirmado en extracto BI junio (Q59,837.62). Diferencia acumulada de Q187.94 al 31/05.</t>
         </is>
       </c>
     </row>
@@ -19793,31 +20761,28 @@
         </is>
       </c>
       <c r="B7">
-        <v>62680.31</v>
+        <v>63559.98</v>
       </c>
       <c r="C7">
         <v>63783.56</v>
       </c>
       <c r="D7">
-        <v>-1103.25</v>
+        <v>223.58</v>
       </c>
       <c r="E7">
-        <v>-1103.25</v>
+        <v>63783.56</v>
       </c>
       <c r="F7">
-        <v>63783.56</v>
-      </c>
-      <c r="G7">
         <v>28194.49</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>✅ Conciliado (Dif = Intereses)</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Conciliado con Ajuste</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Intereses bancarios acreditados / nota de crédito en estado de cuenta por Q 1103.25 pendiente de asiento de ajuste.</t>
+          <t>100% cuadrado en movimientos operativos (Créditos Q53,504.51 | Débitos Q49,594.21). Dif = Q187.94 mayo + Q35.64 intereses junio.</t>
         </is>
       </c>
     </row>
@@ -19828,31 +20793,28 @@
         </is>
       </c>
       <c r="B8">
-        <v>76708.24</v>
+        <v>74271.18</v>
       </c>
       <c r="C8">
         <v>74532.51</v>
       </c>
       <c r="D8">
-        <v>2175.73</v>
+        <v>261.33</v>
       </c>
       <c r="E8">
-        <v>2175.73</v>
+        <v>74532.51</v>
       </c>
       <c r="F8">
-        <v>74532.51</v>
-      </c>
-      <c r="G8">
         <v>39745.58</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>✅ Conciliado (Dif = Intereses)</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Conciliado con Ajuste</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Comisión bancaria / ajuste de centavos en transferencias ACH por Q 2175.73 pendiente de registrar.</t>
+          <t>100% cuadrado en movimientos operativos (Créditos Q68,155.85 | Débitos Q57,444.65). Dif = Q223.58 jun + Q37.75 intereses julio.</t>
         </is>
       </c>
     </row>
@@ -19863,33 +20825,28 @@
         </is>
       </c>
       <c r="B9">
-        <v>53081.13</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pendiente Estado Cta</t>
-        </is>
+        <v>50629.06</v>
+      </c>
+      <c r="C9">
+        <v>50931.57</v>
       </c>
       <c r="D9">
-        <v>0.0</v>
+        <v>302.51</v>
       </c>
       <c r="E9">
-        <v>0.0</v>
+        <v>50931.57</v>
       </c>
       <c r="F9">
-        <v>53081.13</v>
-      </c>
-      <c r="G9">
         <v>81745.58</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>✅ Conciliado (Dif = Intereses)</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>En Curso</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Pendiente ingresar saldo final del estado de cuenta bancario BI.</t>
+          <t>100% cuadrado en movimientos operativos (Créditos Q55,758.34 | Débitos Q79,400.46). Dif = Q261.33 jul + Q41.18 intereses agosto.</t>
         </is>
       </c>
     </row>
@@ -19900,33 +20857,28 @@
         </is>
       </c>
       <c r="B10">
-        <v>54589.51</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Pendiente Estado Cta</t>
-        </is>
+        <v>58580.28</v>
+      </c>
+      <c r="C10">
+        <v>58915.53</v>
       </c>
       <c r="D10">
-        <v>0.0</v>
+        <v>335.25</v>
       </c>
       <c r="E10">
-        <v>0.0</v>
+        <v>58915.53</v>
       </c>
       <c r="F10">
-        <v>54589.51</v>
-      </c>
-      <c r="G10">
-        <v>93296.67</v>
+        <v>89018.67</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>✅ Conciliado (Dif = Intereses)</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>En Curso</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Pendiente ingresar saldo final del estado de cuenta bancario BI.</t>
+          <t>100% cuadrado en movimientos operativos (Créditos Q53,458.34 | Débitos Q45,507.12). Dif = Q302.51 ago + Q32.74 intereses septiembre.</t>
         </is>
       </c>
     </row>
@@ -19937,97 +20889,28 @@
         </is>
       </c>
       <c r="B11">
-        <v>86289.51</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pendiente Estado Cta</t>
-        </is>
+        <v>97546.16</v>
+      </c>
+      <c r="C11">
+        <v>97881.41</v>
       </c>
       <c r="D11">
-        <v>0.0</v>
+        <v>335.25</v>
       </c>
       <c r="E11">
-        <v>0.0</v>
+        <v>97881.41</v>
       </c>
       <c r="F11">
-        <v>86289.51</v>
-      </c>
-      <c r="G11">
-        <v>93296.67</v>
+        <v>89018.67</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>✅ Conciliado (Dif = Intereses)</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>En Curso</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Pendiente ingresar saldo final del estado de cuenta bancario BI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Noviembre</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>0.0</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Pendiente Estado Cta</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.0</v>
-      </c>
-      <c r="E12">
-        <v>0.0</v>
-      </c>
-      <c r="F12">
-        <v>0.0</v>
-      </c>
-      <c r="G12">
-        <v>93296.67</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Diciembre</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>0.0</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pendiente Estado Cta</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.0</v>
-      </c>
-      <c r="E13">
-        <v>0.0</v>
-      </c>
-      <c r="F13">
-        <v>0.0</v>
-      </c>
-      <c r="G13">
-        <v>93296.67</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Futuro</t>
+          <t>100% cuadrado al 08/10/2026 con extracto BI (Créditos Q42,850.00 | Débitos Q3,884.12). Dif = Q335.25 intereses acumulados ene-sep.</t>
         </is>
       </c>
     </row>
@@ -20330,10 +21213,10 @@
         <v>0.0</v>
       </c>
       <c r="I6">
-        <v>0.0</v>
+        <v>7680.0</v>
       </c>
       <c r="J6">
-        <v>0.0</v>
+        <v>4748.58</v>
       </c>
       <c r="K6">
         <v>0.0</v>
@@ -20342,7 +21225,7 @@
         <v>0.0</v>
       </c>
       <c r="M6">
-        <v>35702.5</v>
+        <v>48131.08</v>
       </c>
     </row>
     <row r="7">
@@ -20471,19 +21354,19 @@
         <v>0.0</v>
       </c>
       <c r="K9">
-        <v>0.0</v>
+        <v>4278.0</v>
       </c>
       <c r="L9">
         <v>0.0</v>
       </c>
       <c r="M9">
-        <v>18216.0</v>
+        <v>22494.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2103 - IGSS por Pagar</t>
+          <t>2105 - ISR Retenciones por Pagar</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20495,85 +21378,85 @@
         <v>0.0</v>
       </c>
       <c r="D10">
-        <v>0.0</v>
+        <v>375.85</v>
       </c>
       <c r="E10">
-        <v>0.0</v>
+        <v>376.0</v>
       </c>
       <c r="F10">
-        <v>0.0</v>
+        <v>375.85</v>
       </c>
       <c r="G10">
-        <v>0.0</v>
+        <v>375.85</v>
       </c>
       <c r="H10">
         <v>0.0</v>
       </c>
       <c r="I10">
-        <v>0.0</v>
+        <v>751.73</v>
       </c>
       <c r="J10">
-        <v>0.0</v>
+        <v>375.85</v>
       </c>
       <c r="K10">
-        <v>4278.0</v>
+        <v>0.0</v>
       </c>
       <c r="L10">
-        <v>0.0</v>
+        <v>375.85</v>
       </c>
       <c r="M10">
-        <v>4278.0</v>
+        <v>3006.98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2105 - ISR Retenciones por Pagar</t>
+          <t>2106 - Acreedores por Cuenta Ajena</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pasivo</t>
         </is>
       </c>
       <c r="C11">
-        <v>0.0</v>
+        <v>3629.0</v>
       </c>
       <c r="D11">
-        <v>375.85</v>
+        <v>69.0</v>
       </c>
       <c r="E11">
-        <v>376.0</v>
+        <v>247.0</v>
       </c>
       <c r="F11">
-        <v>375.85</v>
+        <v>1047.0</v>
       </c>
       <c r="G11">
-        <v>375.85</v>
+        <v>0.0</v>
       </c>
       <c r="H11">
         <v>0.0</v>
       </c>
       <c r="I11">
-        <v>751.73</v>
+        <v>0.0</v>
       </c>
       <c r="J11">
-        <v>375.85</v>
+        <v>0.0</v>
       </c>
       <c r="K11">
-        <v>375.85</v>
+        <v>0.0</v>
       </c>
       <c r="L11">
         <v>0.0</v>
       </c>
       <c r="M11">
-        <v>3006.98</v>
+        <v>4992.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2106 - Acreedores por Cuenta Ajena</t>
+          <t>2107 - Anticipo de inscripciones</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -20582,16 +21465,16 @@
         </is>
       </c>
       <c r="C12">
-        <v>3629.0</v>
+        <v>0.0</v>
       </c>
       <c r="D12">
-        <v>69.0</v>
+        <v>0.0</v>
       </c>
       <c r="E12">
-        <v>247.0</v>
+        <v>0.0</v>
       </c>
       <c r="F12">
-        <v>1047.0</v>
+        <v>0.0</v>
       </c>
       <c r="G12">
         <v>0.0</v>
@@ -20600,70 +21483,70 @@
         <v>0.0</v>
       </c>
       <c r="I12">
-        <v>0.0</v>
+        <v>5150.0</v>
       </c>
       <c r="J12">
         <v>0.0</v>
       </c>
       <c r="K12">
-        <v>0.0</v>
+        <v>4000.0</v>
       </c>
       <c r="L12">
         <v>0.0</v>
       </c>
       <c r="M12">
-        <v>4992.0</v>
+        <v>9150.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2107 - Anticipo de inscripciones</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pasivo</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="C13">
-        <v>0.0</v>
+        <v>58716.66</v>
       </c>
       <c r="D13">
-        <v>0.0</v>
+        <v>1716.66</v>
       </c>
       <c r="E13">
-        <v>0.0</v>
+        <v>1716.66</v>
       </c>
       <c r="F13">
-        <v>0.0</v>
+        <v>3312.5</v>
       </c>
       <c r="G13">
-        <v>0.0</v>
+        <v>1595.5</v>
       </c>
       <c r="H13">
-        <v>0.0</v>
+        <v>3312.51</v>
       </c>
       <c r="I13">
-        <v>5150.0</v>
+        <v>3312.54</v>
       </c>
       <c r="J13">
-        <v>0.0</v>
+        <v>308.34</v>
       </c>
       <c r="K13">
-        <v>4000.0</v>
+        <v>308.34</v>
       </c>
       <c r="L13">
         <v>0.0</v>
       </c>
       <c r="M13">
-        <v>9150.0</v>
+        <v>74299.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -20672,43 +21555,43 @@
         </is>
       </c>
       <c r="C14">
-        <v>58716.66</v>
+        <v>31700.0</v>
       </c>
       <c r="D14">
-        <v>1716.66</v>
+        <v>44800.0</v>
       </c>
       <c r="E14">
-        <v>1716.66</v>
+        <v>43257.57</v>
       </c>
       <c r="F14">
-        <v>3312.5</v>
+        <v>52950.0</v>
       </c>
       <c r="G14">
-        <v>1595.5</v>
+        <v>51908.33</v>
       </c>
       <c r="H14">
-        <v>3312.84</v>
+        <v>50192.0</v>
       </c>
       <c r="I14">
-        <v>3312.54</v>
+        <v>47193.31</v>
       </c>
       <c r="J14">
-        <v>308.35</v>
+        <v>55450.0</v>
       </c>
       <c r="K14">
-        <v>308.35</v>
+        <v>49150.0</v>
       </c>
       <c r="L14">
-        <v>0.0</v>
+        <v>42850.0</v>
       </c>
       <c r="M14">
-        <v>74300.06</v>
+        <v>469451.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4200 - Ingresos Comerciales (Afectos)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -20717,43 +21600,43 @@
         </is>
       </c>
       <c r="C15">
-        <v>31700.0</v>
+        <v>0.0</v>
       </c>
       <c r="D15">
-        <v>44800.0</v>
+        <v>1075.0</v>
       </c>
       <c r="E15">
-        <v>43257.57</v>
+        <v>0.0</v>
       </c>
       <c r="F15">
-        <v>52950.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15">
-        <v>51908.33</v>
+        <v>300.0</v>
       </c>
       <c r="H15">
-        <v>50192.0</v>
+        <v>0.0</v>
       </c>
       <c r="I15">
-        <v>50495.04</v>
+        <v>0.0</v>
       </c>
       <c r="J15">
-        <v>55450.0</v>
+        <v>0.0</v>
       </c>
       <c r="K15">
-        <v>49150.0</v>
+        <v>0.0</v>
       </c>
       <c r="L15">
-        <v>31700.0</v>
+        <v>0.0</v>
       </c>
       <c r="M15">
-        <v>461602.94</v>
+        <v>1375.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4200 - Ingresos Comerciales (Afectos)</t>
+          <t>4201 - Venta de Libros y Uniformes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -20765,7 +21648,7 @@
         <v>0.0</v>
       </c>
       <c r="D16">
-        <v>1075.0</v>
+        <v>0.0</v>
       </c>
       <c r="E16">
         <v>0.0</v>
@@ -20774,7 +21657,7 @@
         <v>0.0</v>
       </c>
       <c r="G16">
-        <v>300.0</v>
+        <v>400.0</v>
       </c>
       <c r="H16">
         <v>0.0</v>
@@ -20792,13 +21675,13 @@
         <v>0.0</v>
       </c>
       <c r="M16">
-        <v>1375.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4201 - Venta de Libros y Uniformes</t>
+          <t>4203 - Donaciones recibidas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -20813,19 +21696,19 @@
         <v>0.0</v>
       </c>
       <c r="E17">
-        <v>0.0</v>
+        <v>38976.9</v>
       </c>
       <c r="F17">
         <v>0.0</v>
       </c>
       <c r="G17">
-        <v>400.0</v>
+        <v>12960.0</v>
       </c>
       <c r="H17">
         <v>0.0</v>
       </c>
       <c r="I17">
-        <v>0.0</v>
+        <v>12500.0</v>
       </c>
       <c r="J17">
         <v>0.0</v>
@@ -20837,58 +21720,58 @@
         <v>0.0</v>
       </c>
       <c r="M17">
-        <v>400.0</v>
+        <v>64436.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4203 - Donaciones recibidas</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="C18">
-        <v>0.0</v>
+        <v>27204.35</v>
       </c>
       <c r="D18">
-        <v>0.0</v>
+        <v>27254.35</v>
       </c>
       <c r="E18">
-        <v>38976.9</v>
+        <v>27154.17</v>
       </c>
       <c r="F18">
-        <v>0.0</v>
+        <v>27154.17</v>
       </c>
       <c r="G18">
-        <v>12960.0</v>
+        <v>27154.17</v>
       </c>
       <c r="H18">
-        <v>0.0</v>
+        <v>27144.07</v>
       </c>
       <c r="I18">
-        <v>12500.0</v>
+        <v>27141.07</v>
       </c>
       <c r="J18">
-        <v>0.0</v>
+        <v>27141.07</v>
       </c>
       <c r="K18">
-        <v>0.0</v>
+        <v>27141.07</v>
       </c>
       <c r="L18">
         <v>0.0</v>
       </c>
       <c r="M18">
-        <v>64436.9</v>
+        <v>244488.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5104 - Bono 14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -20897,37 +21780,37 @@
         </is>
       </c>
       <c r="C19">
-        <v>27204.35</v>
+        <v>0.0</v>
       </c>
       <c r="D19">
-        <v>27254.35</v>
+        <v>0.0</v>
       </c>
       <c r="E19">
-        <v>27154.17</v>
+        <v>0.0</v>
       </c>
       <c r="F19">
-        <v>27154.17</v>
+        <v>0.0</v>
       </c>
       <c r="G19">
-        <v>27154.17</v>
+        <v>0.0</v>
       </c>
       <c r="H19">
-        <v>27144.07</v>
+        <v>2000.0</v>
       </c>
       <c r="I19">
-        <v>27141.07</v>
+        <v>0.0</v>
       </c>
       <c r="J19">
-        <v>27141.06</v>
+        <v>0.0</v>
       </c>
       <c r="K19">
-        <v>27141.06</v>
+        <v>0.0</v>
       </c>
       <c r="L19">
         <v>0.0</v>
       </c>
       <c r="M19">
-        <v>244488.47</v>
+        <v>2000.0</v>
       </c>
     </row>
     <row r="20">
@@ -21005,7 +21888,7 @@
         <v>0.0</v>
       </c>
       <c r="I21">
-        <v>1201.8</v>
+        <v>455.9</v>
       </c>
       <c r="J21">
         <v>0.0</v>
@@ -21017,7 +21900,7 @@
         <v>0.0</v>
       </c>
       <c r="M21">
-        <v>5560.07</v>
+        <v>4814.17</v>
       </c>
     </row>
     <row r="22">
@@ -21050,19 +21933,19 @@
         <v>3150.0</v>
       </c>
       <c r="I22">
-        <v>0.0</v>
+        <v>2550.0</v>
       </c>
       <c r="J22">
         <v>2550.0</v>
       </c>
       <c r="K22">
-        <v>0.0</v>
+        <v>1600.0</v>
       </c>
       <c r="L22">
         <v>0.0</v>
       </c>
       <c r="M22">
-        <v>7300.0</v>
+        <v>11450.0</v>
       </c>
     </row>
     <row r="23">
@@ -21092,10 +21975,10 @@
         <v>642.87</v>
       </c>
       <c r="H23">
-        <v>3210.0</v>
+        <v>1210.0</v>
       </c>
       <c r="I23">
-        <v>895.0</v>
+        <v>1640.9</v>
       </c>
       <c r="J23">
         <v>0.0</v>
@@ -21107,7 +21990,7 @@
         <v>0.0</v>
       </c>
       <c r="M23">
-        <v>6536.87</v>
+        <v>5282.77</v>
       </c>
     </row>
     <row r="24">
@@ -21137,7 +22020,7 @@
         <v>0.0</v>
       </c>
       <c r="H24">
-        <v>895.0</v>
+        <v>0.0</v>
       </c>
       <c r="I24">
         <v>0.0</v>
@@ -21152,7 +22035,7 @@
         <v>0.0</v>
       </c>
       <c r="M24">
-        <v>1820.0</v>
+        <v>925.0</v>
       </c>
     </row>
     <row r="25">
@@ -21230,19 +22113,19 @@
         <v>2303.48</v>
       </c>
       <c r="I26">
-        <v>10834.0</v>
+        <v>3154.0</v>
       </c>
       <c r="J26">
-        <v>5098.58</v>
+        <v>350.0</v>
       </c>
       <c r="K26">
-        <v>4954.0</v>
+        <v>1550.0</v>
       </c>
       <c r="L26">
-        <v>0.0</v>
+        <v>3258.0</v>
       </c>
       <c r="M26">
-        <v>37671.14</v>
+        <v>25096.56</v>
       </c>
     </row>
     <row r="27">
@@ -21272,22 +22155,22 @@
         <v>0.0</v>
       </c>
       <c r="H27">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="I27">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="J27">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="K27">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="L27">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="M27">
-        <v>668.0</v>
+        <v>743.0</v>
       </c>
     </row>
     <row r="28">
@@ -21320,7 +22203,7 @@
         <v>519.66</v>
       </c>
       <c r="I28">
-        <v>3354.96</v>
+        <v>804.96</v>
       </c>
       <c r="J28">
         <v>519.96</v>
@@ -21329,10 +22212,10 @@
         <v>519.96</v>
       </c>
       <c r="L28">
-        <v>0.0</v>
+        <v>235.27</v>
       </c>
       <c r="M28">
-        <v>7335.85</v>
+        <v>5021.12</v>
       </c>
     </row>
   </sheetData>

--- a/Libro_Contable_ALTUS_26_Auditado.xlsx
+++ b/Libro_Contable_ALTUS_26_Auditado.xlsx
@@ -7630,12 +7630,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Pago Lourdes Escribá</t>
+          <t>Débito BiCheque comisión manejo de cuenta mayo</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="G122">
-        <v>1454.0</v>
+        <v>15.0</v>
       </c>
       <c r="H122">
-        <v>155.79</v>
+        <v>0.0</v>
       </c>
       <c r="I122">
-        <v>1298.21</v>
+        <v>15.0</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -7658,19 +7658,24 @@
         </is>
       </c>
       <c r="K122">
-        <v>69345.0</v>
+        <v>70784.0</v>
       </c>
       <c r="L122">
         <v>44310.49</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>AUT-20260501-121</t>
+          <t>BI-308785</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Agregado según extracto BI 01/05/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7687,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7692,27 +7697,27 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Gabriel Ruíz</t>
+          <t>Pago Lourdes Escribá</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G123">
-        <v>9300.0</v>
+        <v>1454.0</v>
       </c>
       <c r="H123">
-        <v>0.0</v>
+        <v>155.79</v>
       </c>
       <c r="I123">
-        <v>9300.0</v>
+        <v>1298.21</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -7720,19 +7725,24 @@
         </is>
       </c>
       <c r="K123">
-        <v>78645.0</v>
+        <v>69330.0</v>
       </c>
       <c r="L123">
         <v>44310.49</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>AUT-20260504-122</t>
+          <t>BI-1153410</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 01/05/2026</t>
         </is>
       </c>
     </row>
@@ -7754,12 +7764,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Cobro 3 playeras polo de Gabriel Ruíz</t>
+          <t>Cobro mensualidad Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>4201 - Venta de Libros y Uniformes</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7768,13 +7778,13 @@
         </is>
       </c>
       <c r="G124">
-        <v>300.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H124">
         <v>0.0</v>
       </c>
       <c r="I124">
-        <v>300.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -7782,19 +7792,24 @@
         </is>
       </c>
       <c r="K124">
-        <v>78945.0</v>
+        <v>78630.0</v>
       </c>
       <c r="L124">
         <v>44310.49</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>AUT-20260504-123</t>
+          <t>BI-4197036</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7816,12 +7831,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Cobro mensualidad Giulia Fiorini</t>
+          <t>Cobro 3 playeras polo de Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4201 - Venta de Libros y Uniformes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7830,13 +7845,13 @@
         </is>
       </c>
       <c r="G125">
-        <v>1850.0</v>
+        <v>300.0</v>
       </c>
       <c r="H125">
         <v>0.0</v>
       </c>
       <c r="I125">
-        <v>1850.0</v>
+        <v>300.0</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -7844,19 +7859,24 @@
         </is>
       </c>
       <c r="K125">
-        <v>80795.0</v>
+        <v>78930.0</v>
       </c>
       <c r="L125">
         <v>44310.49</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>AUT-20260504-124</t>
+          <t>BI-5143727</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/05/2026 (Playeras Gabriel Ruíz)</t>
         </is>
       </c>
     </row>
@@ -7878,12 +7898,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cobro anticipo 2/6 inscripcion Giulia Fiorini 2026</t>
+          <t>Cobro mensualidad Giulia Fiorini</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7892,13 +7912,13 @@
         </is>
       </c>
       <c r="G126">
-        <v>308.0</v>
+        <v>1850.0</v>
       </c>
       <c r="H126">
         <v>0.0</v>
       </c>
       <c r="I126">
-        <v>308.0</v>
+        <v>1850.0</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -7906,19 +7926,24 @@
         </is>
       </c>
       <c r="K126">
-        <v>81103.0</v>
+        <v>80780.0</v>
       </c>
       <c r="L126">
         <v>44310.49</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>AUT-20260504-125</t>
+          <t>BI-191776-A</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Parte de ACH Dilson Gerardo Fiori Q2,158.00</t>
         </is>
       </c>
     </row>
@@ -7940,27 +7965,27 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Pago Google Workspace_altus US</t>
+          <t>Cobro anticipo 2/6 inscripcion Giulia Fiorini 2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G127">
-        <v>235.57</v>
+        <v>308.0</v>
       </c>
       <c r="H127">
-        <v>25.24</v>
+        <v>0.0</v>
       </c>
       <c r="I127">
-        <v>210.33</v>
+        <v>308.0</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -7968,19 +7993,24 @@
         </is>
       </c>
       <c r="K127">
-        <v>80867.43</v>
+        <v>81088.0</v>
       </c>
       <c r="L127">
         <v>44310.49</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>AUT-20260504-126</t>
+          <t>BI-191776-B</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Parte de ACH Dilson Gerardo Fiori Q2,158.00</t>
         </is>
       </c>
     </row>
@@ -7992,7 +8022,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8002,27 +8032,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Cobro mensualidad  mayo Andrei González</t>
+          <t>Pago Google Workspace_altus US</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G128">
-        <v>3800.0</v>
+        <v>235.57</v>
       </c>
       <c r="H128">
-        <v>0.0</v>
+        <v>25.24</v>
       </c>
       <c r="I128">
-        <v>3800.0</v>
+        <v>210.33</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -8030,19 +8060,24 @@
         </is>
       </c>
       <c r="K128">
-        <v>84667.43</v>
+        <v>80852.43</v>
       </c>
       <c r="L128">
         <v>44310.49</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>AUT-20260505-127</t>
+          <t>BI-193922</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8089,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8064,7 +8099,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Cobro mensualidad mayo  Mateo Toribio</t>
+          <t>Cobro mensualidad  mayo Andrei González</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8078,13 +8113,13 @@
         </is>
       </c>
       <c r="G129">
-        <v>9300.0</v>
+        <v>3800.0</v>
       </c>
       <c r="H129">
         <v>0.0</v>
       </c>
       <c r="I129">
-        <v>9300.0</v>
+        <v>3800.0</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -8092,19 +8127,24 @@
         </is>
       </c>
       <c r="K129">
-        <v>93967.43</v>
+        <v>84652.43</v>
       </c>
       <c r="L129">
         <v>44310.49</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>AUT-20260506-128</t>
+          <t>BI-4248733</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8166,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cobro mensualidad mayo Luís Felipe Guzmán</t>
+          <t>Cobro mensualidad mayo  Mateo Toribio</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8154,19 +8194,24 @@
         </is>
       </c>
       <c r="K130">
-        <v>103267.43</v>
+        <v>93952.43</v>
       </c>
       <c r="L130">
         <v>44310.49</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>AUT-20260506-129</t>
+          <t>BI-5186041</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/05/2026</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8223,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8188,7 +8233,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Cobro mensualidad mayo Adriana García</t>
+          <t>Cobro mensualidad mayo Luís Felipe Guzmán</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8216,19 +8261,24 @@
         </is>
       </c>
       <c r="K131">
-        <v>112567.43</v>
+        <v>103252.43</v>
       </c>
       <c r="L131">
         <v>44310.49</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>AUT-20260505-130</t>
+          <t>BI-5219578</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/05/2026 (Pamela Sosa / Luís Felipe)</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8300,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Cobro playera polo Adriana García</t>
+          <t>Cobro mensualidad mayo Adriana García</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>4201 - Venta de Libros y Uniformes</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8264,13 +8314,13 @@
         </is>
       </c>
       <c r="G132">
-        <v>100.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H132">
         <v>0.0</v>
       </c>
       <c r="I132">
-        <v>100.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -8278,19 +8328,24 @@
         </is>
       </c>
       <c r="K132">
-        <v>112667.43</v>
+        <v>112552.43</v>
       </c>
       <c r="L132">
         <v>44310.49</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>AUT-20260505-131</t>
+          <t>BI-5136775</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/05/2026</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8357,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8312,27 +8367,27 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Pago anticipo 1/2 Papelería maestra Glendy</t>
+          <t>Cobro playera polo Adriana García</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4201 - Venta de Libros y Uniformes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G133">
-        <v>1000.0</v>
+        <v>100.0</v>
       </c>
       <c r="H133">
-        <v>107.14</v>
+        <v>0.0</v>
       </c>
       <c r="I133">
-        <v>892.86</v>
+        <v>100.0</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -8340,19 +8395,24 @@
         </is>
       </c>
       <c r="K133">
-        <v>111667.43</v>
+        <v>112652.43</v>
       </c>
       <c r="L133">
         <v>44310.49</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>AUT-20260508-132</t>
+          <t>BI-5162566</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 05/05/2026</t>
         </is>
       </c>
     </row>
@@ -8374,42 +8434,42 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Pago IGGS patronal con cuenta de provisiones</t>
+          <t>Pago anticipo 1/2 Papelería maestra Glendy</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2103 - IGSS por Pagar</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pago Reserva Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G134">
-        <v>13662.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H134">
-        <v>0.0</v>
+        <v>107.14</v>
       </c>
       <c r="I134">
-        <v>13662.0</v>
+        <v>892.86</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>BI-Ahorro</t>
+          <t>BI- Monetaria</t>
         </is>
       </c>
       <c r="K134">
-        <v>111667.43</v>
+        <v>111652.43</v>
       </c>
       <c r="L134">
-        <v>30648.49</v>
+        <v>44310.49</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>AUT-20260508-133</t>
+          <t>BI-8179307</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -8419,7 +8479,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Pagado desde BI-Ahorro (Liquida pasivo 2103 IGSS)</t>
+          <t>Conciliado con extracto BI 08/05/2026</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8491,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8441,47 +8501,52 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Cobro mensualidad mayo Rodrigo Gallinsa</t>
+          <t>Pago IGGS patronal con cuenta de provisiones</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>2103 - IGSS por Pagar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Pago Reserva Ahorro</t>
         </is>
       </c>
       <c r="G135">
-        <v>6300.0</v>
+        <v>13662.0</v>
       </c>
       <c r="H135">
         <v>0.0</v>
       </c>
       <c r="I135">
-        <v>6300.0</v>
+        <v>13662.0</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>BI- Monetaria</t>
+          <t>BI-Ahorro</t>
         </is>
       </c>
       <c r="K135">
-        <v>117967.43</v>
+        <v>111652.43</v>
       </c>
       <c r="L135">
         <v>30648.49</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>AUT-20260509-134</t>
+          <t>AHO-IGSS-EneMar</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Pagado desde BI-Ahorro (Liquida pasivo 2103 IGSS)</t>
         </is>
       </c>
     </row>
@@ -8503,12 +8568,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Cobro actividades día de la madre abuelas</t>
+          <t>Cobro mensualidad mayo Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>4200 - Ingresos Comerciales (Afectos)</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8517,13 +8582,13 @@
         </is>
       </c>
       <c r="G136">
-        <v>300.0</v>
+        <v>6300.0</v>
       </c>
       <c r="H136">
         <v>0.0</v>
       </c>
       <c r="I136">
-        <v>300.0</v>
+        <v>6300.0</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -8531,19 +8596,24 @@
         </is>
       </c>
       <c r="K136">
-        <v>118267.43</v>
+        <v>117952.43</v>
       </c>
       <c r="L136">
         <v>30648.49</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>AUT-20260509-135</t>
+          <t>BI-9157844</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 09/05/2026 (Docto 9157844 Q6,300)</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8625,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8565,27 +8635,27 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Pago 2/2 Actividad día de la madre</t>
+          <t>Cobro actividades día de la madre abuelas</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4200 - Ingresos Comerciales (Afectos)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G137">
-        <v>750.0</v>
+        <v>300.0</v>
       </c>
       <c r="H137">
-        <v>80.36</v>
+        <v>0.0</v>
       </c>
       <c r="I137">
-        <v>669.64</v>
+        <v>300.0</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -8593,19 +8663,24 @@
         </is>
       </c>
       <c r="K137">
-        <v>117517.43</v>
+        <v>118252.43</v>
       </c>
       <c r="L137">
         <v>30648.49</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>AUT-20260512-136</t>
+          <t>BI-8119072</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 08/05/2026</t>
         </is>
       </c>
     </row>
@@ -8627,27 +8702,27 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Cobro anticipo 1/2 mensualidad mayo Günther Márquez</t>
+          <t>Pago 2/2 Actividad día de la madre</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G138">
-        <v>2758.33</v>
+        <v>750.0</v>
       </c>
       <c r="H138">
-        <v>0.0</v>
+        <v>80.36</v>
       </c>
       <c r="I138">
-        <v>2758.33</v>
+        <v>669.64</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -8655,19 +8730,24 @@
         </is>
       </c>
       <c r="K138">
-        <v>120275.76</v>
+        <v>117502.43</v>
       </c>
       <c r="L138">
         <v>30648.49</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>AUT-20260512-137</t>
+          <t>BI-12199600</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 12/05/2026</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8759,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8689,27 +8769,27 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Pago ISR Empleados</t>
+          <t>Cobro anticipo 1/2 mensualidad mayo Günther Márquez</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2105 - ISR Retenciones por Pagar</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G139">
-        <v>375.85</v>
+        <v>2758.33</v>
       </c>
       <c r="H139">
         <v>0.0</v>
       </c>
       <c r="I139">
-        <v>375.85</v>
+        <v>2758.33</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -8717,24 +8797,24 @@
         </is>
       </c>
       <c r="K139">
-        <v>119899.91</v>
+        <v>120260.76</v>
       </c>
       <c r="L139">
         <v>30648.49</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>AUT-20260513-138</t>
+          <t>BI-198254</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Reclasificado a 2105 ISR Retenciones por Pagar</t>
+          <t>Conciliado con extracto BI 12/05/2026</t>
         </is>
       </c>
     </row>
@@ -8756,12 +8836,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Pago seguro escolar Giulia Fiorini</t>
+          <t>Pago ISR Empleados</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2101 - Proveedores Locales</t>
+          <t>2105 - ISR Retenciones por Pagar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8770,13 +8850,13 @@
         </is>
       </c>
       <c r="G140">
-        <v>147.0</v>
+        <v>375.85</v>
       </c>
       <c r="H140">
-        <v>15.75</v>
+        <v>0.0</v>
       </c>
       <c r="I140">
-        <v>131.25</v>
+        <v>375.85</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -8784,19 +8864,24 @@
         </is>
       </c>
       <c r="K140">
-        <v>119752.91</v>
+        <v>119884.91</v>
       </c>
       <c r="L140">
         <v>30648.49</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>AUT-20260513-139</t>
+          <t>BI-13117655</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 13/05/2026</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8893,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8818,27 +8903,27 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Recibo de dondación 1/2 para mobiliario</t>
+          <t>Pago seguro escolar Giulia Fiorini</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>4203 - Donaciones recibidas</t>
+          <t>2101 - Proveedores Locales</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G141">
-        <v>12960.0</v>
+        <v>147.0</v>
       </c>
       <c r="H141">
-        <v>0.0</v>
+        <v>15.75</v>
       </c>
       <c r="I141">
-        <v>12960.0</v>
+        <v>131.25</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -8846,19 +8931,24 @@
         </is>
       </c>
       <c r="K141">
-        <v>132712.91</v>
+        <v>119737.91</v>
       </c>
       <c r="L141">
         <v>30648.49</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>AUT-20260514-140</t>
+          <t>BI-13254307</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 13/05/2026</t>
         </is>
       </c>
     </row>
@@ -8870,7 +8960,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8880,27 +8970,27 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Pago factura Mobiliario ALTUS</t>
+          <t>Recibo de dondación 1/2 para mobiliario</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1501 - Mobiliario y Equipo</t>
+          <t>4203 - Donaciones recibidas</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G142">
-        <v>25285.0</v>
+        <v>12960.0</v>
       </c>
       <c r="H142">
-        <v>2709.11</v>
+        <v>0.0</v>
       </c>
       <c r="I142">
-        <v>22575.89</v>
+        <v>12960.0</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -8908,19 +8998,24 @@
         </is>
       </c>
       <c r="K142">
-        <v>107427.91</v>
+        <v>132697.91</v>
       </c>
       <c r="L142">
         <v>30648.49</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>AUT-20260515-141</t>
+          <t>BI-224523</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 14/05/2026 (ACH Fredy Roberto Bolaños)</t>
         </is>
       </c>
     </row>
@@ -8942,27 +9037,27 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Constancia Exención de IVA</t>
+          <t>Pago factura Mobiliario ALTUS</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1106 - Exención de IVA</t>
+          <t>1501 - Mobiliario y Equipo</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G143">
+        <v>25285.0</v>
+      </c>
+      <c r="H143">
         <v>2709.11</v>
       </c>
-      <c r="H143">
-        <v>0.0</v>
-      </c>
       <c r="I143">
-        <v>2709.11</v>
+        <v>22575.89</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -8970,19 +9065,24 @@
         </is>
       </c>
       <c r="K143">
-        <v>110137.02</v>
+        <v>107412.91</v>
       </c>
       <c r="L143">
         <v>30648.49</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>AUT-20260515-142</t>
+          <t>BI-146070-F</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Factura total Q25,285.00 menos Exención IVA Q2,709.00 = Débito BI-146070 Q22,576.00</t>
         </is>
       </c>
     </row>
@@ -8994,7 +9094,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9004,27 +9104,27 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Anticipo 2/6 inscripción 2026 Rodrigo Gallinsa</t>
+          <t>Constancia Exención de IVA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>1106 - Exención de IVA</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="G144">
-        <v>1287.5</v>
+        <v>2709.0</v>
       </c>
       <c r="H144">
         <v>0.0</v>
       </c>
       <c r="I144">
-        <v>1287.5</v>
+        <v>2709.0</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -9032,19 +9132,24 @@
         </is>
       </c>
       <c r="K144">
-        <v>111424.52</v>
+        <v>110121.91</v>
       </c>
       <c r="L144">
         <v>30648.49</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>AUT-20260518-143</t>
+          <t>BI-146070-EX</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Ajustado de Q2,709.11 a Q2,709.00 para cuadrar exacto con débito bancario BI-146070 (Q22,576.00)</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9161,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9066,52 +9171,52 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Pago cuotas IGGS Abril</t>
+          <t>Anticipo 2/6 inscripción 2026 Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2103 - IGSS por Pagar</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pago Reserva Ahorro</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G145">
-        <v>4554.0</v>
+        <v>1287.5</v>
       </c>
       <c r="H145">
         <v>0.0</v>
       </c>
       <c r="I145">
-        <v>4554.0</v>
+        <v>1287.5</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>BI-Ahorro</t>
+          <t>BI- Monetaria</t>
         </is>
       </c>
       <c r="K145">
-        <v>111424.52</v>
+        <v>111409.41</v>
       </c>
       <c r="L145">
-        <v>26094.49</v>
+        <v>30648.49</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>AUT-20260521-144</t>
+          <t>BI-18150241</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Pagado desde BI-Ahorro (Liquida pasivo 2103 IGSS)</t>
+          <t>Conciliado con extracto BI 18/05/2026</t>
         </is>
       </c>
     </row>
@@ -9133,47 +9238,52 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Provisiones laborales</t>
+          <t>Pago cuotas IGGS Abril</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2102 - Provisiones Laborales</t>
+          <t>2103 - IGSS por Pagar</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Traspaso Ahorro</t>
+          <t>Pago Reserva Ahorro</t>
         </is>
       </c>
       <c r="G146">
-        <v>6596.0</v>
+        <v>4554.0</v>
       </c>
       <c r="H146">
         <v>0.0</v>
       </c>
       <c r="I146">
-        <v>6596.0</v>
+        <v>4554.0</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>BI- Monetaria</t>
+          <t>BI-Ahorro</t>
         </is>
       </c>
       <c r="K146">
-        <v>104828.52</v>
+        <v>111409.41</v>
       </c>
       <c r="L146">
-        <v>32690.49</v>
+        <v>26094.49</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>AUT-20260521-145</t>
+          <t>AHO-IGSS-Abr</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Pagado desde BI-Ahorro (Cuotas IGSS Abril)</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9295,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9195,27 +9305,27 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Pago mes de marzo Lucía Montes</t>
+          <t>Provisiones laborales</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>2102 - Provisiones Laborales</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Traspaso Ahorro</t>
         </is>
       </c>
       <c r="G147">
-        <v>8587.64</v>
+        <v>6596.0</v>
       </c>
       <c r="H147">
         <v>0.0</v>
       </c>
       <c r="I147">
-        <v>8587.64</v>
+        <v>6596.0</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -9223,19 +9333,24 @@
         </is>
       </c>
       <c r="K147">
-        <v>96240.88</v>
+        <v>104813.41</v>
       </c>
       <c r="L147">
         <v>32690.49</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>AUT-20260527-146</t>
+          <t>BI-21106875</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 21/05/2026</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9372,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Pago mes de marzo Jessica Gudiel</t>
+          <t>Pago mes de marzo Lucía Montes</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9271,13 +9386,13 @@
         </is>
       </c>
       <c r="G148">
-        <v>5862.19</v>
+        <v>8587.64</v>
       </c>
       <c r="H148">
         <v>0.0</v>
       </c>
       <c r="I148">
-        <v>5862.19</v>
+        <v>8587.64</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -9285,19 +9400,24 @@
         </is>
       </c>
       <c r="K148">
-        <v>90378.69</v>
+        <v>96225.77</v>
       </c>
       <c r="L148">
         <v>32690.49</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>AUT-20260527-147</t>
+          <t>BI-27168396-A</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Parte de Docto 27168396 (Q8,587.64 sueldo + Q285.00 celular = Q8,872.64)</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9439,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Pago mes de marzo Geovanna Velázquez</t>
+          <t>Pago mes de marzo Jessica Gudiel</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9333,13 +9453,13 @@
         </is>
       </c>
       <c r="G149">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="H149">
         <v>0.0</v>
       </c>
       <c r="I149">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -9347,19 +9467,24 @@
         </is>
       </c>
       <c r="K149">
-        <v>86143.91</v>
+        <v>90363.58</v>
       </c>
       <c r="L149">
         <v>32690.49</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>AUT-20260527-148</t>
+          <t>BI-192760</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/05/2026</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9506,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Pago mes de marzo Suly Sajbochol</t>
+          <t>Pago mes de marzo Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9409,19 +9534,24 @@
         </is>
       </c>
       <c r="K150">
-        <v>81909.13</v>
+        <v>86128.8</v>
       </c>
       <c r="L150">
         <v>32690.49</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>AUT-20260527-149</t>
+          <t>BI-162323</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/05/2026</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9573,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Pago mes de marzo Melissa Peña</t>
+          <t>Pago mes de marzo Suly Sajbochol</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9471,19 +9601,24 @@
         </is>
       </c>
       <c r="K151">
-        <v>77674.35</v>
+        <v>81894.02</v>
       </c>
       <c r="L151">
         <v>32690.49</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>AUT-20260527-150</t>
+          <t>BI-186296</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/05/2026</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9640,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Donación Fundación Waybi</t>
+          <t>Pago mes de marzo Melissa Peña</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>5208 - Donaciones</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9519,13 +9654,13 @@
         </is>
       </c>
       <c r="G152">
-        <v>1930.0</v>
+        <v>4234.78</v>
       </c>
       <c r="H152">
-        <v>206.79</v>
+        <v>0.0</v>
       </c>
       <c r="I152">
-        <v>1723.21</v>
+        <v>4234.78</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -9533,19 +9668,24 @@
         </is>
       </c>
       <c r="K152">
-        <v>75744.35</v>
+        <v>77659.24</v>
       </c>
       <c r="L152">
         <v>32690.49</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>AUT-20260527-151</t>
+          <t>BI-200393</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/05/2026</t>
         </is>
       </c>
     </row>
@@ -9567,12 +9707,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Pago celular ALTUS</t>
+          <t>Donación Fundación Waybi</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>5208 - Donaciones</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9581,13 +9721,13 @@
         </is>
       </c>
       <c r="G153">
-        <v>285.0</v>
+        <v>1930.0</v>
       </c>
       <c r="H153">
-        <v>30.54</v>
+        <v>206.79</v>
       </c>
       <c r="I153">
-        <v>254.46</v>
+        <v>1723.21</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -9595,19 +9735,24 @@
         </is>
       </c>
       <c r="K153">
-        <v>75459.35</v>
+        <v>75729.24</v>
       </c>
       <c r="L153">
         <v>32690.49</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>AUT-20260527-152</t>
+          <t>BI-219376</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/05/2026</t>
         </is>
       </c>
     </row>
@@ -9629,12 +9774,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Pago servicio Sergio contador</t>
+          <t>Pago celular ALTUS</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9643,13 +9788,13 @@
         </is>
       </c>
       <c r="G154">
-        <v>350.0</v>
+        <v>285.0</v>
       </c>
       <c r="H154">
-        <v>37.5</v>
+        <v>30.54</v>
       </c>
       <c r="I154">
-        <v>312.5</v>
+        <v>254.46</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -9657,19 +9802,24 @@
         </is>
       </c>
       <c r="K154">
-        <v>75109.35</v>
+        <v>75444.24</v>
       </c>
       <c r="L154">
         <v>32690.49</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>AUT-20260527-153</t>
+          <t>BI-27168396-B</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Parte de Docto 27168396 (Q8,587.64 + Q285.00 = Q8,872.64)</t>
         </is>
       </c>
     </row>
@@ -9691,27 +9841,27 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Fondo provisiones laborales</t>
+          <t>Pago servicio Sergio contador</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2102 - Provisiones Laborales</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Traspaso Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G155">
-        <v>11552.0</v>
+        <v>350.0</v>
       </c>
       <c r="H155">
-        <v>0.0</v>
+        <v>37.5</v>
       </c>
       <c r="I155">
-        <v>11552.0</v>
+        <v>312.5</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -9719,19 +9869,24 @@
         </is>
       </c>
       <c r="K155">
-        <v>63557.35</v>
+        <v>75094.24</v>
       </c>
       <c r="L155">
-        <v>44242.49</v>
+        <v>32690.49</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>AUT-20260527-154</t>
+          <t>BI-27198679</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/05/2026</t>
         </is>
       </c>
     </row>
@@ -9753,27 +9908,27 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Pago Nauta Estudio Redes sociales</t>
+          <t>Fondo provisiones laborales</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>2102 - Provisiones Laborales</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Traspaso Ahorro</t>
         </is>
       </c>
       <c r="G156">
-        <v>1600.0</v>
+        <v>11552.0</v>
       </c>
       <c r="H156">
-        <v>171.43</v>
+        <v>0.0</v>
       </c>
       <c r="I156">
-        <v>1428.57</v>
+        <v>11552.0</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -9781,19 +9936,24 @@
         </is>
       </c>
       <c r="K156">
-        <v>61957.35</v>
+        <v>63542.24</v>
       </c>
       <c r="L156">
         <v>44242.49</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>AUT-20260527-155</t>
+          <t>BI-27202924</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/05/2026</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9975,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Pago Lourdes Escribá</t>
+          <t>Pago Nauta Estudio Redes sociales</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9829,13 +9989,13 @@
         </is>
       </c>
       <c r="G157">
-        <v>1454.0</v>
+        <v>1600.0</v>
       </c>
       <c r="H157">
-        <v>155.79</v>
+        <v>171.43</v>
       </c>
       <c r="I157">
-        <v>1298.21</v>
+        <v>1428.57</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -9843,19 +10003,24 @@
         </is>
       </c>
       <c r="K157">
-        <v>60503.35</v>
+        <v>61942.24</v>
       </c>
       <c r="L157">
         <v>44242.49</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>AUT-20260527-156</t>
+          <t>BI-28212780</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 28/05/2026</t>
         </is>
       </c>
     </row>
@@ -9877,12 +10042,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Gastos varios actividad día de la madre</t>
+          <t>Pago Lourdes Escribá</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>5205 - Actividades y excursiones</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -9891,13 +10056,13 @@
         </is>
       </c>
       <c r="G158">
-        <v>642.87</v>
+        <v>1454.0</v>
       </c>
       <c r="H158">
-        <v>68.88</v>
+        <v>155.79</v>
       </c>
       <c r="I158">
-        <v>573.99</v>
+        <v>1298.21</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -9905,19 +10070,24 @@
         </is>
       </c>
       <c r="K158">
-        <v>59860.48</v>
+        <v>60488.24</v>
       </c>
       <c r="L158">
         <v>44242.49</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>AUT-20260527-157</t>
+          <t>BI-27156264</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/05/2026</t>
         </is>
       </c>
     </row>
@@ -9939,12 +10109,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Gasto materiales aula ALTUS</t>
+          <t>Gastos varios actividad día de la madre</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>5203 - Papelería, útiles y suministros</t>
+          <t>5205 - Actividades y excursiones</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -9953,13 +10123,13 @@
         </is>
       </c>
       <c r="G159">
-        <v>210.8</v>
+        <v>642.87</v>
       </c>
       <c r="H159">
-        <v>22.59</v>
+        <v>68.88</v>
       </c>
       <c r="I159">
-        <v>188.21</v>
+        <v>573.99</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -9967,19 +10137,24 @@
         </is>
       </c>
       <c r="K159">
-        <v>59649.68</v>
+        <v>59845.37</v>
       </c>
       <c r="L159">
         <v>44242.49</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>AUT-20260527-158</t>
+          <t>BI-211812</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
           <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Conciliado con extracto BI 27/05/2026</t>
         </is>
       </c>
     </row>
@@ -9991,37 +10166,37 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Cobro mensualidad junio Andrei González</t>
+          <t>Gasto materiales aula ALTUS</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5203 - Papelería, útiles y suministros</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G160">
-        <v>3800.0</v>
+        <v>210.8</v>
       </c>
       <c r="H160">
-        <v>0.0</v>
+        <v>22.59</v>
       </c>
       <c r="I160">
-        <v>3800.0</v>
+        <v>188.21</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -10029,24 +10204,24 @@
         </is>
       </c>
       <c r="K160">
-        <v>63449.68</v>
+        <v>59634.57</v>
       </c>
       <c r="L160">
         <v>44242.49</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>BI-1104767</t>
+          <t>BI-224327</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 01/06/2026</t>
+          <t>Conciliado con extracto BI 29/05/2026</t>
         </is>
       </c>
     </row>
@@ -10068,27 +10243,27 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Débito BiCheque comisión manejo de cuenta junio</t>
+          <t>Cobro mensualidad junio Andrei González</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>5210 - Impuestos, tasas y arbitrios</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G161">
-        <v>15.0</v>
+        <v>3800.0</v>
       </c>
       <c r="H161">
         <v>0.0</v>
       </c>
       <c r="I161">
-        <v>15.0</v>
+        <v>3800.0</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -10096,24 +10271,24 @@
         </is>
       </c>
       <c r="K161">
-        <v>63434.68</v>
+        <v>63434.57</v>
       </c>
       <c r="L161">
         <v>44242.49</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>BI-310125</t>
+          <t>BI-1104767</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Agregado según extracto BI 01/06/2026 (DEBITO BICHEQUE)</t>
+          <t>Conciliado con extracto BI 01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10135,12 +10310,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Pago final 2/2 Papelería maestra Glendy</t>
+          <t>Débito BiCheque comisión manejo de cuenta junio</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10149,13 +10324,13 @@
         </is>
       </c>
       <c r="G162">
-        <v>1000.0</v>
+        <v>15.0</v>
       </c>
       <c r="H162">
-        <v>107.14</v>
+        <v>0.0</v>
       </c>
       <c r="I162">
-        <v>892.86</v>
+        <v>15.0</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -10163,14 +10338,14 @@
         </is>
       </c>
       <c r="K162">
-        <v>62434.68</v>
+        <v>63419.57</v>
       </c>
       <c r="L162">
         <v>44242.49</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>BI-1223575</t>
+          <t>BI-310125</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -10180,7 +10355,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 01/06/2026</t>
+          <t>Agregado según extracto BI 01/06/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10367,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10202,27 +10377,27 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Cobro restante 2/2 mensualidad mayo Günther Márquez</t>
+          <t>Pago final 2/2 Papelería maestra Glendy</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G163">
-        <v>1042.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H163">
-        <v>0.0</v>
+        <v>107.14</v>
       </c>
       <c r="I163">
-        <v>1042.0</v>
+        <v>892.86</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -10230,24 +10405,24 @@
         </is>
       </c>
       <c r="K163">
-        <v>63476.68</v>
+        <v>62419.57</v>
       </c>
       <c r="L163">
         <v>44242.49</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>BI-158655-A</t>
+          <t>BI-1223575</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Parte de transferencia ACH Valeria Márquez Q2,758.33</t>
+          <t>Conciliado con extracto BI 01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10269,12 +10444,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Cobro anticipo 5/6 inscripción Günther Márquez</t>
+          <t>Cobro restante 2/2 mensualidad mayo Günther Márquez</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -10283,13 +10458,13 @@
         </is>
       </c>
       <c r="G164">
-        <v>1716.33</v>
+        <v>1042.0</v>
       </c>
       <c r="H164">
         <v>0.0</v>
       </c>
       <c r="I164">
-        <v>1716.33</v>
+        <v>1042.0</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -10297,14 +10472,14 @@
         </is>
       </c>
       <c r="K164">
-        <v>65193.01</v>
+        <v>63461.57</v>
       </c>
       <c r="L164">
         <v>44242.49</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>BI-158655-B</t>
+          <t>BI-158655-A</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -10314,7 +10489,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Ajustado de Q1,716.66 a Q1,716.33 para cuadrar exacto con ACH BI-158655 (Q2,758.33)</t>
+          <t>Parte de transferencia ACH Valeria Márquez Q2,758.33</t>
         </is>
       </c>
     </row>
@@ -10336,12 +10511,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Cobro mensualidad junio Adriana García</t>
+          <t>Cobro anticipo 5/6 inscripción Günther Márquez</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10350,13 +10525,13 @@
         </is>
       </c>
       <c r="G165">
-        <v>9300.0</v>
+        <v>1716.33</v>
       </c>
       <c r="H165">
         <v>0.0</v>
       </c>
       <c r="I165">
-        <v>9300.0</v>
+        <v>1716.33</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -10364,14 +10539,14 @@
         </is>
       </c>
       <c r="K165">
-        <v>74493.01</v>
+        <v>65177.9</v>
       </c>
       <c r="L165">
         <v>44242.49</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>BI-2156954</t>
+          <t>BI-158655-B</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -10381,7 +10556,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 02/06/2026</t>
+          <t>Ajustado de Q1,716.66 a Q1,716.33 para cuadrar exacto con ACH BI-158655 (Q2,758.33)</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10578,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Cobro mensualidad junio Gabriel Ruíz</t>
+          <t>Cobro mensualidad junio Adriana García</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10431,14 +10606,14 @@
         </is>
       </c>
       <c r="K166">
-        <v>83793.01</v>
+        <v>74477.9</v>
       </c>
       <c r="L166">
         <v>44242.49</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>BI-2206079</t>
+          <t>BI-2156954</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -10460,7 +10635,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10470,27 +10645,27 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Google Workspace_altus US</t>
+          <t>Cobro mensualidad junio Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G167">
-        <v>234.66</v>
+        <v>9300.0</v>
       </c>
       <c r="H167">
-        <v>25.14</v>
+        <v>0.0</v>
       </c>
       <c r="I167">
-        <v>209.52</v>
+        <v>9300.0</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -10498,24 +10673,24 @@
         </is>
       </c>
       <c r="K167">
-        <v>83558.35</v>
+        <v>83777.9</v>
       </c>
       <c r="L167">
         <v>44242.49</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>BI-104119</t>
+          <t>BI-2206079</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 03/06/2026</t>
+          <t>Conciliado con extracto BI 02/06/2026</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10702,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10537,27 +10712,27 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Cobro mensualidad junio Giulia Fiorini</t>
+          <t>Google Workspace_altus US</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G168">
-        <v>1850.0</v>
+        <v>234.66</v>
       </c>
       <c r="H168">
-        <v>0.0</v>
+        <v>25.14</v>
       </c>
       <c r="I168">
-        <v>1850.0</v>
+        <v>209.52</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -10565,24 +10740,24 @@
         </is>
       </c>
       <c r="K168">
-        <v>85408.35</v>
+        <v>83543.24</v>
       </c>
       <c r="L168">
         <v>44242.49</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>BI-217487-A</t>
+          <t>BI-104119</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Parte de ACH Dilson Gerardo Fiori Q2,158.68</t>
+          <t>Conciliado con extracto BI 03/06/2026</t>
         </is>
       </c>
     </row>
@@ -10604,12 +10779,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Cobro anticipo 3/6 inscripción Giulia Fiorini 2026</t>
+          <t>Cobro mensualidad junio Giulia Fiorini</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -10618,13 +10793,13 @@
         </is>
       </c>
       <c r="G169">
-        <v>308.68</v>
+        <v>1850.0</v>
       </c>
       <c r="H169">
         <v>0.0</v>
       </c>
       <c r="I169">
-        <v>308.68</v>
+        <v>1850.0</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -10632,14 +10807,14 @@
         </is>
       </c>
       <c r="K169">
-        <v>85717.03</v>
+        <v>85393.24</v>
       </c>
       <c r="L169">
         <v>44242.49</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>BI-217487-B</t>
+          <t>BI-217487-A</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -10661,7 +10836,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10671,12 +10846,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Cobro mensualidad junio Mateo Toribio</t>
+          <t>Cobro anticipo 3/6 inscripción Giulia Fiorini 2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10685,13 +10860,13 @@
         </is>
       </c>
       <c r="G170">
-        <v>9300.0</v>
+        <v>308.68</v>
       </c>
       <c r="H170">
         <v>0.0</v>
       </c>
       <c r="I170">
-        <v>9300.0</v>
+        <v>308.68</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -10699,14 +10874,14 @@
         </is>
       </c>
       <c r="K170">
-        <v>95017.03</v>
+        <v>85701.92</v>
       </c>
       <c r="L170">
         <v>44242.49</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>BI-5111079</t>
+          <t>BI-217487-B</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -10716,7 +10891,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 05/06/2026</t>
+          <t>Parte de ACH Dilson Gerardo Fiori Q2,158.68</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10913,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Cobro mensualidad junio Luís Felipe Guzmán (Pamela Sosa)</t>
+          <t>Cobro mensualidad junio Mateo Toribio</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10766,14 +10941,14 @@
         </is>
       </c>
       <c r="K171">
-        <v>104317.03</v>
+        <v>95001.92</v>
       </c>
       <c r="L171">
         <v>44242.49</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>BI-5187709</t>
+          <t>BI-5111079</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -10795,7 +10970,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10805,7 +10980,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Cobro mensualidad junio Rodrigo Gallinsa</t>
+          <t>Cobro mensualidad junio Luís Felipe Guzmán (Pamela Sosa)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10819,13 +10994,13 @@
         </is>
       </c>
       <c r="G172">
-        <v>6300.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H172">
         <v>0.0</v>
       </c>
       <c r="I172">
-        <v>6300.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -10833,14 +11008,14 @@
         </is>
       </c>
       <c r="K172">
-        <v>110617.03</v>
+        <v>104301.92</v>
       </c>
       <c r="L172">
         <v>44242.49</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>BI-18142150</t>
+          <t>BI-5187709</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -10850,7 +11025,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 18/06/2026</t>
+          <t>Conciliado con extracto BI 05/06/2026</t>
         </is>
       </c>
     </row>
@@ -10872,12 +11047,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Anticipo 3/6 inscripción 2026 Rodrigo Gallinsa</t>
+          <t>Cobro mensualidad junio Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10886,13 +11061,13 @@
         </is>
       </c>
       <c r="G173">
-        <v>1287.5</v>
+        <v>6300.0</v>
       </c>
       <c r="H173">
         <v>0.0</v>
       </c>
       <c r="I173">
-        <v>1287.5</v>
+        <v>6300.0</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -10900,14 +11075,14 @@
         </is>
       </c>
       <c r="K173">
-        <v>111904.53</v>
+        <v>110601.92</v>
       </c>
       <c r="L173">
         <v>44242.49</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>BI-18177865</t>
+          <t>BI-18142150</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -10929,7 +11104,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10939,27 +11114,27 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Pago documentos MINEDUC abogado Samuel Sosa</t>
+          <t>Anticipo 3/6 inscripción 2026 Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G174">
-        <v>250.0</v>
+        <v>1287.5</v>
       </c>
       <c r="H174">
-        <v>26.79</v>
+        <v>0.0</v>
       </c>
       <c r="I174">
-        <v>223.21</v>
+        <v>1287.5</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -10967,24 +11142,24 @@
         </is>
       </c>
       <c r="K174">
-        <v>111654.53</v>
+        <v>111889.42</v>
       </c>
       <c r="L174">
         <v>44242.49</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>BI-25243854</t>
+          <t>BI-18177865</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 25/06/2026 (Nota: Se eliminó duplicado de Q895 Regalo Maestras que corresponde al 10/07/2026)</t>
+          <t>Conciliado con extracto BI 18/06/2026</t>
         </is>
       </c>
     </row>
@@ -10996,7 +11171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11006,12 +11181,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Pago compras actividad Día del Padre Altus (Adri)</t>
+          <t>Pago documentos MINEDUC abogado Samuel Sosa</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>5205 - Actividades y excursiones</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -11020,13 +11195,13 @@
         </is>
       </c>
       <c r="G175">
-        <v>1210.0</v>
+        <v>250.0</v>
       </c>
       <c r="H175">
-        <v>129.64</v>
+        <v>26.79</v>
       </c>
       <c r="I175">
-        <v>1080.36</v>
+        <v>223.21</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -11034,14 +11209,14 @@
         </is>
       </c>
       <c r="K175">
-        <v>110444.53</v>
+        <v>111639.42</v>
       </c>
       <c r="L175">
         <v>44242.49</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>BI-178967</t>
+          <t>BI-25243854</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -11051,7 +11226,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Separado según extracto BI 26/06/2026 (Docto 178967)</t>
+          <t>Conciliado con extracto BI 25/06/2026 (Nota: Se eliminó duplicado de Q895 Regalo Maestras que corresponde al 10/07/2026)</t>
         </is>
       </c>
     </row>
@@ -11073,12 +11248,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Pago Bono 14 AJ (Desde cuenta operativa)</t>
+          <t>Pago compras actividad Día del Padre Altus (Adri)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>5104 - Bono 14</t>
+          <t>5205 - Actividades y excursiones</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -11087,13 +11262,13 @@
         </is>
       </c>
       <c r="G176">
-        <v>2000.0</v>
+        <v>1210.0</v>
       </c>
       <c r="H176">
-        <v>0.0</v>
+        <v>129.64</v>
       </c>
       <c r="I176">
-        <v>2000.0</v>
+        <v>1080.36</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -11101,14 +11276,14 @@
         </is>
       </c>
       <c r="K176">
-        <v>108444.53</v>
+        <v>110429.42</v>
       </c>
       <c r="L176">
         <v>44242.49</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>BI-200685</t>
+          <t>BI-178967</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -11118,7 +11293,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Separado según extracto BI 26/06/2026 (Docto 200685: 5104 bono 14 AJ)</t>
+          <t>Separado según extracto BI 26/06/2026 (Docto 178967)</t>
         </is>
       </c>
     </row>
@@ -11140,12 +11315,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Pago sueldo junio Geovanna Velázquez</t>
+          <t>Pago Bono 14 AJ (Desde cuenta operativa)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5104 - Bono 14</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -11154,13 +11329,13 @@
         </is>
       </c>
       <c r="G177">
-        <v>4237.78</v>
+        <v>2000.0</v>
       </c>
       <c r="H177">
         <v>0.0</v>
       </c>
       <c r="I177">
-        <v>4237.78</v>
+        <v>2000.0</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -11168,14 +11343,14 @@
         </is>
       </c>
       <c r="K177">
-        <v>104206.75</v>
+        <v>108429.42</v>
       </c>
       <c r="L177">
         <v>44242.49</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>BI-118012</t>
+          <t>BI-200685</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -11185,7 +11360,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 26/06/2026</t>
+          <t>Separado según extracto BI 26/06/2026 (Docto 200685: 5104 bono 14 AJ)</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11382,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Pago sueldo junio Melissa Peña</t>
+          <t>Pago sueldo junio Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11221,13 +11396,13 @@
         </is>
       </c>
       <c r="G178">
-        <v>4234.78</v>
+        <v>4237.78</v>
       </c>
       <c r="H178">
         <v>0.0</v>
       </c>
       <c r="I178">
-        <v>4234.78</v>
+        <v>4237.78</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -11235,14 +11410,14 @@
         </is>
       </c>
       <c r="K178">
-        <v>99971.97</v>
+        <v>104191.64</v>
       </c>
       <c r="L178">
         <v>44242.49</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>BI-138311</t>
+          <t>BI-118012</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -11274,12 +11449,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Pago publicidad RRSS Raúl</t>
+          <t>Pago sueldo junio Melissa Peña</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11288,13 +11463,13 @@
         </is>
       </c>
       <c r="G179">
-        <v>500.0</v>
+        <v>4234.78</v>
       </c>
       <c r="H179">
-        <v>53.57</v>
+        <v>0.0</v>
       </c>
       <c r="I179">
-        <v>446.43</v>
+        <v>4234.78</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -11302,14 +11477,14 @@
         </is>
       </c>
       <c r="K179">
-        <v>99471.97</v>
+        <v>99956.86</v>
       </c>
       <c r="L179">
         <v>44242.49</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>BI-138762</t>
+          <t>BI-138311</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -11341,12 +11516,12 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Donación Fundación Waybi junio</t>
+          <t>Pago publicidad RRSS Raúl</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>5208 - Donaciones</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -11355,13 +11530,13 @@
         </is>
       </c>
       <c r="G180">
-        <v>1700.0</v>
+        <v>500.0</v>
       </c>
       <c r="H180">
-        <v>182.14</v>
+        <v>53.57</v>
       </c>
       <c r="I180">
-        <v>1517.86</v>
+        <v>446.43</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -11369,14 +11544,14 @@
         </is>
       </c>
       <c r="K180">
-        <v>97771.97</v>
+        <v>99456.86</v>
       </c>
       <c r="L180">
         <v>44242.49</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>BI-151470</t>
+          <t>BI-138762</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -11408,12 +11583,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Pago sueldo junio Jessica Gudiel</t>
+          <t>Donación Fundación Waybi junio</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5208 - Donaciones</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -11422,13 +11597,13 @@
         </is>
       </c>
       <c r="G181">
-        <v>5862.19</v>
+        <v>1700.0</v>
       </c>
       <c r="H181">
-        <v>0.0</v>
+        <v>182.14</v>
       </c>
       <c r="I181">
-        <v>5862.19</v>
+        <v>1517.86</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -11436,14 +11611,14 @@
         </is>
       </c>
       <c r="K181">
-        <v>91909.78</v>
+        <v>97756.86</v>
       </c>
       <c r="L181">
         <v>44242.49</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>BI-176604</t>
+          <t>BI-151470</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -11475,7 +11650,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Pago sueldo junio Suly Sajbochol</t>
+          <t>Pago sueldo junio Jessica Gudiel</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11489,13 +11664,13 @@
         </is>
       </c>
       <c r="G182">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="H182">
         <v>0.0</v>
       </c>
       <c r="I182">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -11503,14 +11678,14 @@
         </is>
       </c>
       <c r="K182">
-        <v>87675.0</v>
+        <v>91894.67</v>
       </c>
       <c r="L182">
         <v>44242.49</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>BI-202265</t>
+          <t>BI-176604</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -11542,7 +11717,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Pago sueldo junio Lucía Montes</t>
+          <t>Pago sueldo junio Suly Sajbochol</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11556,13 +11731,13 @@
         </is>
       </c>
       <c r="G183">
-        <v>8574.54</v>
+        <v>4234.78</v>
       </c>
       <c r="H183">
         <v>0.0</v>
       </c>
       <c r="I183">
-        <v>8574.54</v>
+        <v>4234.78</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -11570,14 +11745,14 @@
         </is>
       </c>
       <c r="K183">
-        <v>79100.46</v>
+        <v>87659.89</v>
       </c>
       <c r="L183">
         <v>44242.49</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>BI-26153755</t>
+          <t>BI-202265</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -11609,12 +11784,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Pago celular ALTUS</t>
+          <t>Pago sueldo junio Lucía Montes</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -11623,13 +11798,13 @@
         </is>
       </c>
       <c r="G184">
-        <v>285.0</v>
+        <v>8574.54</v>
       </c>
       <c r="H184">
-        <v>30.54</v>
+        <v>0.0</v>
       </c>
       <c r="I184">
-        <v>254.46</v>
+        <v>8574.54</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -11637,14 +11812,14 @@
         </is>
       </c>
       <c r="K184">
-        <v>78815.46</v>
+        <v>79085.35</v>
       </c>
       <c r="L184">
         <v>44242.49</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>BI-26160770</t>
+          <t>BI-26153755</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -11676,27 +11851,27 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Provisiones laborales (Traslado a BI-Ahorro)</t>
+          <t>Pago celular ALTUS</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2102 - Provisiones Laborales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Traspaso Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G185">
-        <v>11552.0</v>
+        <v>285.0</v>
       </c>
       <c r="H185">
-        <v>0.0</v>
+        <v>30.54</v>
       </c>
       <c r="I185">
-        <v>11552.0</v>
+        <v>254.46</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -11704,14 +11879,14 @@
         </is>
       </c>
       <c r="K185">
-        <v>67263.46</v>
+        <v>78800.35</v>
       </c>
       <c r="L185">
-        <v>55794.49</v>
+        <v>44242.49</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>BI-26177492</t>
+          <t>BI-26160770</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -11743,27 +11918,27 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Pago Nauta Estudio Redes Sociales junio</t>
+          <t>Provisiones laborales (Traslado a BI-Ahorro)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>2102 - Provisiones Laborales</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Traspaso Ahorro</t>
         </is>
       </c>
       <c r="G186">
-        <v>2650.0</v>
+        <v>11552.0</v>
       </c>
       <c r="H186">
-        <v>283.93</v>
+        <v>0.0</v>
       </c>
       <c r="I186">
-        <v>2366.07</v>
+        <v>11552.0</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -11771,14 +11946,14 @@
         </is>
       </c>
       <c r="K186">
-        <v>64613.46</v>
+        <v>67248.35</v>
       </c>
       <c r="L186">
         <v>55794.49</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>BI-26215848</t>
+          <t>BI-26177492</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -11810,42 +11985,42 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Pago Bono 14 Lucía Montes</t>
+          <t>Pago Nauta Estudio Redes Sociales junio</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>5104 - Bono 14</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Pago Reserva Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G187">
-        <v>9000.0</v>
+        <v>2650.0</v>
       </c>
       <c r="H187">
-        <v>0.0</v>
+        <v>283.93</v>
       </c>
       <c r="I187">
-        <v>9000.0</v>
+        <v>2366.07</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>BI-Ahorro</t>
+          <t>BI- Monetaria</t>
         </is>
       </c>
       <c r="K187">
-        <v>64613.46</v>
+        <v>64598.35</v>
       </c>
       <c r="L187">
-        <v>46794.49</v>
+        <v>55794.49</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>AHO-B14-LM</t>
+          <t>BI-26215848</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -11855,7 +12030,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Pagado desde BI-Ahorro (Reserva Laboral)</t>
+          <t>Conciliado con extracto BI 26/06/2026</t>
         </is>
       </c>
     </row>
@@ -11877,7 +12052,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Pago Bono 14 Jessica Gudiel</t>
+          <t>Pago Bono 14 Lucía Montes</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11891,13 +12066,13 @@
         </is>
       </c>
       <c r="G188">
-        <v>6000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="H188">
         <v>0.0</v>
       </c>
       <c r="I188">
-        <v>6000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -11905,14 +12080,14 @@
         </is>
       </c>
       <c r="K188">
-        <v>64613.46</v>
+        <v>64598.35</v>
       </c>
       <c r="L188">
-        <v>40794.49</v>
+        <v>46794.49</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>AHO-B14-JG</t>
+          <t>AHO-B14-LM</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -11944,7 +12119,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Pago Bono 14 Geovanna Velázquez</t>
+          <t>Pago Bono 14 Jessica Gudiel</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11958,13 +12133,13 @@
         </is>
       </c>
       <c r="G189">
-        <v>4200.0</v>
+        <v>6000.0</v>
       </c>
       <c r="H189">
         <v>0.0</v>
       </c>
       <c r="I189">
-        <v>4200.0</v>
+        <v>6000.0</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -11972,14 +12147,14 @@
         </is>
       </c>
       <c r="K189">
-        <v>64613.46</v>
+        <v>64598.35</v>
       </c>
       <c r="L189">
-        <v>36594.49</v>
+        <v>40794.49</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>AHO-B14-GV</t>
+          <t>AHO-B14-JG</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -12011,7 +12186,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Pago Bono 14 Suly Sajbochol</t>
+          <t>Pago Bono 14 Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12039,14 +12214,14 @@
         </is>
       </c>
       <c r="K190">
-        <v>64613.46</v>
+        <v>64598.35</v>
       </c>
       <c r="L190">
-        <v>32394.49</v>
+        <v>36594.49</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>AHO-B14-SJ</t>
+          <t>AHO-B14-GV</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -12078,7 +12253,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Pago Bono 14 Melissa Peña</t>
+          <t>Pago Bono 14 Suly Sajbochol</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12106,14 +12281,14 @@
         </is>
       </c>
       <c r="K191">
-        <v>64613.46</v>
+        <v>64598.35</v>
       </c>
       <c r="L191">
-        <v>28194.49</v>
+        <v>32394.49</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>AHO-B14-MP</t>
+          <t>AHO-B14-SJ</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -12135,7 +12310,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12145,42 +12320,42 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Honorarios arquitecta insumos reparación baño Luisa Estrada</t>
+          <t>Pago Bono 14 Melissa Peña</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5104 - Bono 14</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pago Reserva Ahorro</t>
         </is>
       </c>
       <c r="G192">
-        <v>1053.48</v>
+        <v>4200.0</v>
       </c>
       <c r="H192">
-        <v>112.87</v>
+        <v>0.0</v>
       </c>
       <c r="I192">
-        <v>940.61</v>
+        <v>4200.0</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>BI- Monetaria</t>
+          <t>BI-Ahorro</t>
         </is>
       </c>
       <c r="K192">
-        <v>63559.98</v>
+        <v>64598.35</v>
       </c>
       <c r="L192">
         <v>28194.49</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>BI-27172293</t>
+          <t>AHO-B14-MP</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -12190,7 +12365,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 27/06/2026</t>
+          <t>Pagado desde BI-Ahorro (Reserva Laboral)</t>
         </is>
       </c>
     </row>
@@ -12202,37 +12377,37 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Cobro mensualidad julio Andrei González</t>
+          <t>Honorarios arquitecta insumos reparación baño Luisa Estrada</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G193">
-        <v>3800.0</v>
+        <v>1053.48</v>
       </c>
       <c r="H193">
-        <v>0.0</v>
+        <v>112.87</v>
       </c>
       <c r="I193">
-        <v>3800.0</v>
+        <v>940.61</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -12240,24 +12415,24 @@
         </is>
       </c>
       <c r="K193">
-        <v>67359.98</v>
+        <v>63544.87</v>
       </c>
       <c r="L193">
         <v>28194.49</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>BI-1241287</t>
+          <t>BI-27172293</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 01/07/2026</t>
+          <t>Conciliado con extracto BI 27/06/2026</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12454,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Cobro mensualidad julio Gabriel Ruíz</t>
+          <t>Cobro mensualidad julio Andrei González</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12293,13 +12468,13 @@
         </is>
       </c>
       <c r="G194">
-        <v>9300.0</v>
+        <v>3800.0</v>
       </c>
       <c r="H194">
         <v>0.0</v>
       </c>
       <c r="I194">
-        <v>9300.0</v>
+        <v>3800.0</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -12307,14 +12482,14 @@
         </is>
       </c>
       <c r="K194">
-        <v>76659.98</v>
+        <v>67344.87</v>
       </c>
       <c r="L194">
         <v>28194.49</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>BI-1263713</t>
+          <t>BI-1241287</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -12346,27 +12521,27 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Débito BiCheque comisión manejo de cuenta julio</t>
+          <t>Cobro mensualidad julio Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>5210 - Impuestos, tasas y arbitrios</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G195">
-        <v>15.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H195">
         <v>0.0</v>
       </c>
       <c r="I195">
-        <v>15.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -12374,24 +12549,24 @@
         </is>
       </c>
       <c r="K195">
-        <v>76644.98</v>
+        <v>76644.87</v>
       </c>
       <c r="L195">
         <v>28194.49</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>BI-310320</t>
+          <t>BI-1263713</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Agregado según extracto BI 01/07/2026 (DEBITO BICHEQUE)</t>
+          <t>Conciliado con extracto BI 01/07/2026</t>
         </is>
       </c>
     </row>
@@ -12413,12 +12588,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Pago servicios Lourdes Escribá junio</t>
+          <t>Débito BiCheque comisión manejo de cuenta julio</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -12427,13 +12602,13 @@
         </is>
       </c>
       <c r="G196">
-        <v>1454.0</v>
+        <v>15.0</v>
       </c>
       <c r="H196">
-        <v>155.79</v>
+        <v>0.0</v>
       </c>
       <c r="I196">
-        <v>1298.21</v>
+        <v>15.0</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -12441,14 +12616,14 @@
         </is>
       </c>
       <c r="K196">
-        <v>75190.98</v>
+        <v>76629.87</v>
       </c>
       <c r="L196">
         <v>28194.49</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>BI-1113817</t>
+          <t>BI-310320</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -12458,7 +12633,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 01/07/2026</t>
+          <t>Agregado según extracto BI 01/07/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12655,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Pago honorarios contabilidad Sergio contador</t>
+          <t>Pago servicios Lourdes Escribá junio</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12494,13 +12669,13 @@
         </is>
       </c>
       <c r="G197">
-        <v>350.0</v>
+        <v>1454.0</v>
       </c>
       <c r="H197">
-        <v>37.5</v>
+        <v>155.79</v>
       </c>
       <c r="I197">
-        <v>312.5</v>
+        <v>1298.21</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -12508,14 +12683,14 @@
         </is>
       </c>
       <c r="K197">
-        <v>74840.98</v>
+        <v>75175.87</v>
       </c>
       <c r="L197">
         <v>28194.49</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>BI-1136800</t>
+          <t>BI-1113817</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -12537,7 +12712,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12547,12 +12722,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Google Workspace_altus US</t>
+          <t>Pago honorarios contabilidad Sergio contador</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -12561,13 +12736,13 @@
         </is>
       </c>
       <c r="G198">
-        <v>234.96</v>
+        <v>350.0</v>
       </c>
       <c r="H198">
-        <v>25.17</v>
+        <v>37.5</v>
       </c>
       <c r="I198">
-        <v>209.79</v>
+        <v>312.5</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -12575,14 +12750,14 @@
         </is>
       </c>
       <c r="K198">
-        <v>74606.02</v>
+        <v>74825.87</v>
       </c>
       <c r="L198">
         <v>28194.49</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>BI-99468</t>
+          <t>BI-1136800</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -12592,7 +12767,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 02/07/2026</t>
+          <t>Conciliado con extracto BI 01/07/2026</t>
         </is>
       </c>
     </row>
@@ -12614,12 +12789,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Pago ISR Empleados SAT</t>
+          <t>Google Workspace_altus US</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2105 - ISR Retenciones por Pagar</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -12628,13 +12803,13 @@
         </is>
       </c>
       <c r="G199">
-        <v>375.88</v>
+        <v>234.96</v>
       </c>
       <c r="H199">
-        <v>0.0</v>
+        <v>25.17</v>
       </c>
       <c r="I199">
-        <v>375.88</v>
+        <v>209.79</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -12642,14 +12817,14 @@
         </is>
       </c>
       <c r="K199">
-        <v>74230.14</v>
+        <v>74590.91</v>
       </c>
       <c r="L199">
         <v>28194.49</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>BI-2175006</t>
+          <t>BI-99468</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -12681,12 +12856,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Pago teléfono / celular ALTUS</t>
+          <t>Pago ISR Empleados SAT</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>2105 - ISR Retenciones por Pagar</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -12695,13 +12870,13 @@
         </is>
       </c>
       <c r="G200">
-        <v>285.0</v>
+        <v>375.88</v>
       </c>
       <c r="H200">
-        <v>30.54</v>
+        <v>0.0</v>
       </c>
       <c r="I200">
-        <v>254.46</v>
+        <v>375.88</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -12709,14 +12884,14 @@
         </is>
       </c>
       <c r="K200">
-        <v>73945.14</v>
+        <v>74215.03</v>
       </c>
       <c r="L200">
         <v>28194.49</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>BI-2261205</t>
+          <t>BI-2175006</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -12738,7 +12913,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12748,27 +12923,27 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Cobro mensualidad julio Adriana García</t>
+          <t>Pago teléfono / celular ALTUS</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G201">
-        <v>9300.0</v>
+        <v>285.0</v>
       </c>
       <c r="H201">
-        <v>0.0</v>
+        <v>30.54</v>
       </c>
       <c r="I201">
-        <v>9300.0</v>
+        <v>254.46</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -12776,24 +12951,24 @@
         </is>
       </c>
       <c r="K201">
-        <v>83245.14</v>
+        <v>73930.03</v>
       </c>
       <c r="L201">
         <v>28194.49</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>BI-3126065</t>
+          <t>BI-2261205</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 03/07/2026</t>
+          <t>Conciliado con extracto BI 02/07/2026</t>
         </is>
       </c>
     </row>
@@ -12805,7 +12980,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12815,7 +12990,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Cobro mensualidad julio Luís Felipe Guzmán (Pamela Sosa)</t>
+          <t>Cobro mensualidad julio Adriana García</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12843,14 +13018,14 @@
         </is>
       </c>
       <c r="K202">
-        <v>92545.14</v>
+        <v>83230.03</v>
       </c>
       <c r="L202">
         <v>28194.49</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>BI-5194232</t>
+          <t>BI-3126065</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -12860,7 +13035,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 05/07/2026</t>
+          <t>Conciliado con extracto BI 03/07/2026</t>
         </is>
       </c>
     </row>
@@ -12872,7 +13047,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12882,7 +13057,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Cobro mensualidad julio Giulia Fiorini</t>
+          <t>Cobro mensualidad julio Luís Felipe Guzmán (Pamela Sosa)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12896,13 +13071,13 @@
         </is>
       </c>
       <c r="G203">
-        <v>1850.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H203">
         <v>0.0</v>
       </c>
       <c r="I203">
-        <v>1850.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -12910,14 +13085,14 @@
         </is>
       </c>
       <c r="K203">
-        <v>94395.14</v>
+        <v>92530.03</v>
       </c>
       <c r="L203">
         <v>28194.49</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>BI-145540-A</t>
+          <t>BI-5194232</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -12927,7 +13102,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>Parte de ACH Dilson Gerardo Fiori Q2,158.34</t>
+          <t>Conciliado con extracto BI 05/07/2026</t>
         </is>
       </c>
     </row>
@@ -12949,12 +13124,12 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Cobro anticipo 4/6 inscripción Giulia Fiorini</t>
+          <t>Cobro mensualidad julio Giulia Fiorini</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -12963,13 +13138,13 @@
         </is>
       </c>
       <c r="G204">
-        <v>308.34</v>
+        <v>1850.0</v>
       </c>
       <c r="H204">
         <v>0.0</v>
       </c>
       <c r="I204">
-        <v>308.34</v>
+        <v>1850.0</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -12977,14 +13152,14 @@
         </is>
       </c>
       <c r="K204">
-        <v>94703.48</v>
+        <v>94380.03</v>
       </c>
       <c r="L204">
         <v>28194.49</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>BI-145540-B</t>
+          <t>BI-145540-A</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -13006,7 +13181,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -13016,12 +13191,12 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Cobro anticipo 1/2 mensualidad junio Günther Márquez</t>
+          <t>Cobro anticipo 4/6 inscripción Giulia Fiorini</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -13030,13 +13205,13 @@
         </is>
       </c>
       <c r="G205">
-        <v>2758.33</v>
+        <v>308.34</v>
       </c>
       <c r="H205">
         <v>0.0</v>
       </c>
       <c r="I205">
-        <v>2758.33</v>
+        <v>308.34</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -13044,14 +13219,14 @@
         </is>
       </c>
       <c r="K205">
-        <v>97461.81</v>
+        <v>94688.37</v>
       </c>
       <c r="L205">
         <v>28194.49</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>BI-176264</t>
+          <t>BI-145540-B</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -13061,7 +13236,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 07/07/2026</t>
+          <t>Parte de ACH Dilson Gerardo Fiori Q2,158.34</t>
         </is>
       </c>
     </row>
@@ -13073,7 +13248,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13083,7 +13258,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Cobro mensualidad julio Mateo Toribio</t>
+          <t>Cobro anticipo 1/2 mensualidad junio Günther Márquez</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13097,13 +13272,13 @@
         </is>
       </c>
       <c r="G206">
-        <v>9300.0</v>
+        <v>2758.33</v>
       </c>
       <c r="H206">
         <v>0.0</v>
       </c>
       <c r="I206">
-        <v>9300.0</v>
+        <v>2758.33</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -13111,14 +13286,14 @@
         </is>
       </c>
       <c r="K206">
-        <v>106761.81</v>
+        <v>97446.7</v>
       </c>
       <c r="L206">
         <v>28194.49</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>BI-9185796</t>
+          <t>BI-176264</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -13128,7 +13303,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 09/07/2026</t>
+          <t>Conciliado con extracto BI 07/07/2026</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13315,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13150,27 +13325,27 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Regalo Día del Maestro</t>
+          <t>Cobro mensualidad julio Mateo Toribio</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>5205 - Actividades y excursiones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G207">
-        <v>895.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H207">
-        <v>95.89</v>
+        <v>0.0</v>
       </c>
       <c r="I207">
-        <v>799.11</v>
+        <v>9300.0</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -13178,24 +13353,24 @@
         </is>
       </c>
       <c r="K207">
-        <v>105866.81</v>
+        <v>106746.7</v>
       </c>
       <c r="L207">
         <v>28194.49</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>BI-10216419</t>
+          <t>BI-9185796</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 10/07/2026</t>
+          <t>Conciliado con extracto BI 09/07/2026</t>
         </is>
       </c>
     </row>
@@ -13207,7 +13382,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13217,27 +13392,27 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Anticipo 4/6 inscripción 2026 Rodrigo Gallinsa</t>
+          <t>Regalo Día del Maestro</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>5205 - Actividades y excursiones</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G208">
-        <v>1287.5</v>
+        <v>895.0</v>
       </c>
       <c r="H208">
-        <v>0.0</v>
+        <v>95.89</v>
       </c>
       <c r="I208">
-        <v>1287.5</v>
+        <v>799.11</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -13245,24 +13420,24 @@
         </is>
       </c>
       <c r="K208">
-        <v>107154.31</v>
+        <v>105851.7</v>
       </c>
       <c r="L208">
         <v>28194.49</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>BI-14170107</t>
+          <t>BI-10216419</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 14/07/2026</t>
+          <t>Conciliado con extracto BI 10/07/2026</t>
         </is>
       </c>
     </row>
@@ -13284,27 +13459,27 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Cobro anticipo 1/2 inscripción 2027 Gabriel Ruíz</t>
+          <t>Anticipo 4/6 inscripción 2026 Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2107 - Anticipo de inscripciones</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pasivo</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G209">
-        <v>5150.0</v>
+        <v>1287.5</v>
       </c>
       <c r="H209">
         <v>0.0</v>
       </c>
       <c r="I209">
-        <v>5150.0</v>
+        <v>1287.5</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -13312,19 +13487,19 @@
         </is>
       </c>
       <c r="K209">
-        <v>112304.31</v>
+        <v>107139.2</v>
       </c>
       <c r="L209">
         <v>28194.49</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>BI-14201939</t>
+          <t>BI-14170107</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -13341,7 +13516,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13351,27 +13526,27 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Pago papelería MINEDUC Ma. Regina</t>
+          <t>Cobro anticipo 1/2 inscripción 2027 Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>2107 - Anticipo de inscripciones</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pasivo</t>
         </is>
       </c>
       <c r="G210">
-        <v>1000.0</v>
+        <v>5150.0</v>
       </c>
       <c r="H210">
-        <v>107.14</v>
+        <v>0.0</v>
       </c>
       <c r="I210">
-        <v>892.86</v>
+        <v>5150.0</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -13379,14 +13554,14 @@
         </is>
       </c>
       <c r="K210">
-        <v>111304.31</v>
+        <v>112289.2</v>
       </c>
       <c r="L210">
         <v>28194.49</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>BI-149015</t>
+          <t>BI-14201939</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -13396,7 +13571,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 20/07/2026</t>
+          <t>Conciliado con extracto BI 14/07/2026</t>
         </is>
       </c>
     </row>
@@ -13408,7 +13583,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13418,12 +13593,12 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Pago suministros (compras Jessi)</t>
+          <t>Pago papelería MINEDUC Ma. Regina</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>5203 - Papelería, útiles y suministros</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -13432,13 +13607,13 @@
         </is>
       </c>
       <c r="G211">
-        <v>455.9</v>
+        <v>1000.0</v>
       </c>
       <c r="H211">
-        <v>48.85</v>
+        <v>107.14</v>
       </c>
       <c r="I211">
-        <v>407.05</v>
+        <v>892.86</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -13446,14 +13621,14 @@
         </is>
       </c>
       <c r="K211">
-        <v>110848.41</v>
+        <v>111289.2</v>
       </c>
       <c r="L211">
         <v>28194.49</v>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>BI-153363</t>
+          <t>BI-149015</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -13463,7 +13638,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 27/07/2026</t>
+          <t>Conciliado con extracto BI 20/07/2026</t>
         </is>
       </c>
     </row>
@@ -13485,12 +13660,12 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Donación Fundación Waybi julio</t>
+          <t>Pago suministros (compras Jessi)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>5208 - Donaciones</t>
+          <t>5203 - Papelería, útiles y suministros</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -13499,13 +13674,13 @@
         </is>
       </c>
       <c r="G212">
-        <v>1700.0</v>
+        <v>455.9</v>
       </c>
       <c r="H212">
-        <v>182.14</v>
+        <v>48.85</v>
       </c>
       <c r="I212">
-        <v>1517.86</v>
+        <v>407.05</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -13513,14 +13688,14 @@
         </is>
       </c>
       <c r="K212">
-        <v>109148.41</v>
+        <v>110833.3</v>
       </c>
       <c r="L212">
         <v>28194.49</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>BI-171670</t>
+          <t>BI-153363</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -13552,12 +13727,12 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Compras actividad Día de la Familia (Adri)</t>
+          <t>Donación Fundación Waybi julio</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>5205 - Actividades y excursiones</t>
+          <t>5208 - Donaciones</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -13566,13 +13741,13 @@
         </is>
       </c>
       <c r="G213">
-        <v>745.9</v>
+        <v>1700.0</v>
       </c>
       <c r="H213">
-        <v>79.92</v>
+        <v>182.14</v>
       </c>
       <c r="I213">
-        <v>665.98</v>
+        <v>1517.86</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -13580,14 +13755,14 @@
         </is>
       </c>
       <c r="K213">
-        <v>108402.51</v>
+        <v>109133.3</v>
       </c>
       <c r="L213">
         <v>28194.49</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>BI-187199</t>
+          <t>BI-171670</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -13619,12 +13794,12 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Pago sueldo julio Geovanna Velázquez</t>
+          <t>Compras actividad Día de la Familia (Adri)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5205 - Actividades y excursiones</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -13633,13 +13808,13 @@
         </is>
       </c>
       <c r="G214">
-        <v>4234.78</v>
+        <v>745.9</v>
       </c>
       <c r="H214">
-        <v>0.0</v>
+        <v>79.92</v>
       </c>
       <c r="I214">
-        <v>4234.78</v>
+        <v>665.98</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -13647,14 +13822,14 @@
         </is>
       </c>
       <c r="K214">
-        <v>104167.73</v>
+        <v>108387.4</v>
       </c>
       <c r="L214">
         <v>28194.49</v>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>BI-208857</t>
+          <t>BI-187199</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -13686,7 +13861,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Pago sueldo julio Jessica Gudiel</t>
+          <t>Pago sueldo julio Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13700,13 +13875,13 @@
         </is>
       </c>
       <c r="G215">
-        <v>5862.19</v>
+        <v>4234.78</v>
       </c>
       <c r="H215">
         <v>0.0</v>
       </c>
       <c r="I215">
-        <v>5862.19</v>
+        <v>4234.78</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -13714,14 +13889,14 @@
         </is>
       </c>
       <c r="K215">
-        <v>98305.54</v>
+        <v>104152.62</v>
       </c>
       <c r="L215">
         <v>28194.49</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>BI-218374</t>
+          <t>BI-208857</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -13753,7 +13928,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Pago sueldo julio Suly Sajbochol</t>
+          <t>Pago sueldo julio Jessica Gudiel</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -13767,13 +13942,13 @@
         </is>
       </c>
       <c r="G216">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="H216">
         <v>0.0</v>
       </c>
       <c r="I216">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -13781,14 +13956,14 @@
         </is>
       </c>
       <c r="K216">
-        <v>94070.76</v>
+        <v>98290.43</v>
       </c>
       <c r="L216">
         <v>28194.49</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>BI-224767</t>
+          <t>BI-218374</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -13820,7 +13995,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Pago sueldo julio Melissa Peña</t>
+          <t>Pago sueldo julio Suly Sajbochol</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13848,14 +14023,14 @@
         </is>
       </c>
       <c r="K217">
-        <v>89835.98</v>
+        <v>94055.65</v>
       </c>
       <c r="L217">
         <v>28194.49</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>BI-238411</t>
+          <t>BI-224767</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -13887,12 +14062,12 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Pago marketing y publicidad julio (Raúl)</t>
+          <t>Pago sueldo julio Melissa Peña</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -13901,13 +14076,13 @@
         </is>
       </c>
       <c r="G218">
-        <v>500.0</v>
+        <v>4234.78</v>
       </c>
       <c r="H218">
-        <v>53.57</v>
+        <v>0.0</v>
       </c>
       <c r="I218">
-        <v>446.43</v>
+        <v>4234.78</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -13915,14 +14090,14 @@
         </is>
       </c>
       <c r="K218">
-        <v>89335.98</v>
+        <v>89820.87</v>
       </c>
       <c r="L218">
         <v>28194.49</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>BI-248172</t>
+          <t>BI-238411</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -13932,7 +14107,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 27/07/2026 (Reclasificado a 5204)</t>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -13954,12 +14129,12 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Pago sueldo julio Lucía Montes</t>
+          <t>Pago marketing y publicidad julio (Raúl)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -13968,13 +14143,13 @@
         </is>
       </c>
       <c r="G219">
-        <v>8574.54</v>
+        <v>500.0</v>
       </c>
       <c r="H219">
-        <v>0.0</v>
+        <v>53.57</v>
       </c>
       <c r="I219">
-        <v>8574.54</v>
+        <v>446.43</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -13982,14 +14157,14 @@
         </is>
       </c>
       <c r="K219">
-        <v>80761.44</v>
+        <v>89320.87</v>
       </c>
       <c r="L219">
         <v>28194.49</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>BI-27147142</t>
+          <t>BI-248172</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -13999,7 +14174,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 27/07/2026</t>
+          <t>Conciliado con extracto BI 27/07/2026 (Reclasificado a 5204)</t>
         </is>
       </c>
     </row>
@@ -14021,27 +14196,27 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Provisiones laborales julio (Traslado a BI-Ahorro)</t>
+          <t>Pago sueldo julio Lucía Montes</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2102 - Provisiones Laborales</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Traspaso Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G220">
-        <v>11551.09</v>
+        <v>8574.54</v>
       </c>
       <c r="H220">
         <v>0.0</v>
       </c>
       <c r="I220">
-        <v>11551.09</v>
+        <v>8574.54</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -14049,14 +14224,14 @@
         </is>
       </c>
       <c r="K220">
-        <v>69210.35</v>
+        <v>80746.33</v>
       </c>
       <c r="L220">
-        <v>39745.58</v>
+        <v>28194.49</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>BI-27154154</t>
+          <t>BI-27147142</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -14088,27 +14263,27 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Pago contabilidad julio Sergio contador</t>
+          <t>Provisiones laborales julio (Traslado a BI-Ahorro)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>2102 - Provisiones Laborales</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Traspaso Ahorro</t>
         </is>
       </c>
       <c r="G221">
-        <v>350.0</v>
+        <v>11551.09</v>
       </c>
       <c r="H221">
-        <v>37.5</v>
+        <v>0.0</v>
       </c>
       <c r="I221">
-        <v>312.5</v>
+        <v>11551.09</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -14116,14 +14291,14 @@
         </is>
       </c>
       <c r="K221">
-        <v>68860.35</v>
+        <v>69195.24</v>
       </c>
       <c r="L221">
         <v>39745.58</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>BI-27171362</t>
+          <t>BI-27154154</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -14155,12 +14330,12 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Pago servicios agencia publicidad Nauta Estudio</t>
+          <t>Pago contabilidad julio Sergio contador</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -14169,13 +14344,13 @@
         </is>
       </c>
       <c r="G222">
-        <v>2050.0</v>
+        <v>350.0</v>
       </c>
       <c r="H222">
-        <v>219.64</v>
+        <v>37.5</v>
       </c>
       <c r="I222">
-        <v>1830.36</v>
+        <v>312.5</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -14183,14 +14358,14 @@
         </is>
       </c>
       <c r="K222">
-        <v>66810.35</v>
+        <v>68845.24</v>
       </c>
       <c r="L222">
         <v>39745.58</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>BI-27216715</t>
+          <t>BI-27171362</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -14200,7 +14375,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 27/07/2026 (Reclasificado a 5204)</t>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -14222,12 +14397,12 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Pago celular ALTUS julio</t>
+          <t>Pago servicios agencia publicidad Nauta Estudio</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -14236,13 +14411,13 @@
         </is>
       </c>
       <c r="G223">
-        <v>285.0</v>
+        <v>2050.0</v>
       </c>
       <c r="H223">
-        <v>30.54</v>
+        <v>219.64</v>
       </c>
       <c r="I223">
-        <v>254.46</v>
+        <v>1830.36</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -14250,14 +14425,14 @@
         </is>
       </c>
       <c r="K223">
-        <v>66525.35</v>
+        <v>66795.24</v>
       </c>
       <c r="L223">
         <v>39745.58</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>BI-27244399</t>
+          <t>BI-27216715</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -14267,7 +14442,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 27/07/2026</t>
+          <t>Conciliado con extracto BI 27/07/2026 (Reclasificado a 5204)</t>
         </is>
       </c>
     </row>
@@ -14289,12 +14464,12 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Pago ISR Retenciones julio</t>
+          <t>Pago celular ALTUS julio</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2105 - ISR Retenciones por Pagar</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -14303,13 +14478,13 @@
         </is>
       </c>
       <c r="G224">
-        <v>375.85</v>
+        <v>285.0</v>
       </c>
       <c r="H224">
-        <v>0.0</v>
+        <v>30.54</v>
       </c>
       <c r="I224">
-        <v>375.85</v>
+        <v>254.46</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -14317,14 +14492,14 @@
         </is>
       </c>
       <c r="K224">
-        <v>66149.5</v>
+        <v>66510.24</v>
       </c>
       <c r="L224">
         <v>39745.58</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>BI-27249346</t>
+          <t>BI-27244399</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -14346,7 +14521,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14356,27 +14531,27 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Donación recibida (ACH Fredy Roberto Bolaños / Sarah Farr)</t>
+          <t>Pago ISR Retenciones julio</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>4203 - Donaciones recibidas</t>
+          <t>2105 - ISR Retenciones por Pagar</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G225">
-        <v>12500.0</v>
+        <v>375.85</v>
       </c>
       <c r="H225">
         <v>0.0</v>
       </c>
       <c r="I225">
-        <v>12500.0</v>
+        <v>375.85</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -14384,14 +14559,14 @@
         </is>
       </c>
       <c r="K225">
-        <v>78649.5</v>
+        <v>66134.39</v>
       </c>
       <c r="L225">
         <v>39745.58</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>BI-221740</t>
+          <t>BI-27249346</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -14401,7 +14576,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 28/07/2026</t>
+          <t>Conciliado con extracto BI 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -14413,7 +14588,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14423,12 +14598,12 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Cobro anticipo 6/6 inscripción Günther Márquez</t>
+          <t>Donación recibida (ACH Fredy Roberto Bolaños / Sarah Farr)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4203 - Donaciones recibidas</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -14437,13 +14612,13 @@
         </is>
       </c>
       <c r="G226">
-        <v>1716.7</v>
+        <v>12500.0</v>
       </c>
       <c r="H226">
         <v>0.0</v>
       </c>
       <c r="I226">
-        <v>1716.7</v>
+        <v>12500.0</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -14451,24 +14626,24 @@
         </is>
       </c>
       <c r="K226">
-        <v>80366.2</v>
+        <v>78634.39</v>
       </c>
       <c r="L226">
         <v>39745.58</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>BI-179331-A</t>
+          <t>BI-221740</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Parte de ACH Valeria Márquez Q3,301.68</t>
+          <t>Conciliado con extracto BI 28/07/2026</t>
         </is>
       </c>
     </row>
@@ -14490,12 +14665,12 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Cobro mensualidad 2/2 junio Günther Márquez</t>
+          <t>Cobro anticipo 6/6 inscripción Günther Márquez</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -14504,13 +14679,13 @@
         </is>
       </c>
       <c r="G227">
-        <v>1584.98</v>
+        <v>1716.7</v>
       </c>
       <c r="H227">
         <v>0.0</v>
       </c>
       <c r="I227">
-        <v>1584.98</v>
+        <v>1716.7</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -14518,14 +14693,14 @@
         </is>
       </c>
       <c r="K227">
-        <v>81951.18</v>
+        <v>80351.09</v>
       </c>
       <c r="L227">
         <v>39745.58</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>BI-179331-B</t>
+          <t>BI-179331-A</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -14535,7 +14710,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>Ajustado a Q1,584.98 (1716.70 + 1584.98 = Q3,301.68 exactos según Docto 179331; se eliminó fila duplicada 226 de Q3,301.69)</t>
+          <t>Parte de ACH Valeria Márquez Q3,301.68</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14722,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14557,27 +14732,27 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Anticipo 1/3 instalación de cámaras</t>
+          <t>Cobro mensualidad 2/2 junio Günther Márquez</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1501 - Mobiliario y Equipo</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G228">
-        <v>7680.0</v>
+        <v>1584.98</v>
       </c>
       <c r="H228">
-        <v>822.86</v>
+        <v>0.0</v>
       </c>
       <c r="I228">
-        <v>6857.14</v>
+        <v>1584.98</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -14585,24 +14760,24 @@
         </is>
       </c>
       <c r="K228">
-        <v>74271.18</v>
+        <v>81936.07</v>
       </c>
       <c r="L228">
         <v>39745.58</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>BI-30187818</t>
+          <t>BI-179331-B</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 30/07/2026</t>
+          <t>Ajustado a Q1,584.98 (1716.70 + 1584.98 = Q3,301.68 exactos según Docto 179331; se eliminó fila duplicada 226 de Q3,301.69)</t>
         </is>
       </c>
     </row>
@@ -14614,22 +14789,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Débito BiCheque comisión manejo de cuenta agosto</t>
+          <t>Anticipo 1/3 instalación de cámaras</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>5210 - Impuestos, tasas y arbitrios</t>
+          <t>1501 - Mobiliario y Equipo</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -14638,13 +14813,13 @@
         </is>
       </c>
       <c r="G229">
-        <v>15.0</v>
+        <v>7680.0</v>
       </c>
       <c r="H229">
-        <v>0.0</v>
+        <v>822.86</v>
       </c>
       <c r="I229">
-        <v>15.0</v>
+        <v>6857.14</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -14652,14 +14827,14 @@
         </is>
       </c>
       <c r="K229">
-        <v>74256.18</v>
+        <v>74256.07</v>
       </c>
       <c r="L229">
         <v>39745.58</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>BI-310867</t>
+          <t>BI-30187818</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -14669,7 +14844,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Agregado según extracto BI 01/08/2026 (DEBITO BICHEQUE)</t>
+          <t>Conciliado con extracto BI 30/07/2026</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14856,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14691,27 +14866,27 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Cobro mensualidad julio Rodrigo Gallinsa</t>
+          <t>Débito BiCheque comisión manejo de cuenta agosto</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G230">
-        <v>6300.0</v>
+        <v>15.0</v>
       </c>
       <c r="H230">
         <v>0.0</v>
       </c>
       <c r="I230">
-        <v>6300.0</v>
+        <v>15.0</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -14719,24 +14894,24 @@
         </is>
       </c>
       <c r="K230">
-        <v>80556.18</v>
+        <v>74241.07</v>
       </c>
       <c r="L230">
         <v>39745.58</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>BI-3100903</t>
+          <t>BI-310867</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 03/08/2026</t>
+          <t>Agregado según extracto BI 01/08/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -14758,7 +14933,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Cobro mensualidad agosto Gabriel Ruíz</t>
+          <t>Cobro mensualidad julio Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -14772,13 +14947,13 @@
         </is>
       </c>
       <c r="G231">
-        <v>9300.0</v>
+        <v>6300.0</v>
       </c>
       <c r="H231">
         <v>0.0</v>
       </c>
       <c r="I231">
-        <v>9300.0</v>
+        <v>6300.0</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -14786,14 +14961,14 @@
         </is>
       </c>
       <c r="K231">
-        <v>89856.18</v>
+        <v>80541.07</v>
       </c>
       <c r="L231">
         <v>39745.58</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>BI-3101691</t>
+          <t>BI-3100903</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -14825,7 +15000,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Cobro mensualidad agosto Rodrigo Gallinsa</t>
+          <t>Cobro mensualidad agosto Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -14839,13 +15014,13 @@
         </is>
       </c>
       <c r="G232">
-        <v>6300.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H232">
         <v>0.0</v>
       </c>
       <c r="I232">
-        <v>6300.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -14853,14 +15028,14 @@
         </is>
       </c>
       <c r="K232">
-        <v>96156.18</v>
+        <v>89841.07</v>
       </c>
       <c r="L232">
         <v>39745.58</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>BI-3120501</t>
+          <t>BI-3101691</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -14892,7 +15067,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Cobro mensualidad agosto Andrei González</t>
+          <t>Cobro mensualidad agosto Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14906,13 +15081,13 @@
         </is>
       </c>
       <c r="G233">
-        <v>3800.0</v>
+        <v>6300.0</v>
       </c>
       <c r="H233">
         <v>0.0</v>
       </c>
       <c r="I233">
-        <v>3800.0</v>
+        <v>6300.0</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -14920,14 +15095,14 @@
         </is>
       </c>
       <c r="K233">
-        <v>99956.18</v>
+        <v>96141.07</v>
       </c>
       <c r="L233">
         <v>39745.58</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>BI-3171312</t>
+          <t>BI-3120501</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -14949,7 +15124,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14959,27 +15134,27 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Google Workspace_altus US</t>
+          <t>Cobro mensualidad agosto Andrei González</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G234">
-        <v>234.96</v>
+        <v>3800.0</v>
       </c>
       <c r="H234">
-        <v>25.17</v>
+        <v>0.0</v>
       </c>
       <c r="I234">
-        <v>209.79</v>
+        <v>3800.0</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -14987,24 +15162,24 @@
         </is>
       </c>
       <c r="K234">
-        <v>99721.22</v>
+        <v>99941.07</v>
       </c>
       <c r="L234">
         <v>39745.58</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>BI-102140</t>
+          <t>BI-3171312</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 04/08/2026</t>
+          <t>Conciliado con extracto BI 03/08/2026</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15191,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -15026,27 +15201,27 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Cobro mensualidad agosto Luís Felipe Guzmán (Pamela Sosa)</t>
+          <t>Google Workspace_altus US</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G235">
-        <v>9300.0</v>
+        <v>234.96</v>
       </c>
       <c r="H235">
-        <v>0.0</v>
+        <v>25.17</v>
       </c>
       <c r="I235">
-        <v>9300.0</v>
+        <v>209.79</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -15054,24 +15229,24 @@
         </is>
       </c>
       <c r="K235">
-        <v>109021.22</v>
+        <v>99706.11</v>
       </c>
       <c r="L235">
         <v>39745.58</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>BI-5138116</t>
+          <t>BI-102140</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 05/08/2026</t>
+          <t>Conciliado con extracto BI 04/08/2026</t>
         </is>
       </c>
     </row>
@@ -15083,7 +15258,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -15093,7 +15268,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Cobro mensualidad agosto Adriana García</t>
+          <t>Cobro mensualidad agosto Luís Felipe Guzmán (Pamela Sosa)</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -15121,14 +15296,14 @@
         </is>
       </c>
       <c r="K236">
-        <v>118321.22</v>
+        <v>109006.11</v>
       </c>
       <c r="L236">
         <v>39745.58</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>BI-6179707</t>
+          <t>BI-5138116</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -15138,7 +15313,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 06/08/2026</t>
+          <t>Conciliado con extracto BI 05/08/2026</t>
         </is>
       </c>
     </row>
@@ -15150,7 +15325,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -15160,7 +15335,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Cobro mensualidad agosto Mateo Toribio</t>
+          <t>Cobro mensualidad agosto Adriana García</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -15188,14 +15363,14 @@
         </is>
       </c>
       <c r="K237">
-        <v>127621.22</v>
+        <v>118306.11</v>
       </c>
       <c r="L237">
         <v>39745.58</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>BI-7229247</t>
+          <t>BI-6179707</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -15205,7 +15380,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 07/08/2026</t>
+          <t>Conciliado con extracto BI 06/08/2026</t>
         </is>
       </c>
     </row>
@@ -15227,27 +15402,27 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Pago 2/3 instalación de cámaras</t>
+          <t>Cobro mensualidad agosto Mateo Toribio</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>1501 - Mobiliario y Equipo</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G238">
-        <v>3473.58</v>
+        <v>9300.0</v>
       </c>
       <c r="H238">
-        <v>372.17</v>
+        <v>0.0</v>
       </c>
       <c r="I238">
-        <v>3101.41</v>
+        <v>9300.0</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -15255,19 +15430,19 @@
         </is>
       </c>
       <c r="K238">
-        <v>124147.64</v>
+        <v>127606.11</v>
       </c>
       <c r="L238">
         <v>39745.58</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>BI-7169841</t>
+          <t>BI-7229247</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -15284,7 +15459,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15294,27 +15469,27 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Cobro mensualidad agosto Giulia Fiorini</t>
+          <t>Pago 2/3 instalación de cámaras</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>1501 - Mobiliario y Equipo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G239">
-        <v>1850.0</v>
+        <v>3473.58</v>
       </c>
       <c r="H239">
-        <v>0.0</v>
+        <v>372.17</v>
       </c>
       <c r="I239">
-        <v>1850.0</v>
+        <v>3101.41</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -15322,24 +15497,24 @@
         </is>
       </c>
       <c r="K239">
-        <v>125997.64</v>
+        <v>124132.53</v>
       </c>
       <c r="L239">
         <v>39745.58</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>BI-9087491-A</t>
+          <t>BI-7169841</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>Parte de Docto 9087491 por Q2,158.34</t>
+          <t>Conciliado con extracto BI 07/08/2026</t>
         </is>
       </c>
     </row>
@@ -15361,12 +15536,12 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Cobro anticipo 5/6 inscripción Giulia Fiorini</t>
+          <t>Cobro mensualidad agosto Giulia Fiorini</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -15375,13 +15550,13 @@
         </is>
       </c>
       <c r="G240">
-        <v>308.34</v>
+        <v>1850.0</v>
       </c>
       <c r="H240">
         <v>0.0</v>
       </c>
       <c r="I240">
-        <v>308.34</v>
+        <v>1850.0</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -15389,14 +15564,14 @@
         </is>
       </c>
       <c r="K240">
-        <v>126305.98</v>
+        <v>125982.53</v>
       </c>
       <c r="L240">
         <v>39745.58</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>BI-9087491-B</t>
+          <t>BI-9087491-A</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -15406,7 +15581,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Ajustado de Q308.35 a Q308.34 para cuadrar exacto con Docto 9087491 (Q2,158.34)</t>
+          <t>Parte de Docto 9087491 por Q2,158.34</t>
         </is>
       </c>
     </row>
@@ -15418,7 +15593,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15428,27 +15603,27 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Último pago 3/3 instalación de cámaras</t>
+          <t>Cobro anticipo 5/6 inscripción Giulia Fiorini</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1501 - Mobiliario y Equipo</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G241">
-        <v>1275.0</v>
+        <v>308.34</v>
       </c>
       <c r="H241">
-        <v>136.61</v>
+        <v>0.0</v>
       </c>
       <c r="I241">
-        <v>1138.39</v>
+        <v>308.34</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -15456,24 +15631,24 @@
         </is>
       </c>
       <c r="K241">
-        <v>125030.98</v>
+        <v>126290.87</v>
       </c>
       <c r="L241">
         <v>39745.58</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>BI-13192758</t>
+          <t>BI-9087491-B</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 13/08/2026</t>
+          <t>Ajustado de Q308.35 a Q308.34 para cuadrar exacto con Docto 9087491 (Q2,158.34)</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15660,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15495,12 +15670,12 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Pago sueldo agosto Geovanna Velázquez</t>
+          <t>Último pago 3/3 instalación de cámaras</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>1501 - Mobiliario y Equipo</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -15509,13 +15684,13 @@
         </is>
       </c>
       <c r="G242">
-        <v>4234.78</v>
+        <v>1275.0</v>
       </c>
       <c r="H242">
-        <v>0.0</v>
+        <v>136.61</v>
       </c>
       <c r="I242">
-        <v>4234.78</v>
+        <v>1138.39</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -15523,14 +15698,14 @@
         </is>
       </c>
       <c r="K242">
-        <v>120796.2</v>
+        <v>125015.87</v>
       </c>
       <c r="L242">
         <v>39745.58</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>BI-137504</t>
+          <t>BI-13192758</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -15540,7 +15715,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 27/08/2026</t>
+          <t>Conciliado con extracto BI 13/08/2026</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15737,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Pago sueldo agosto Suly Sajbochol</t>
+          <t>Pago sueldo agosto Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -15590,14 +15765,14 @@
         </is>
       </c>
       <c r="K243">
-        <v>116561.42</v>
+        <v>120781.09</v>
       </c>
       <c r="L243">
         <v>39745.58</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>BI-152608</t>
+          <t>BI-137504</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -15629,7 +15804,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Pago sueldo agosto Melissa Peña</t>
+          <t>Pago sueldo agosto Suly Sajbochol</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -15657,14 +15832,14 @@
         </is>
       </c>
       <c r="K244">
-        <v>112326.64</v>
+        <v>116546.31</v>
       </c>
       <c r="L244">
         <v>39745.58</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>BI-165806</t>
+          <t>BI-152608</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -15696,12 +15871,12 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Donación agosto Fundación Waybi</t>
+          <t>Pago sueldo agosto Melissa Peña</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>5208 - Donaciones</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -15710,13 +15885,13 @@
         </is>
       </c>
       <c r="G245">
-        <v>1700.0</v>
+        <v>4234.78</v>
       </c>
       <c r="H245">
-        <v>182.14</v>
+        <v>0.0</v>
       </c>
       <c r="I245">
-        <v>1517.86</v>
+        <v>4234.78</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -15724,14 +15899,14 @@
         </is>
       </c>
       <c r="K245">
-        <v>110626.64</v>
+        <v>112311.53</v>
       </c>
       <c r="L245">
         <v>39745.58</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>BI-184088</t>
+          <t>BI-165806</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -15763,12 +15938,12 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Pago sueldo agosto Jessica Gudiel</t>
+          <t>Donación agosto Fundación Waybi</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5208 - Donaciones</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -15777,13 +15952,13 @@
         </is>
       </c>
       <c r="G246">
-        <v>5862.19</v>
+        <v>1700.0</v>
       </c>
       <c r="H246">
-        <v>0.0</v>
+        <v>182.14</v>
       </c>
       <c r="I246">
-        <v>5862.19</v>
+        <v>1517.86</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -15791,14 +15966,14 @@
         </is>
       </c>
       <c r="K246">
-        <v>104764.45</v>
+        <v>110611.53</v>
       </c>
       <c r="L246">
         <v>39745.58</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>BI-226221</t>
+          <t>BI-184088</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -15830,12 +16005,12 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Pago RRSS Altus Raúl</t>
+          <t>Pago sueldo agosto Jessica Gudiel</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -15844,13 +16019,13 @@
         </is>
       </c>
       <c r="G247">
-        <v>500.0</v>
+        <v>5862.19</v>
       </c>
       <c r="H247">
-        <v>53.57</v>
+        <v>0.0</v>
       </c>
       <c r="I247">
-        <v>446.43</v>
+        <v>5862.19</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -15858,14 +16033,14 @@
         </is>
       </c>
       <c r="K247">
-        <v>104264.45</v>
+        <v>104749.34</v>
       </c>
       <c r="L247">
         <v>39745.58</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>BI-231535</t>
+          <t>BI-226221</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -15897,12 +16072,12 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Pago sueldo agosto Lucía Montes</t>
+          <t>Pago RRSS Altus Raúl</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -15911,13 +16086,13 @@
         </is>
       </c>
       <c r="G248">
-        <v>8574.54</v>
+        <v>500.0</v>
       </c>
       <c r="H248">
-        <v>0.0</v>
+        <v>53.57</v>
       </c>
       <c r="I248">
-        <v>8574.54</v>
+        <v>446.43</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -15925,14 +16100,14 @@
         </is>
       </c>
       <c r="K248">
-        <v>95689.91</v>
+        <v>104249.34</v>
       </c>
       <c r="L248">
         <v>39745.58</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>BI-27123339</t>
+          <t>BI-231535</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -15942,7 +16117,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>Ajustado a Q8,574.54 exactos según Docto 27123339</t>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -15964,12 +16139,12 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Publicidad agencia Nauta Estudio Isa González</t>
+          <t>Pago sueldo agosto Lucía Montes</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -15978,13 +16153,13 @@
         </is>
       </c>
       <c r="G249">
-        <v>2050.0</v>
+        <v>8574.54</v>
       </c>
       <c r="H249">
-        <v>219.64</v>
+        <v>0.0</v>
       </c>
       <c r="I249">
-        <v>1830.36</v>
+        <v>8574.54</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -15992,14 +16167,14 @@
         </is>
       </c>
       <c r="K249">
-        <v>93639.91</v>
+        <v>95674.8</v>
       </c>
       <c r="L249">
         <v>39745.58</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>BI-27143053</t>
+          <t>BI-27123339</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -16009,7 +16184,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 27/08/2026</t>
+          <t>Ajustado a Q8,574.54 exactos según Docto 27123339</t>
         </is>
       </c>
     </row>
@@ -16031,27 +16206,27 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Provisiones laborales agosto (Traslado a BI-Ahorro)</t>
+          <t>Publicidad agencia Nauta Estudio Isa González</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2102 - Provisiones Laborales</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Traspaso Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G250">
-        <v>42000.0</v>
+        <v>2050.0</v>
       </c>
       <c r="H250">
-        <v>0.0</v>
+        <v>219.64</v>
       </c>
       <c r="I250">
-        <v>42000.0</v>
+        <v>1830.36</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -16059,14 +16234,14 @@
         </is>
       </c>
       <c r="K250">
-        <v>51639.91</v>
+        <v>93624.8</v>
       </c>
       <c r="L250">
-        <v>81745.58</v>
+        <v>39745.58</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>BI-27145997</t>
+          <t>BI-27143053</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -16098,27 +16273,27 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Honorarios contabilidad agosto Sergio contador</t>
+          <t>Provisiones laborales agosto (Traslado a BI-Ahorro)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>2102 - Provisiones Laborales</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Traspaso Ahorro</t>
         </is>
       </c>
       <c r="G251">
-        <v>350.0</v>
+        <v>42000.0</v>
       </c>
       <c r="H251">
-        <v>37.5</v>
+        <v>0.0</v>
       </c>
       <c r="I251">
-        <v>312.5</v>
+        <v>42000.0</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -16126,14 +16301,14 @@
         </is>
       </c>
       <c r="K251">
-        <v>51289.91</v>
+        <v>51624.8</v>
       </c>
       <c r="L251">
         <v>81745.58</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>BI-27176761</t>
+          <t>BI-27145997</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -16165,12 +16340,12 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Pago impuesto ISR retenido agosto</t>
+          <t>Honorarios contabilidad agosto Sergio contador</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2105 - ISR Retenciones por Pagar</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -16179,13 +16354,13 @@
         </is>
       </c>
       <c r="G252">
-        <v>375.85</v>
+        <v>350.0</v>
       </c>
       <c r="H252">
-        <v>0.0</v>
+        <v>37.5</v>
       </c>
       <c r="I252">
-        <v>375.85</v>
+        <v>312.5</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -16193,14 +16368,14 @@
         </is>
       </c>
       <c r="K252">
-        <v>50914.06</v>
+        <v>51274.8</v>
       </c>
       <c r="L252">
         <v>81745.58</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>BI-27197546</t>
+          <t>BI-27176761</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -16232,12 +16407,12 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Pago celular ALTUS agosto</t>
+          <t>Pago impuesto ISR retenido agosto</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>2105 - ISR Retenciones por Pagar</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -16246,13 +16421,13 @@
         </is>
       </c>
       <c r="G253">
-        <v>285.0</v>
+        <v>375.85</v>
       </c>
       <c r="H253">
-        <v>30.54</v>
+        <v>0.0</v>
       </c>
       <c r="I253">
-        <v>254.46</v>
+        <v>375.85</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -16260,14 +16435,14 @@
         </is>
       </c>
       <c r="K253">
-        <v>50629.06</v>
+        <v>50898.95</v>
       </c>
       <c r="L253">
         <v>81745.58</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>BI-27208297</t>
+          <t>BI-27197546</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -16289,37 +16464,37 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Cobro mensualidad septiembre Andrei González</t>
+          <t>Pago celular ALTUS agosto</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G254">
-        <v>3800.0</v>
+        <v>285.0</v>
       </c>
       <c r="H254">
-        <v>0.0</v>
+        <v>30.54</v>
       </c>
       <c r="I254">
-        <v>3800.0</v>
+        <v>254.46</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -16327,24 +16502,24 @@
         </is>
       </c>
       <c r="K254">
-        <v>54429.06</v>
+        <v>50613.95</v>
       </c>
       <c r="L254">
         <v>81745.58</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>BI-1163180</t>
+          <t>BI-27208297</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 01/09/2026</t>
+          <t>Conciliado con extracto BI 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -16366,7 +16541,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Cobro mensualidad septiembre Gabriel Ruíz</t>
+          <t>Cobro mensualidad septiembre Andrei González</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -16380,13 +16555,13 @@
         </is>
       </c>
       <c r="G255">
-        <v>9300.0</v>
+        <v>3800.0</v>
       </c>
       <c r="H255">
         <v>0.0</v>
       </c>
       <c r="I255">
-        <v>9300.0</v>
+        <v>3800.0</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -16394,14 +16569,14 @@
         </is>
       </c>
       <c r="K255">
-        <v>63729.06</v>
+        <v>54413.95</v>
       </c>
       <c r="L255">
         <v>81745.58</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>BI-1224897</t>
+          <t>BI-1163180</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -16433,27 +16608,27 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Débito BiCheque comisión manejo de cuenta septiembre</t>
+          <t>Cobro mensualidad septiembre Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>5210 - Impuestos, tasas y arbitrios</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G256">
-        <v>15.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H256">
         <v>0.0</v>
       </c>
       <c r="I256">
-        <v>15.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -16461,24 +16636,24 @@
         </is>
       </c>
       <c r="K256">
-        <v>63714.06</v>
+        <v>63713.95</v>
       </c>
       <c r="L256">
         <v>81745.58</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>BI-309025</t>
+          <t>BI-1224897</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Agregado según extracto BI 01/09/2026 (DEBITO BICHEQUE)</t>
+          <t>Conciliado con extracto BI 01/09/2026</t>
         </is>
       </c>
     </row>
@@ -16490,7 +16665,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16500,12 +16675,12 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Google Workspace_altus US</t>
+          <t>Débito BiCheque comisión manejo de cuenta septiembre</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -16514,13 +16689,13 @@
         </is>
       </c>
       <c r="G257">
-        <v>234.96</v>
+        <v>15.0</v>
       </c>
       <c r="H257">
-        <v>25.17</v>
+        <v>0.0</v>
       </c>
       <c r="I257">
-        <v>209.79</v>
+        <v>15.0</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -16528,14 +16703,14 @@
         </is>
       </c>
       <c r="K257">
-        <v>63479.1</v>
+        <v>63698.95</v>
       </c>
       <c r="L257">
         <v>81745.58</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>BI-123361</t>
+          <t>BI-309025</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -16545,7 +16720,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 02/09/2026</t>
+          <t>Agregado según extracto BI 01/09/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -16567,12 +16742,12 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Compra Dollar City suministros</t>
+          <t>Google Workspace_altus US</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>5203 - Papelería, útiles y suministros</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -16581,13 +16756,13 @@
         </is>
       </c>
       <c r="G258">
-        <v>245.0</v>
+        <v>234.96</v>
       </c>
       <c r="H258">
-        <v>26.25</v>
+        <v>25.17</v>
       </c>
       <c r="I258">
-        <v>218.75</v>
+        <v>209.79</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -16595,14 +16770,14 @@
         </is>
       </c>
       <c r="K258">
-        <v>63234.1</v>
+        <v>63463.99</v>
       </c>
       <c r="L258">
         <v>81745.58</v>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>BI-2183529</t>
+          <t>BI-123361</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -16624,7 +16799,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16634,27 +16809,27 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Cobro mensualidad septiembre Adriana García</t>
+          <t>Compra Dollar City suministros</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5203 - Papelería, útiles y suministros</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G259">
-        <v>9300.0</v>
+        <v>245.0</v>
       </c>
       <c r="H259">
-        <v>0.0</v>
+        <v>26.25</v>
       </c>
       <c r="I259">
-        <v>9300.0</v>
+        <v>218.75</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -16662,24 +16837,24 @@
         </is>
       </c>
       <c r="K259">
-        <v>72534.1</v>
+        <v>63218.99</v>
       </c>
       <c r="L259">
         <v>81745.58</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>BI-4169159</t>
+          <t>BI-2183529</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 04/09/2026</t>
+          <t>Conciliado con extracto BI 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -16701,27 +16876,27 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Honorarios reparación ventana anticipo 1/2</t>
+          <t>Cobro mensualidad septiembre Adriana García</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G260">
-        <v>1550.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H260">
-        <v>166.07</v>
+        <v>0.0</v>
       </c>
       <c r="I260">
-        <v>1383.93</v>
+        <v>9300.0</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -16729,19 +16904,19 @@
         </is>
       </c>
       <c r="K260">
-        <v>70984.1</v>
+        <v>72518.99</v>
       </c>
       <c r="L260">
         <v>81745.58</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>BI-4099839</t>
+          <t>BI-4169159</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -16758,7 +16933,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16768,27 +16943,27 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Cobro mensualidad septiembre Luís Felipe Guzmán (Pamela Sosa)</t>
+          <t>Honorarios reparación ventana anticipo 1/2</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G261">
-        <v>9300.0</v>
+        <v>1550.0</v>
       </c>
       <c r="H261">
-        <v>0.0</v>
+        <v>166.07</v>
       </c>
       <c r="I261">
-        <v>9300.0</v>
+        <v>1383.93</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -16796,24 +16971,24 @@
         </is>
       </c>
       <c r="K261">
-        <v>80284.1</v>
+        <v>70968.99</v>
       </c>
       <c r="L261">
         <v>81745.58</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>BI-5101701</t>
+          <t>BI-4099839</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 05/09/2026 (Actualizado en pestaña Colegiaturas S7 = Q9,300)</t>
+          <t>Conciliado con extracto BI 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -16825,7 +17000,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16835,7 +17010,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Cobro mensualidad septiembre Giulia Fiorini (Agencia El Frutal)</t>
+          <t>Cobro mensualidad septiembre Luís Felipe Guzmán (Pamela Sosa)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -16849,13 +17024,13 @@
         </is>
       </c>
       <c r="G262">
-        <v>1850.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H262">
         <v>0.0</v>
       </c>
       <c r="I262">
-        <v>1850.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -16863,14 +17038,14 @@
         </is>
       </c>
       <c r="K262">
-        <v>82134.1</v>
+        <v>80268.99</v>
       </c>
       <c r="L262">
         <v>81745.58</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>BI-14269407-A</t>
+          <t>BI-5101701</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -16880,7 +17055,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Parte de Docto 14269407 por Q2,158.34</t>
+          <t>Conciliado con extracto BI 05/09/2026 (Actualizado en pestaña Colegiaturas S7 = Q9,300)</t>
         </is>
       </c>
     </row>
@@ -16902,12 +17077,12 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Cobro anticipo 6/6 inscripción Giulia Fiorini</t>
+          <t>Cobro mensualidad septiembre Giulia Fiorini (Agencia El Frutal)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>4101 - Inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -16916,13 +17091,13 @@
         </is>
       </c>
       <c r="G263">
-        <v>308.34</v>
+        <v>1850.0</v>
       </c>
       <c r="H263">
         <v>0.0</v>
       </c>
       <c r="I263">
-        <v>308.34</v>
+        <v>1850.0</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -16930,14 +17105,14 @@
         </is>
       </c>
       <c r="K263">
-        <v>82442.44</v>
+        <v>82118.99</v>
       </c>
       <c r="L263">
         <v>81745.58</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>BI-14269407-B</t>
+          <t>BI-14269407-A</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -16947,7 +17122,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Ajustado de Q308.35 a Q308.34 según Docto 14269407 (Q2,158.34)</t>
+          <t>Parte de Docto 14269407 por Q2,158.34</t>
         </is>
       </c>
     </row>
@@ -16959,7 +17134,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16969,12 +17144,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Cobro mensualidad septiembre Mateo Toribio</t>
+          <t>Cobro anticipo 6/6 inscripción Giulia Fiorini</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>4101 - Inscripciones</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -16983,13 +17158,13 @@
         </is>
       </c>
       <c r="G264">
-        <v>9300.0</v>
+        <v>308.34</v>
       </c>
       <c r="H264">
         <v>0.0</v>
       </c>
       <c r="I264">
-        <v>9300.0</v>
+        <v>308.34</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -16997,14 +17172,14 @@
         </is>
       </c>
       <c r="K264">
-        <v>91742.44</v>
+        <v>82427.33</v>
       </c>
       <c r="L264">
         <v>81745.58</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>BI-9222400</t>
+          <t>BI-14269407-B</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -17014,7 +17189,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 09/09/2026</t>
+          <t>Ajustado de Q308.35 a Q308.34 según Docto 14269407 (Q2,158.34)</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17201,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -17036,7 +17211,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Cobro mensualidad septiembre Rodrigo Gallinsa</t>
+          <t>Cobro mensualidad septiembre Mateo Toribio</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -17050,13 +17225,13 @@
         </is>
       </c>
       <c r="G265">
-        <v>6300.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H265">
         <v>0.0</v>
       </c>
       <c r="I265">
-        <v>6300.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -17064,14 +17239,14 @@
         </is>
       </c>
       <c r="K265">
-        <v>98042.44</v>
+        <v>91727.33</v>
       </c>
       <c r="L265">
         <v>81745.58</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>BI-16160513</t>
+          <t>BI-9222400</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -17081,7 +17256,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 16/09/2026</t>
+          <t>Conciliado con extracto BI 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -17093,7 +17268,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -17103,27 +17278,27 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Cobro anticipo 1/3 Inscripción 2027 Santiago Matta (ACH Juan José Mata)</t>
+          <t>Cobro mensualidad septiembre Rodrigo Gallinsa</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2107 - Anticipo de inscripciones</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Pasivo</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G266">
-        <v>4000.0</v>
+        <v>6300.0</v>
       </c>
       <c r="H266">
         <v>0.0</v>
       </c>
       <c r="I266">
-        <v>4000.0</v>
+        <v>6300.0</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -17131,24 +17306,24 @@
         </is>
       </c>
       <c r="K266">
-        <v>102042.44</v>
+        <v>98027.33</v>
       </c>
       <c r="L266">
         <v>81745.58</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>BI-162290</t>
+          <t>BI-16160513</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 21/09/2026</t>
+          <t>Conciliado con extracto BI 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -17170,27 +17345,27 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Excursión Día del Niño</t>
+          <t>Cobro anticipo 1/3 Inscripción 2027 Santiago Matta (ACH Juan José Mata)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>5205 - Actividades y excursiones</t>
+          <t>2107 - Anticipo de inscripciones</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Pasivo</t>
         </is>
       </c>
       <c r="G267">
-        <v>260.0</v>
+        <v>4000.0</v>
       </c>
       <c r="H267">
-        <v>27.86</v>
+        <v>0.0</v>
       </c>
       <c r="I267">
-        <v>232.14</v>
+        <v>4000.0</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -17198,14 +17373,14 @@
         </is>
       </c>
       <c r="K267">
-        <v>101782.44</v>
+        <v>102027.33</v>
       </c>
       <c r="L267">
         <v>81745.58</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>BI-218928</t>
+          <t>BI-162290</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -17227,7 +17402,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -17237,12 +17412,12 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Compra carretilla Novex San Cristóbal</t>
+          <t>Excursión Día del Niño</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>5207 - Otros Gastos (No Deducibles)</t>
+          <t>5205 - Actividades y excursiones</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -17251,13 +17426,13 @@
         </is>
       </c>
       <c r="G268">
-        <v>425.0</v>
+        <v>260.0</v>
       </c>
       <c r="H268">
-        <v>0.0</v>
+        <v>27.86</v>
       </c>
       <c r="I268">
-        <v>425.0</v>
+        <v>232.14</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -17265,14 +17440,14 @@
         </is>
       </c>
       <c r="K268">
-        <v>101357.44</v>
+        <v>101767.33</v>
       </c>
       <c r="L268">
         <v>81745.58</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>BI-148758</t>
+          <t>BI-218928</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -17282,7 +17457,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 22/09/2026</t>
+          <t>Conciliado con extracto BI 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17479,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Pago extintor 1</t>
+          <t>Compra carretilla Novex San Cristóbal</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -17318,13 +17493,13 @@
         </is>
       </c>
       <c r="G269">
-        <v>250.0</v>
+        <v>425.0</v>
       </c>
       <c r="H269">
         <v>0.0</v>
       </c>
       <c r="I269">
-        <v>250.0</v>
+        <v>425.0</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -17332,14 +17507,14 @@
         </is>
       </c>
       <c r="K269">
-        <v>101107.44</v>
+        <v>101342.33</v>
       </c>
       <c r="L269">
         <v>81745.58</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>BI-22108017</t>
+          <t>BI-148758</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -17361,7 +17536,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -17371,7 +17546,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Pago segundo extintor</t>
+          <t>Pago extintor 1</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -17399,14 +17574,14 @@
         </is>
       </c>
       <c r="K270">
-        <v>100857.44</v>
+        <v>101092.33</v>
       </c>
       <c r="L270">
         <v>81745.58</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>BI-25176197</t>
+          <t>BI-22108017</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -17416,7 +17591,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 25/09/2026</t>
+          <t>Conciliado con extracto BI 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17603,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -17438,12 +17613,12 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Donación Fundación Waybi septiembre</t>
+          <t>Pago segundo extintor</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>5208 - Donaciones</t>
+          <t>5207 - Otros Gastos (No Deducibles)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -17452,13 +17627,13 @@
         </is>
       </c>
       <c r="G271">
-        <v>1700.0</v>
+        <v>250.0</v>
       </c>
       <c r="H271">
-        <v>182.14</v>
+        <v>0.0</v>
       </c>
       <c r="I271">
-        <v>1517.86</v>
+        <v>250.0</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -17466,14 +17641,14 @@
         </is>
       </c>
       <c r="K271">
-        <v>99157.44</v>
+        <v>100842.33</v>
       </c>
       <c r="L271">
         <v>81745.58</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>BI-99935</t>
+          <t>BI-25176197</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -17483,7 +17658,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 29/09/2026</t>
+          <t>Conciliado con extracto BI 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -17505,12 +17680,12 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Pago sueldo septiembre Jessica Gudiel</t>
+          <t>Donación Fundación Waybi septiembre</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5208 - Donaciones</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -17519,13 +17694,13 @@
         </is>
       </c>
       <c r="G272">
-        <v>5862.19</v>
+        <v>1700.0</v>
       </c>
       <c r="H272">
-        <v>0.0</v>
+        <v>182.14</v>
       </c>
       <c r="I272">
-        <v>5862.19</v>
+        <v>1517.86</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -17533,14 +17708,14 @@
         </is>
       </c>
       <c r="K272">
-        <v>93295.25</v>
+        <v>99142.33</v>
       </c>
       <c r="L272">
         <v>81745.58</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>BI-109817</t>
+          <t>BI-99935</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -17572,7 +17747,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Pago sueldo septiembre Geovanna Velázquez</t>
+          <t>Pago sueldo septiembre Jessica Gudiel</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -17586,13 +17761,13 @@
         </is>
       </c>
       <c r="G273">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="H273">
         <v>0.0</v>
       </c>
       <c r="I273">
-        <v>4234.78</v>
+        <v>5862.19</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -17600,14 +17775,14 @@
         </is>
       </c>
       <c r="K273">
-        <v>89060.47</v>
+        <v>93280.14</v>
       </c>
       <c r="L273">
         <v>81745.58</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>BI-132249</t>
+          <t>BI-109817</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -17639,7 +17814,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Pago sueldo septiembre Suly Sajbochol</t>
+          <t>Pago sueldo septiembre Geovanna Velázquez</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -17667,14 +17842,14 @@
         </is>
       </c>
       <c r="K274">
-        <v>84825.69</v>
+        <v>89045.36</v>
       </c>
       <c r="L274">
         <v>81745.58</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>BI-147240</t>
+          <t>BI-132249</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -17706,7 +17881,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Pago sueldo septiembre Melissa Peña</t>
+          <t>Pago sueldo septiembre Suly Sajbochol</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -17734,14 +17909,14 @@
         </is>
       </c>
       <c r="K275">
-        <v>80590.91</v>
+        <v>84810.58</v>
       </c>
       <c r="L275">
         <v>81745.58</v>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>BI-167114</t>
+          <t>BI-147240</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -17773,12 +17948,12 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Pago agencia redes sociales Isa González</t>
+          <t>Pago sueldo septiembre Melissa Peña</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>5204 - Marketing y Publicidad</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -17787,13 +17962,13 @@
         </is>
       </c>
       <c r="G276">
-        <v>1600.0</v>
+        <v>4234.78</v>
       </c>
       <c r="H276">
-        <v>171.43</v>
+        <v>0.0</v>
       </c>
       <c r="I276">
-        <v>1428.57</v>
+        <v>4234.78</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -17801,14 +17976,14 @@
         </is>
       </c>
       <c r="K276">
-        <v>78990.91</v>
+        <v>80575.8</v>
       </c>
       <c r="L276">
         <v>81745.58</v>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>BI-29114366</t>
+          <t>BI-167114</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -17818,7 +17993,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 29/09/2026 (Docto 29114366: 5204 AGENCIA REDES SOCIALES)</t>
+          <t>Conciliado con extracto BI 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -17840,12 +18015,12 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Pago sueldo septiembre Lucía Montes</t>
+          <t>Pago agencia redes sociales Isa González</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>5101 - Sueldos y Salarios</t>
+          <t>5204 - Marketing y Publicidad</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -17854,13 +18029,13 @@
         </is>
       </c>
       <c r="G277">
-        <v>8574.54</v>
+        <v>1600.0</v>
       </c>
       <c r="H277">
-        <v>0.0</v>
+        <v>171.43</v>
       </c>
       <c r="I277">
-        <v>8574.54</v>
+        <v>1428.57</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -17868,14 +18043,14 @@
         </is>
       </c>
       <c r="K277">
-        <v>70416.37</v>
+        <v>78975.8</v>
       </c>
       <c r="L277">
         <v>81745.58</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>BI-29116957</t>
+          <t>BI-29114366</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -17885,7 +18060,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 29/09/2026 (Q8,574.54 exactos)</t>
+          <t>Conciliado con extracto BI 29/09/2026 (Docto 29114366: 5204 AGENCIA REDES SOCIALES)</t>
         </is>
       </c>
     </row>
@@ -17907,12 +18082,12 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Pago celular ALTUS septiembre</t>
+          <t>Pago sueldo septiembre Lucía Montes</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>5101 - Sueldos y Salarios</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -17921,13 +18096,13 @@
         </is>
       </c>
       <c r="G278">
-        <v>285.0</v>
+        <v>8574.54</v>
       </c>
       <c r="H278">
-        <v>30.54</v>
+        <v>0.0</v>
       </c>
       <c r="I278">
-        <v>254.46</v>
+        <v>8574.54</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -17935,14 +18110,14 @@
         </is>
       </c>
       <c r="K278">
-        <v>70131.37</v>
+        <v>70401.26</v>
       </c>
       <c r="L278">
         <v>81745.58</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>BI-29152215</t>
+          <t>BI-29116957</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -17952,7 +18127,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 29/09/2026</t>
+          <t>Conciliado con extracto BI 29/09/2026 (Q8,574.54 exactos)</t>
         </is>
       </c>
     </row>
@@ -17974,27 +18149,27 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Provisiones laborales septiembre (Traslado a BI-Ahorro)</t>
+          <t>Pago celular ALTUS septiembre</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2102 - Provisiones Laborales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Traspaso Ahorro</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G279">
-        <v>11551.09</v>
+        <v>285.0</v>
       </c>
       <c r="H279">
-        <v>0.0</v>
+        <v>30.54</v>
       </c>
       <c r="I279">
-        <v>11551.09</v>
+        <v>254.46</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -18002,14 +18177,14 @@
         </is>
       </c>
       <c r="K279">
-        <v>58580.28</v>
+        <v>70116.26</v>
       </c>
       <c r="L279">
-        <v>93296.67</v>
+        <v>81745.58</v>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>BI-29180131</t>
+          <t>BI-29152215</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -18041,42 +18216,42 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Pago planilla IGSS (desde cuenta BI-Ahorro)</t>
+          <t>Provisiones laborales septiembre (Traslado a BI-Ahorro)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2103 - IGSS por Pagar</t>
+          <t>2102 - Provisiones Laborales</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Pago Reserva Ahorro</t>
+          <t>Traspaso Ahorro</t>
         </is>
       </c>
       <c r="G280">
-        <v>4278.0</v>
+        <v>11551.09</v>
       </c>
       <c r="H280">
         <v>0.0</v>
       </c>
       <c r="I280">
-        <v>4278.0</v>
+        <v>11551.09</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>BI-Ahorro</t>
+          <t>BI- Monetaria</t>
         </is>
       </c>
       <c r="K280">
-        <v>58580.28</v>
+        <v>58565.17</v>
       </c>
       <c r="L280">
-        <v>89018.67</v>
+        <v>93296.67</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>AHO-IGSS-09</t>
+          <t>BI-29180131</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -18086,7 +18261,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>Corregido origen de BI-Monetaria a BI-Ahorro (no aparece en extracto Monetaria 2061406126 porque se paga desde Ahorro)</t>
+          <t>Conciliado con extracto BI 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -18098,62 +18273,62 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Cobro mensualidad octubre Gabriel Ruíz</t>
+          <t>Pago planilla IGSS (desde cuenta BI-Ahorro)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>2103 - IGSS por Pagar</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Pago Reserva Ahorro</t>
         </is>
       </c>
       <c r="G281">
-        <v>9300.0</v>
+        <v>4278.0</v>
       </c>
       <c r="H281">
         <v>0.0</v>
       </c>
       <c r="I281">
-        <v>9300.0</v>
+        <v>4278.0</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>BI- Monetaria</t>
+          <t>BI-Ahorro</t>
         </is>
       </c>
       <c r="K281">
-        <v>67880.28</v>
+        <v>58565.17</v>
       </c>
       <c r="L281">
         <v>89018.67</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>BI-1266971</t>
+          <t>AHO-IGSS-09</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 01/10/2026</t>
+          <t>Corregido origen de BI-Monetaria a BI-Ahorro (no aparece en extracto Monetaria 2061406126 porque se paga desde Ahorro)</t>
         </is>
       </c>
     </row>
@@ -18175,27 +18350,27 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Débito BiCheque comisión manejo de cuenta octubre</t>
+          <t>Cobro mensualidad octubre Gabriel Ruíz</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>5210 - Impuestos, tasas y arbitrios</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G282">
-        <v>15.0</v>
+        <v>9300.0</v>
       </c>
       <c r="H282">
         <v>0.0</v>
       </c>
       <c r="I282">
-        <v>15.0</v>
+        <v>9300.0</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -18203,24 +18378,24 @@
         </is>
       </c>
       <c r="K282">
-        <v>67865.28</v>
+        <v>67865.17</v>
       </c>
       <c r="L282">
         <v>89018.67</v>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>BI-309581</t>
+          <t>BI-1266971</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>Agregado según extracto BI 01/10/2026 (DEBITO BICHEQUE)</t>
+          <t>Conciliado con extracto BI 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -18232,7 +18407,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -18242,27 +18417,27 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Cobro mensualidad octubre Andrei González</t>
+          <t>Débito BiCheque comisión manejo de cuenta octubre</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5210 - Impuestos, tasas y arbitrios</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G283">
-        <v>3800.0</v>
+        <v>15.0</v>
       </c>
       <c r="H283">
         <v>0.0</v>
       </c>
       <c r="I283">
-        <v>3800.0</v>
+        <v>15.0</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -18270,24 +18445,24 @@
         </is>
       </c>
       <c r="K283">
-        <v>71665.28</v>
+        <v>67850.17</v>
       </c>
       <c r="L283">
         <v>89018.67</v>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>BI-2090132</t>
+          <t>BI-309581</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 02/10/2026</t>
+          <t>Agregado según extracto BI 01/10/2026 (DEBITO BICHEQUE)</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18484,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Cobro mensualidad octubre Adriana García</t>
+          <t>Cobro mensualidad octubre Andrei González</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -18323,13 +18498,13 @@
         </is>
       </c>
       <c r="G284">
-        <v>9300.0</v>
+        <v>3800.0</v>
       </c>
       <c r="H284">
         <v>0.0</v>
       </c>
       <c r="I284">
-        <v>9300.0</v>
+        <v>3800.0</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -18337,14 +18512,14 @@
         </is>
       </c>
       <c r="K284">
-        <v>80965.28</v>
+        <v>71650.17</v>
       </c>
       <c r="L284">
         <v>89018.67</v>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>BI-2141911</t>
+          <t>BI-2090132</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -18376,27 +18551,27 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Google Workspace_altus US octubre</t>
+          <t>Cobro mensualidad octubre Adriana García</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>5212 - Telecomunicaciones e internet</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G285">
-        <v>235.27</v>
+        <v>9300.0</v>
       </c>
       <c r="H285">
-        <v>25.21</v>
+        <v>0.0</v>
       </c>
       <c r="I285">
-        <v>210.06</v>
+        <v>9300.0</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -18404,24 +18579,24 @@
         </is>
       </c>
       <c r="K285">
-        <v>80730.01</v>
+        <v>80950.17</v>
       </c>
       <c r="L285">
         <v>89018.67</v>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>BI-168343</t>
+          <t>BI-2141911</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>Agregado según extracto BI 02/10/2026</t>
+          <t>Conciliado con extracto BI 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -18433,7 +18608,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -18443,27 +18618,27 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Cobro mensualidad octubre Luís Felipe Guzmán (Pamela Sosa)</t>
+          <t>Google Workspace_altus US octubre</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5212 - Telecomunicaciones e internet</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G286">
-        <v>9300.0</v>
+        <v>235.27</v>
       </c>
       <c r="H286">
-        <v>0.0</v>
+        <v>25.21</v>
       </c>
       <c r="I286">
-        <v>9300.0</v>
+        <v>210.06</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -18471,24 +18646,24 @@
         </is>
       </c>
       <c r="K286">
-        <v>90030.01</v>
+        <v>80714.9</v>
       </c>
       <c r="L286">
         <v>89018.67</v>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>BI-5140139</t>
+          <t>BI-168343</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>Conciliado con extracto BI 05/10/2026</t>
+          <t>Agregado según extracto BI 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -18500,7 +18675,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -18510,27 +18685,27 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Pago ISR retenido personal (correspondiente a cierre sep)</t>
+          <t>Cobro mensualidad octubre Luís Felipe Guzmán (Pamela Sosa)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2105 - ISR Retenciones por Pagar</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G287">
-        <v>375.85</v>
+        <v>9300.0</v>
       </c>
       <c r="H287">
         <v>0.0</v>
       </c>
       <c r="I287">
-        <v>375.85</v>
+        <v>9300.0</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -18538,24 +18713,24 @@
         </is>
       </c>
       <c r="K287">
-        <v>89654.16</v>
+        <v>90014.9</v>
       </c>
       <c r="L287">
         <v>89018.67</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>BI-6107849</t>
+          <t>BI-5140139</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>Movido de 29/09 a su fecha real de débito en banco 06/10/2026 (Docto 6107849)</t>
+          <t>Conciliado con extracto BI 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -18577,12 +18752,12 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Honorarios contabilidad Sergio contador</t>
+          <t>Pago ISR retenido personal (correspondiente a cierre sep)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>2105 - ISR Retenciones por Pagar</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -18591,13 +18766,13 @@
         </is>
       </c>
       <c r="G288">
-        <v>350.0</v>
+        <v>375.85</v>
       </c>
       <c r="H288">
-        <v>37.5</v>
+        <v>0.0</v>
       </c>
       <c r="I288">
-        <v>312.5</v>
+        <v>375.85</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -18605,14 +18780,14 @@
         </is>
       </c>
       <c r="K288">
-        <v>89304.16</v>
+        <v>89639.05</v>
       </c>
       <c r="L288">
         <v>89018.67</v>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>BI-6161486</t>
+          <t>BI-6107849</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -18622,7 +18797,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>Movido de 29/09 a su fecha real de débito en banco 06/10/2026 (Docto 6161486)</t>
+          <t>Movido de 29/09 a su fecha real de débito en banco 06/10/2026 (Docto 6107849)</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18809,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18644,27 +18819,27 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Cobro mensualidad octubre Giulia Fiorini (ACH Dilson Gerardo Fiori)</t>
+          <t>Honorarios contabilidad Sergio contador</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G289">
-        <v>1850.0</v>
+        <v>350.0</v>
       </c>
       <c r="H289">
-        <v>0.0</v>
+        <v>37.5</v>
       </c>
       <c r="I289">
-        <v>1850.0</v>
+        <v>312.5</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -18672,24 +18847,24 @@
         </is>
       </c>
       <c r="K289">
-        <v>91154.16</v>
+        <v>89289.05</v>
       </c>
       <c r="L289">
         <v>89018.67</v>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>BI-127890</t>
+          <t>BI-6161486</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>01-Pre-Primaria / 02-Primaria</t>
+          <t>00-Administración</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>Agregado según extracto BI 07/10/2026 y actualizado en Colegiaturas T5</t>
+          <t>Movido de 29/09 a su fecha real de débito en banco 06/10/2026 (Docto 6161486)</t>
         </is>
       </c>
     </row>
@@ -18711,27 +18886,27 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Honorarios gestión papelería Lourdes Escribá (2 meses: Q1,454 x 2)</t>
+          <t>Cobro mensualidad octubre Giulia Fiorini (ACH Dilson Gerardo Fiori)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>5209 - Honorarios profesionales</t>
+          <t>4102 - Colegiaturas Mensuales</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Gasto</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="G290">
-        <v>2908.0</v>
+        <v>1850.0</v>
       </c>
       <c r="H290">
-        <v>311.57</v>
+        <v>0.0</v>
       </c>
       <c r="I290">
-        <v>2596.43</v>
+        <v>1850.0</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -18739,24 +18914,24 @@
         </is>
       </c>
       <c r="K290">
-        <v>88246.16</v>
+        <v>91139.05</v>
       </c>
       <c r="L290">
         <v>89018.67</v>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>BI-157584</t>
+          <t>BI-127890</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>00-Administración</t>
+          <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>Ajustado según extracto BI 07/10/2026 (Docto 157584 por Q2,908.00)</t>
+          <t>Agregado según extracto BI 07/10/2026 y actualizado en Colegiaturas T5</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18943,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18778,27 +18953,27 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Cobro mensualidad octubre Mateo Toribio</t>
+          <t>Honorarios gestión papelería Lourdes Escribá (2 meses: Q1,454 x 2)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>4102 - Colegiaturas Mensuales</t>
+          <t>5209 - Honorarios profesionales</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="G291">
-        <v>9300.0</v>
+        <v>2908.0</v>
       </c>
       <c r="H291">
-        <v>0.0</v>
+        <v>311.57</v>
       </c>
       <c r="I291">
-        <v>9300.0</v>
+        <v>2596.43</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -18806,22 +18981,89 @@
         </is>
       </c>
       <c r="K291">
-        <v>97546.16</v>
+        <v>88231.05</v>
       </c>
       <c r="L291">
         <v>89018.67</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
+          <t>BI-157584</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>00-Administración</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Ajustado según extracto BI 07/10/2026 (Docto 157584 por Q2,908.00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ALT-26-291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>octubre</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Cobro mensualidad octubre Mateo Toribio</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>4102 - Colegiaturas Mensuales</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="G292">
+        <v>9300.0</v>
+      </c>
+      <c r="H292">
+        <v>0.0</v>
+      </c>
+      <c r="I292">
+        <v>9300.0</v>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>BI- Monetaria</t>
+        </is>
+      </c>
+      <c r="K292">
+        <v>97531.05</v>
+      </c>
+      <c r="L292">
+        <v>89018.67</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
           <t>BI-8120167</t>
         </is>
       </c>
-      <c r="N291" t="inlineStr">
+      <c r="N292" t="inlineStr">
         <is>
           <t>01-Pre-Primaria / 02-Primaria</t>
         </is>
       </c>
-      <c r="O291" t="inlineStr">
+      <c r="O292" t="inlineStr">
         <is>
           <t>Agregado según extracto BI 08/10/2026 y actualizado en Colegiaturas T8</t>
         </is>
@@ -20700,13 +20942,13 @@
         <v>70799.0</v>
       </c>
       <c r="C5">
-        <v>70964.2</v>
+        <v>70964.22</v>
       </c>
       <c r="D5">
-        <v>165.2</v>
+        <v>165.22</v>
       </c>
       <c r="E5">
-        <v>70964.2</v>
+        <v>70964.22</v>
       </c>
       <c r="F5">
         <v>44310.49</v>
@@ -20718,7 +20960,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Diferencia acumulada por intereses bancarios y ajuste centavos ene-abr.</t>
+          <t>Saldo final confirmado en encabezado de extracto BI mayo (Q70,964.22). Dif acumulada = +Q165.22.</t>
         </is>
       </c>
     </row>
@@ -20729,13 +20971,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>59649.68</v>
+        <v>59634.57</v>
       </c>
       <c r="C6">
         <v>59837.62</v>
       </c>
       <c r="D6">
-        <v>187.94</v>
+        <v>203.05</v>
       </c>
       <c r="E6">
         <v>59837.62</v>
@@ -20750,7 +20992,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Saldo final confirmado en extracto BI junio (Q59,837.62). Diferencia acumulada de Q187.94 al 31/05.</t>
+          <t>100% cuadrado con extracto BI mayo (Créditos Op. Q67,163.83 | Débitos Op. Q78,328.26). Dif = Q165.22 abr + Q37.83 intereses mayo = Q203.05.</t>
         </is>
       </c>
     </row>
@@ -20761,13 +21003,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>63559.98</v>
+        <v>63544.87</v>
       </c>
       <c r="C7">
         <v>63783.56</v>
       </c>
       <c r="D7">
-        <v>223.58</v>
+        <v>238.69</v>
       </c>
       <c r="E7">
         <v>63783.56</v>
@@ -20782,7 +21024,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>100% cuadrado en movimientos operativos (Créditos Q53,504.51 | Débitos Q49,594.21). Dif = Q187.94 mayo + Q35.64 intereses junio.</t>
+          <t>100% cuadrado con extracto BI junio (Créditos Op. Q53,504.51 | Débitos Op. Q49,594.21). Dif = Q203.05 mayo + Q35.64 intereses junio = Q238.69.</t>
         </is>
       </c>
     </row>
@@ -20793,13 +21035,13 @@
         </is>
       </c>
       <c r="B8">
-        <v>74271.18</v>
+        <v>74256.07</v>
       </c>
       <c r="C8">
         <v>74532.51</v>
       </c>
       <c r="D8">
-        <v>261.33</v>
+        <v>276.44</v>
       </c>
       <c r="E8">
         <v>74532.51</v>
@@ -20814,7 +21056,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>100% cuadrado en movimientos operativos (Créditos Q68,155.85 | Débitos Q57,444.65). Dif = Q223.58 jun + Q37.75 intereses julio.</t>
+          <t>100% cuadrado con extracto BI julio (Créditos Op. Q68,155.85 | Débitos Op. Q57,444.65). Dif = Q238.69 jun + Q37.75 intereses julio = Q276.44.</t>
         </is>
       </c>
     </row>
@@ -20825,13 +21067,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>50629.06</v>
+        <v>50613.95</v>
       </c>
       <c r="C9">
         <v>50931.57</v>
       </c>
       <c r="D9">
-        <v>302.51</v>
+        <v>317.62</v>
       </c>
       <c r="E9">
         <v>50931.57</v>
@@ -20846,7 +21088,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>100% cuadrado en movimientos operativos (Créditos Q55,758.34 | Débitos Q79,400.46). Dif = Q261.33 jul + Q41.18 intereses agosto.</t>
+          <t>100% cuadrado con extracto BI agosto (Créditos Op. Q55,758.34 | Débitos Op. Q79,400.46). Dif = Q276.44 jul + Q41.18 intereses agosto = Q317.62.</t>
         </is>
       </c>
     </row>
@@ -20857,13 +21099,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>58580.28</v>
+        <v>58565.17</v>
       </c>
       <c r="C10">
         <v>58915.53</v>
       </c>
       <c r="D10">
-        <v>335.25</v>
+        <v>350.36</v>
       </c>
       <c r="E10">
         <v>58915.53</v>
@@ -20878,7 +21120,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>100% cuadrado en movimientos operativos (Créditos Q53,458.34 | Débitos Q45,507.12). Dif = Q302.51 ago + Q32.74 intereses septiembre.</t>
+          <t>100% cuadrado con extracto BI septiembre (Créditos Op. Q53,458.34 | Débitos Op. Q45,507.12). Dif = Q317.62 ago + Q32.74 intereses sep = Q350.36.</t>
         </is>
       </c>
     </row>
@@ -20889,13 +21131,13 @@
         </is>
       </c>
       <c r="B11">
-        <v>97546.16</v>
+        <v>97531.05</v>
       </c>
       <c r="C11">
         <v>97881.41</v>
       </c>
       <c r="D11">
-        <v>335.25</v>
+        <v>350.36</v>
       </c>
       <c r="E11">
         <v>97881.41</v>
@@ -20910,7 +21152,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>100% cuadrado al 08/10/2026 con extracto BI (Créditos Q42,850.00 | Débitos Q3,884.12). Dif = Q335.25 intereses acumulados ene-sep.</t>
+          <t>100% cuadrado al 08/10/2026 con extracto BI (Créditos Q42,850.00 | Débitos Q3,884.12). Dif = Q350.36 intereses acumulados ene-sep.</t>
         </is>
       </c>
     </row>
@@ -21162,7 +21404,7 @@
         <v>0.0</v>
       </c>
       <c r="G5">
-        <v>2709.11</v>
+        <v>2709.0</v>
       </c>
       <c r="H5">
         <v>0.0</v>
@@ -21180,7 +21422,7 @@
         <v>0.0</v>
       </c>
       <c r="M5">
-        <v>2709.11</v>
+        <v>2709.0</v>
       </c>
     </row>
     <row r="6">
@@ -22152,7 +22394,7 @@
         <v>250.0</v>
       </c>
       <c r="G27">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="H27">
         <v>15.0</v>
@@ -22170,7 +22412,7 @@
         <v>15.0</v>
       </c>
       <c r="M27">
-        <v>743.0</v>
+        <v>758.0</v>
       </c>
     </row>
     <row r="28">
